--- a/downloads/hr/output_automacao_hr.xlsx
+++ b/downloads/hr/output_automacao_hr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F371"/>
+  <dimension ref="A1:I371"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,9 +413,18 @@
         <v>link_datasource</v>
       </c>
       <c r="E1" t="str">
+        <v>origem</v>
+      </c>
+      <c r="F1" t="str">
+        <v>campos</v>
+      </c>
+      <c r="G1" t="str">
+        <v>tipo_campo</v>
+      </c>
+      <c r="H1" t="str">
         <v>schema</v>
       </c>
-      <c r="F1" t="str">
+      <c r="I1" t="str">
         <v>tabela</v>
       </c>
     </row>
@@ -433,9 +442,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F2" t="str">
+      <c r="I2" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -453,9 +471,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F3" t="str">
+      <c r="I3" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -473,9 +500,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F4" t="str">
+      <c r="I4" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -493,9 +529,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F5" t="str">
+      <c r="I5" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -513,9 +558,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F6" t="str">
+      <c r="I6" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -533,9 +587,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F7" t="str">
+      <c r="I7" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -553,9 +616,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F8" t="str">
+      <c r="I8" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -576,6 +648,15 @@
         <v/>
       </c>
       <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -596,6 +677,15 @@
         <v/>
       </c>
       <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -616,6 +706,15 @@
         <v/>
       </c>
       <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -636,6 +735,15 @@
         <v/>
       </c>
       <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -653,9 +761,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F13" t="str">
+      <c r="I13" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -673,9 +790,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F14" t="str">
+      <c r="I14" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -693,9 +819,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F15" t="str">
+      <c r="I15" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -713,9 +848,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F16" t="str">
+      <c r="I16" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -733,9 +877,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F17" t="str">
+      <c r="I17" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -753,9 +906,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F18" t="str">
+      <c r="I18" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -773,9 +935,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F19" t="str">
+      <c r="I19" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -796,6 +967,15 @@
         <v/>
       </c>
       <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -816,6 +996,15 @@
         <v/>
       </c>
       <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -836,6 +1025,15 @@
         <v/>
       </c>
       <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -856,6 +1054,15 @@
         <v/>
       </c>
       <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -876,6 +1083,15 @@
         <v/>
       </c>
       <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -896,6 +1112,15 @@
         <v/>
       </c>
       <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -916,6 +1141,15 @@
         <v/>
       </c>
       <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -936,6 +1170,15 @@
         <v/>
       </c>
       <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -956,6 +1199,15 @@
         <v/>
       </c>
       <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -976,6 +1228,15 @@
         <v/>
       </c>
       <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -996,6 +1257,15 @@
         <v/>
       </c>
       <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -1016,6 +1286,15 @@
         <v/>
       </c>
       <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1036,6 +1315,15 @@
         <v/>
       </c>
       <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1056,6 +1344,15 @@
         <v/>
       </c>
       <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1076,6 +1373,15 @@
         <v/>
       </c>
       <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1096,6 +1402,15 @@
         <v/>
       </c>
       <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1116,6 +1431,15 @@
         <v/>
       </c>
       <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1136,6 +1460,15 @@
         <v/>
       </c>
       <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1156,6 +1489,15 @@
         <v/>
       </c>
       <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1176,6 +1518,15 @@
         <v/>
       </c>
       <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -1196,6 +1547,15 @@
         <v/>
       </c>
       <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -1216,6 +1576,15 @@
         <v/>
       </c>
       <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1236,6 +1605,15 @@
         <v/>
       </c>
       <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1256,6 +1634,15 @@
         <v/>
       </c>
       <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1276,6 +1663,15 @@
         <v/>
       </c>
       <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1296,6 +1692,15 @@
         <v/>
       </c>
       <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1316,6 +1721,15 @@
         <v/>
       </c>
       <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1336,6 +1750,15 @@
         <v/>
       </c>
       <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1356,6 +1779,15 @@
         <v/>
       </c>
       <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1376,6 +1808,15 @@
         <v/>
       </c>
       <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -1396,6 +1837,15 @@
         <v/>
       </c>
       <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -1416,6 +1866,15 @@
         <v/>
       </c>
       <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1436,6 +1895,15 @@
         <v/>
       </c>
       <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1456,6 +1924,15 @@
         <v/>
       </c>
       <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1476,6 +1953,15 @@
         <v/>
       </c>
       <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1496,6 +1982,15 @@
         <v/>
       </c>
       <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1516,6 +2011,15 @@
         <v/>
       </c>
       <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1536,6 +2040,15 @@
         <v/>
       </c>
       <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1556,6 +2069,15 @@
         <v/>
       </c>
       <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1576,6 +2098,15 @@
         <v/>
       </c>
       <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -1596,6 +2127,15 @@
         <v/>
       </c>
       <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -1616,6 +2156,15 @@
         <v/>
       </c>
       <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1636,6 +2185,15 @@
         <v/>
       </c>
       <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1656,6 +2214,15 @@
         <v/>
       </c>
       <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1676,6 +2243,15 @@
         <v/>
       </c>
       <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1696,6 +2272,15 @@
         <v/>
       </c>
       <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1716,6 +2301,15 @@
         <v/>
       </c>
       <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1736,6 +2330,15 @@
         <v/>
       </c>
       <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1756,6 +2359,15 @@
         <v/>
       </c>
       <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1776,6 +2388,15 @@
         <v/>
       </c>
       <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -1793,9 +2414,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F70" t="str">
+      <c r="I70" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -1813,9 +2443,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F71" t="str">
+      <c r="I71" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -1833,9 +2472,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F72" t="str">
+      <c r="I72" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1853,9 +2501,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F73" t="str">
+      <c r="I73" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1873,9 +2530,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F74" t="str">
+      <c r="I74" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -1893,9 +2559,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F75" t="str">
+      <c r="I75" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -1913,9 +2588,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F76" t="str">
+      <c r="I76" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -1933,9 +2617,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F77" t="str">
+      <c r="I77" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -1953,9 +2646,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F78" t="str">
+      <c r="I78" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -1973,9 +2675,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F79" t="str">
+      <c r="I79" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1993,9 +2704,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F80" t="str">
+      <c r="I80" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2013,9 +2733,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F81" t="str">
+      <c r="I81" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -2033,9 +2762,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F82" t="str">
+      <c r="I82" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -2053,9 +2791,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F83" t="str">
+      <c r="I83" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -2073,9 +2820,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage</v>
       </c>
       <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
         <v>PORTALBI</v>
       </c>
-      <c r="F84" t="str">
+      <c r="I84" t="str">
         <v>FILIAL_COMPLEMENTO</v>
       </c>
     </row>
@@ -2093,9 +2849,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage</v>
       </c>
       <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F85" t="str">
+      <c r="I85" t="str">
         <v>F_PROMOCAO</v>
       </c>
     </row>
@@ -2113,9 +2878,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage</v>
       </c>
       <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
         <v>PORTALBI</v>
       </c>
-      <c r="F86" t="str">
+      <c r="I86" t="str">
         <v>FILIAL_COMPLEMENTO@TECNISAW</v>
       </c>
     </row>
@@ -2136,6 +2910,15 @@
         <v/>
       </c>
       <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -2156,6 +2939,15 @@
         <v/>
       </c>
       <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2176,6 +2968,15 @@
         <v/>
       </c>
       <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -2196,6 +2997,15 @@
         <v/>
       </c>
       <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -2216,6 +3026,15 @@
         <v/>
       </c>
       <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
         <v>F_PROMOCAO</v>
       </c>
     </row>
@@ -2236,6 +3055,15 @@
         <v/>
       </c>
       <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -2256,6 +3084,15 @@
         <v/>
       </c>
       <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2276,6 +3113,15 @@
         <v/>
       </c>
       <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -2296,6 +3142,15 @@
         <v/>
       </c>
       <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -2316,6 +3171,15 @@
         <v/>
       </c>
       <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
         <v>F_PROMOCAO</v>
       </c>
     </row>
@@ -2333,9 +3197,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F97" t="str">
+      <c r="I97" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -2353,9 +3226,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F98" t="str">
+      <c r="I98" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -2373,9 +3255,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F99" t="str">
+      <c r="I99" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -2393,9 +3284,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F100" t="str">
+      <c r="I100" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2413,9 +3313,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F101" t="str">
+      <c r="I101" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -2433,9 +3342,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F102" t="str">
+      <c r="I102" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -2453,9 +3371,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F103" t="str">
+      <c r="I103" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -2473,9 +3400,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage</v>
       </c>
       <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F104" t="str">
+      <c r="I104" t="str">
         <v>VW_EVT_RH_PONTO_ANALITICO</v>
       </c>
     </row>
@@ -2493,9 +3429,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage</v>
       </c>
       <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F105" t="str">
+      <c r="I105" t="str">
         <v>D_USUARIO_FILIAL</v>
       </c>
     </row>
@@ -2513,9 +3458,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage</v>
       </c>
       <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F106" t="str">
+      <c r="I106" t="str">
         <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
       </c>
     </row>
@@ -2533,9 +3487,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage</v>
       </c>
       <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F107" t="str">
+      <c r="I107" t="str">
         <v>D_USUARIO_FILIAL</v>
       </c>
     </row>
@@ -2556,6 +3519,15 @@
         <v/>
       </c>
       <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -2576,6 +3548,15 @@
         <v/>
       </c>
       <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
         <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
       </c>
     </row>
@@ -2596,6 +3577,15 @@
         <v/>
       </c>
       <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
         <v>VW_EVT_RH_PONTO_ANALITICO</v>
       </c>
     </row>
@@ -2616,6 +3606,15 @@
         <v/>
       </c>
       <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
         <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
       </c>
     </row>
@@ -2636,6 +3635,15 @@
         <v/>
       </c>
       <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -2656,6 +3664,15 @@
         <v/>
       </c>
       <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -2676,6 +3693,15 @@
         <v/>
       </c>
       <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
         <v>VW_D_FILIAL</v>
       </c>
     </row>
@@ -2696,6 +3722,15 @@
         <v/>
       </c>
       <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -2713,9 +3748,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F116" t="str">
+      <c r="I116" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -2733,9 +3777,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F117" t="str">
+      <c r="I117" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -2753,9 +3806,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F118" t="str">
+      <c r="I118" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -2773,9 +3835,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F119" t="str">
+      <c r="I119" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2793,9 +3864,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F120" t="str">
+      <c r="I120" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -2813,9 +3893,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F121" t="str">
+      <c r="I121" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -2833,9 +3922,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F122" t="str">
+      <c r="I122" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -2853,9 +3951,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F123" t="str">
+      <c r="I123" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -2873,9 +3980,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F124" t="str">
+      <c r="I124" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -2893,9 +4009,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F125" t="str">
+      <c r="I125" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -2913,9 +4038,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F126" t="str">
+      <c r="I126" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2933,9 +4067,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F127" t="str">
+      <c r="I127" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -2953,9 +4096,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F128" t="str">
+      <c r="I128" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -2973,9 +4125,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F129" t="str">
+      <c r="I129" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -2993,9 +4154,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F130" t="str">
+      <c r="I130" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -3013,9 +4183,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+      <c r="H131" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F131" t="str">
+      <c r="I131" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -3033,9 +4212,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F132" t="str">
+      <c r="I132" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -3053,9 +4241,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F133" t="str">
+      <c r="I133" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3073,9 +4270,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E134" t="str">
+        <v/>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+      <c r="H134" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F134" t="str">
+      <c r="I134" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -3093,9 +4299,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E135" t="str">
+        <v/>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+      <c r="H135" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F135" t="str">
+      <c r="I135" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -3113,9 +4328,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E136" t="str">
+        <v/>
+      </c>
+      <c r="F136" t="str">
+        <v/>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+      <c r="H136" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F136" t="str">
+      <c r="I136" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -3136,6 +4360,15 @@
         <v/>
       </c>
       <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+      <c r="H137" t="str">
+        <v/>
+      </c>
+      <c r="I137" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -3156,6 +4389,15 @@
         <v/>
       </c>
       <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+      <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3176,6 +4418,15 @@
         <v/>
       </c>
       <c r="F139" t="str">
+        <v/>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+      <c r="H139" t="str">
+        <v/>
+      </c>
+      <c r="I139" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -3196,6 +4447,15 @@
         <v/>
       </c>
       <c r="F140" t="str">
+        <v/>
+      </c>
+      <c r="G140" t="str">
+        <v/>
+      </c>
+      <c r="H140" t="str">
+        <v/>
+      </c>
+      <c r="I140" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -3216,6 +4476,15 @@
         <v/>
       </c>
       <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+      <c r="H141" t="str">
+        <v/>
+      </c>
+      <c r="I141" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -3236,6 +4505,15 @@
         <v/>
       </c>
       <c r="F142" t="str">
+        <v/>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+      <c r="H142" t="str">
+        <v/>
+      </c>
+      <c r="I142" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -3256,6 +4534,15 @@
         <v/>
       </c>
       <c r="F143" t="str">
+        <v/>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+      <c r="H143" t="str">
+        <v/>
+      </c>
+      <c r="I143" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -3276,6 +4563,15 @@
         <v/>
       </c>
       <c r="F144" t="str">
+        <v/>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+      <c r="H144" t="str">
+        <v/>
+      </c>
+      <c r="I144" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -3296,6 +4592,15 @@
         <v/>
       </c>
       <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+      <c r="H145" t="str">
+        <v/>
+      </c>
+      <c r="I145" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -3316,6 +4621,15 @@
         <v/>
       </c>
       <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v/>
+      </c>
+      <c r="I146" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -3336,6 +4650,15 @@
         <v/>
       </c>
       <c r="F147" t="str">
+        <v/>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+      <c r="H147" t="str">
+        <v/>
+      </c>
+      <c r="I147" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -3356,6 +4679,15 @@
         <v/>
       </c>
       <c r="F148" t="str">
+        <v/>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+      <c r="H148" t="str">
+        <v/>
+      </c>
+      <c r="I148" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -3376,6 +4708,15 @@
         <v/>
       </c>
       <c r="F149" t="str">
+        <v/>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+      <c r="H149" t="str">
+        <v/>
+      </c>
+      <c r="I149" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -3396,6 +4737,15 @@
         <v/>
       </c>
       <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+      <c r="H150" t="str">
+        <v/>
+      </c>
+      <c r="I150" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -3416,6 +4766,15 @@
         <v/>
       </c>
       <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151" t="str">
+        <v/>
+      </c>
+      <c r="H151" t="str">
+        <v/>
+      </c>
+      <c r="I151" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3436,6 +4795,15 @@
         <v/>
       </c>
       <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+      <c r="H152" t="str">
+        <v/>
+      </c>
+      <c r="I152" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -3456,6 +4824,15 @@
         <v/>
       </c>
       <c r="F153" t="str">
+        <v/>
+      </c>
+      <c r="G153" t="str">
+        <v/>
+      </c>
+      <c r="H153" t="str">
+        <v/>
+      </c>
+      <c r="I153" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -3476,6 +4853,15 @@
         <v/>
       </c>
       <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+      <c r="H154" t="str">
+        <v/>
+      </c>
+      <c r="I154" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -3496,6 +4882,15 @@
         <v/>
       </c>
       <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v/>
+      </c>
+      <c r="H155" t="str">
+        <v/>
+      </c>
+      <c r="I155" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -3516,6 +4911,15 @@
         <v/>
       </c>
       <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156" t="str">
+        <v/>
+      </c>
+      <c r="H156" t="str">
+        <v/>
+      </c>
+      <c r="I156" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -3536,6 +4940,15 @@
         <v/>
       </c>
       <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+      <c r="H157" t="str">
+        <v/>
+      </c>
+      <c r="I157" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -3556,6 +4969,15 @@
         <v/>
       </c>
       <c r="F158" t="str">
+        <v/>
+      </c>
+      <c r="G158" t="str">
+        <v/>
+      </c>
+      <c r="H158" t="str">
+        <v/>
+      </c>
+      <c r="I158" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -3576,6 +4998,15 @@
         <v/>
       </c>
       <c r="F159" t="str">
+        <v/>
+      </c>
+      <c r="G159" t="str">
+        <v/>
+      </c>
+      <c r="H159" t="str">
+        <v/>
+      </c>
+      <c r="I159" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -3596,6 +5027,15 @@
         <v/>
       </c>
       <c r="F160" t="str">
+        <v/>
+      </c>
+      <c r="G160" t="str">
+        <v/>
+      </c>
+      <c r="H160" t="str">
+        <v/>
+      </c>
+      <c r="I160" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -3616,6 +5056,15 @@
         <v/>
       </c>
       <c r="F161" t="str">
+        <v/>
+      </c>
+      <c r="G161" t="str">
+        <v/>
+      </c>
+      <c r="H161" t="str">
+        <v/>
+      </c>
+      <c r="I161" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -3636,6 +5085,15 @@
         <v/>
       </c>
       <c r="F162" t="str">
+        <v/>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+      <c r="H162" t="str">
+        <v/>
+      </c>
+      <c r="I162" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -3656,6 +5114,15 @@
         <v/>
       </c>
       <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v/>
+      </c>
+      <c r="I163" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -3676,6 +5143,15 @@
         <v/>
       </c>
       <c r="F164" t="str">
+        <v/>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+      <c r="H164" t="str">
+        <v/>
+      </c>
+      <c r="I164" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3696,6 +5172,15 @@
         <v/>
       </c>
       <c r="F165" t="str">
+        <v/>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+      <c r="H165" t="str">
+        <v/>
+      </c>
+      <c r="I165" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -3716,6 +5201,15 @@
         <v/>
       </c>
       <c r="F166" t="str">
+        <v/>
+      </c>
+      <c r="G166" t="str">
+        <v/>
+      </c>
+      <c r="H166" t="str">
+        <v/>
+      </c>
+      <c r="I166" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -3736,6 +5230,15 @@
         <v/>
       </c>
       <c r="F167" t="str">
+        <v/>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+      <c r="H167" t="str">
+        <v/>
+      </c>
+      <c r="I167" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -3756,6 +5259,15 @@
         <v/>
       </c>
       <c r="F168" t="str">
+        <v/>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+      <c r="H168" t="str">
+        <v/>
+      </c>
+      <c r="I168" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -3776,6 +5288,15 @@
         <v/>
       </c>
       <c r="F169" t="str">
+        <v/>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+      <c r="H169" t="str">
+        <v/>
+      </c>
+      <c r="I169" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -3796,6 +5317,15 @@
         <v/>
       </c>
       <c r="F170" t="str">
+        <v/>
+      </c>
+      <c r="G170" t="str">
+        <v/>
+      </c>
+      <c r="H170" t="str">
+        <v/>
+      </c>
+      <c r="I170" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -3816,6 +5346,15 @@
         <v/>
       </c>
       <c r="F171" t="str">
+        <v/>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+      <c r="H171" t="str">
+        <v/>
+      </c>
+      <c r="I171" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -3836,6 +5375,15 @@
         <v/>
       </c>
       <c r="F172" t="str">
+        <v/>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+      <c r="H172" t="str">
+        <v/>
+      </c>
+      <c r="I172" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -3856,6 +5404,15 @@
         <v/>
       </c>
       <c r="F173" t="str">
+        <v/>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+      <c r="H173" t="str">
+        <v/>
+      </c>
+      <c r="I173" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -3876,6 +5433,15 @@
         <v/>
       </c>
       <c r="F174" t="str">
+        <v/>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+      <c r="H174" t="str">
+        <v/>
+      </c>
+      <c r="I174" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -3896,6 +5462,15 @@
         <v/>
       </c>
       <c r="F175" t="str">
+        <v/>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+      <c r="H175" t="str">
+        <v/>
+      </c>
+      <c r="I175" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -3916,6 +5491,15 @@
         <v/>
       </c>
       <c r="F176" t="str">
+        <v/>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+      <c r="H176" t="str">
+        <v/>
+      </c>
+      <c r="I176" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -3936,6 +5520,15 @@
         <v/>
       </c>
       <c r="F177" t="str">
+        <v/>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+      <c r="H177" t="str">
+        <v/>
+      </c>
+      <c r="I177" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3956,6 +5549,15 @@
         <v/>
       </c>
       <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+      <c r="H178" t="str">
+        <v/>
+      </c>
+      <c r="I178" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -3976,6 +5578,15 @@
         <v/>
       </c>
       <c r="F179" t="str">
+        <v/>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+      <c r="H179" t="str">
+        <v/>
+      </c>
+      <c r="I179" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -3996,6 +5607,15 @@
         <v/>
       </c>
       <c r="F180" t="str">
+        <v/>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+      <c r="H180" t="str">
+        <v/>
+      </c>
+      <c r="I180" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -4016,6 +5636,15 @@
         <v/>
       </c>
       <c r="F181" t="str">
+        <v/>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+      <c r="H181" t="str">
+        <v/>
+      </c>
+      <c r="I181" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -4036,6 +5665,15 @@
         <v/>
       </c>
       <c r="F182" t="str">
+        <v/>
+      </c>
+      <c r="G182" t="str">
+        <v/>
+      </c>
+      <c r="H182" t="str">
+        <v/>
+      </c>
+      <c r="I182" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -4056,6 +5694,15 @@
         <v/>
       </c>
       <c r="F183" t="str">
+        <v/>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+      <c r="H183" t="str">
+        <v/>
+      </c>
+      <c r="I183" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -4076,6 +5723,15 @@
         <v/>
       </c>
       <c r="F184" t="str">
+        <v/>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+      <c r="H184" t="str">
+        <v/>
+      </c>
+      <c r="I184" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -4096,6 +5752,15 @@
         <v/>
       </c>
       <c r="F185" t="str">
+        <v/>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+      <c r="H185" t="str">
+        <v/>
+      </c>
+      <c r="I185" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -4116,6 +5781,15 @@
         <v/>
       </c>
       <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+      <c r="H186" t="str">
+        <v/>
+      </c>
+      <c r="I186" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -4136,6 +5810,15 @@
         <v/>
       </c>
       <c r="F187" t="str">
+        <v/>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+      <c r="H187" t="str">
+        <v/>
+      </c>
+      <c r="I187" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -4156,6 +5839,15 @@
         <v/>
       </c>
       <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+      <c r="H188" t="str">
+        <v/>
+      </c>
+      <c r="I188" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -4176,6 +5868,15 @@
         <v/>
       </c>
       <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+      <c r="H189" t="str">
+        <v/>
+      </c>
+      <c r="I189" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -4196,6 +5897,15 @@
         <v/>
       </c>
       <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v/>
+      </c>
+      <c r="I190" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -4216,6 +5926,15 @@
         <v/>
       </c>
       <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v/>
+      </c>
+      <c r="I191" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -4236,6 +5955,15 @@
         <v/>
       </c>
       <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v/>
+      </c>
+      <c r="I192" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -4256,6 +5984,15 @@
         <v/>
       </c>
       <c r="F193" t="str">
+        <v/>
+      </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v/>
+      </c>
+      <c r="I193" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -4276,6 +6013,15 @@
         <v/>
       </c>
       <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+      <c r="H194" t="str">
+        <v/>
+      </c>
+      <c r="I194" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -4296,6 +6042,15 @@
         <v/>
       </c>
       <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195" t="str">
+        <v/>
+      </c>
+      <c r="H195" t="str">
+        <v/>
+      </c>
+      <c r="I195" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -4316,6 +6071,15 @@
         <v/>
       </c>
       <c r="F196" t="str">
+        <v/>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+      <c r="H196" t="str">
+        <v/>
+      </c>
+      <c r="I196" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -4336,6 +6100,15 @@
         <v/>
       </c>
       <c r="F197" t="str">
+        <v/>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+      <c r="H197" t="str">
+        <v/>
+      </c>
+      <c r="I197" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -4356,6 +6129,15 @@
         <v/>
       </c>
       <c r="F198" t="str">
+        <v/>
+      </c>
+      <c r="G198" t="str">
+        <v/>
+      </c>
+      <c r="H198" t="str">
+        <v/>
+      </c>
+      <c r="I198" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -4376,6 +6158,15 @@
         <v/>
       </c>
       <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199" t="str">
+        <v/>
+      </c>
+      <c r="H199" t="str">
+        <v/>
+      </c>
+      <c r="I199" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -4396,6 +6187,15 @@
         <v/>
       </c>
       <c r="F200" t="str">
+        <v/>
+      </c>
+      <c r="G200" t="str">
+        <v/>
+      </c>
+      <c r="H200" t="str">
+        <v/>
+      </c>
+      <c r="I200" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -4416,6 +6216,15 @@
         <v/>
       </c>
       <c r="F201" t="str">
+        <v/>
+      </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+      <c r="H201" t="str">
+        <v/>
+      </c>
+      <c r="I201" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -4433,9 +6242,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v/>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+      <c r="H202" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F202" t="str">
+      <c r="I202" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -4453,9 +6271,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v/>
+      </c>
+      <c r="G203" t="str">
+        <v/>
+      </c>
+      <c r="H203" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F203" t="str">
+      <c r="I203" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -4473,9 +6300,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+      <c r="H204" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F204" t="str">
+      <c r="I204" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -4493,9 +6329,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+      <c r="H205" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F205" t="str">
+      <c r="I205" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -4513,9 +6358,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+      <c r="H206" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F206" t="str">
+      <c r="I206" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -4533,9 +6387,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+      <c r="H207" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F207" t="str">
+      <c r="I207" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -4553,9 +6416,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v/>
+      </c>
+      <c r="G208" t="str">
+        <v/>
+      </c>
+      <c r="H208" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F208" t="str">
+      <c r="I208" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -4576,6 +6448,15 @@
         <v/>
       </c>
       <c r="F209" t="str">
+        <v/>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+      <c r="H209" t="str">
+        <v/>
+      </c>
+      <c r="I209" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -4596,6 +6477,15 @@
         <v/>
       </c>
       <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+      <c r="H210" t="str">
+        <v/>
+      </c>
+      <c r="I210" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -4616,6 +6506,15 @@
         <v/>
       </c>
       <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+      <c r="H211" t="str">
+        <v/>
+      </c>
+      <c r="I211" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -4636,6 +6535,15 @@
         <v/>
       </c>
       <c r="F212" t="str">
+        <v/>
+      </c>
+      <c r="G212" t="str">
+        <v/>
+      </c>
+      <c r="H212" t="str">
+        <v/>
+      </c>
+      <c r="I212" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -4656,6 +6564,15 @@
         <v/>
       </c>
       <c r="F213" t="str">
+        <v/>
+      </c>
+      <c r="G213" t="str">
+        <v/>
+      </c>
+      <c r="H213" t="str">
+        <v/>
+      </c>
+      <c r="I213" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -4676,6 +6593,15 @@
         <v/>
       </c>
       <c r="F214" t="str">
+        <v/>
+      </c>
+      <c r="G214" t="str">
+        <v/>
+      </c>
+      <c r="H214" t="str">
+        <v/>
+      </c>
+      <c r="I214" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -4696,6 +6622,15 @@
         <v/>
       </c>
       <c r="F215" t="str">
+        <v/>
+      </c>
+      <c r="G215" t="str">
+        <v/>
+      </c>
+      <c r="H215" t="str">
+        <v/>
+      </c>
+      <c r="I215" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -4716,6 +6651,15 @@
         <v/>
       </c>
       <c r="F216" t="str">
+        <v/>
+      </c>
+      <c r="G216" t="str">
+        <v/>
+      </c>
+      <c r="H216" t="str">
+        <v/>
+      </c>
+      <c r="I216" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -4736,6 +6680,15 @@
         <v/>
       </c>
       <c r="F217" t="str">
+        <v/>
+      </c>
+      <c r="G217" t="str">
+        <v/>
+      </c>
+      <c r="H217" t="str">
+        <v/>
+      </c>
+      <c r="I217" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -4756,6 +6709,15 @@
         <v/>
       </c>
       <c r="F218" t="str">
+        <v/>
+      </c>
+      <c r="G218" t="str">
+        <v/>
+      </c>
+      <c r="H218" t="str">
+        <v/>
+      </c>
+      <c r="I218" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -4776,6 +6738,15 @@
         <v/>
       </c>
       <c r="F219" t="str">
+        <v/>
+      </c>
+      <c r="G219" t="str">
+        <v/>
+      </c>
+      <c r="H219" t="str">
+        <v/>
+      </c>
+      <c r="I219" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -4796,6 +6767,15 @@
         <v/>
       </c>
       <c r="F220" t="str">
+        <v/>
+      </c>
+      <c r="G220" t="str">
+        <v/>
+      </c>
+      <c r="H220" t="str">
+        <v/>
+      </c>
+      <c r="I220" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -4816,6 +6796,15 @@
         <v/>
       </c>
       <c r="F221" t="str">
+        <v/>
+      </c>
+      <c r="G221" t="str">
+        <v/>
+      </c>
+      <c r="H221" t="str">
+        <v/>
+      </c>
+      <c r="I221" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -4836,6 +6825,15 @@
         <v/>
       </c>
       <c r="F222" t="str">
+        <v/>
+      </c>
+      <c r="G222" t="str">
+        <v/>
+      </c>
+      <c r="H222" t="str">
+        <v/>
+      </c>
+      <c r="I222" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -4856,6 +6854,15 @@
         <v/>
       </c>
       <c r="F223" t="str">
+        <v/>
+      </c>
+      <c r="G223" t="str">
+        <v/>
+      </c>
+      <c r="H223" t="str">
+        <v/>
+      </c>
+      <c r="I223" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -4876,6 +6883,15 @@
         <v/>
       </c>
       <c r="F224" t="str">
+        <v/>
+      </c>
+      <c r="G224" t="str">
+        <v/>
+      </c>
+      <c r="H224" t="str">
+        <v/>
+      </c>
+      <c r="I224" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -4896,6 +6912,15 @@
         <v/>
       </c>
       <c r="F225" t="str">
+        <v/>
+      </c>
+      <c r="G225" t="str">
+        <v/>
+      </c>
+      <c r="H225" t="str">
+        <v/>
+      </c>
+      <c r="I225" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -4916,6 +6941,15 @@
         <v/>
       </c>
       <c r="F226" t="str">
+        <v/>
+      </c>
+      <c r="G226" t="str">
+        <v/>
+      </c>
+      <c r="H226" t="str">
+        <v/>
+      </c>
+      <c r="I226" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -4936,6 +6970,15 @@
         <v/>
       </c>
       <c r="F227" t="str">
+        <v/>
+      </c>
+      <c r="G227" t="str">
+        <v/>
+      </c>
+      <c r="H227" t="str">
+        <v/>
+      </c>
+      <c r="I227" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -4956,6 +6999,15 @@
         <v/>
       </c>
       <c r="F228" t="str">
+        <v/>
+      </c>
+      <c r="G228" t="str">
+        <v/>
+      </c>
+      <c r="H228" t="str">
+        <v/>
+      </c>
+      <c r="I228" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -4976,6 +7028,15 @@
         <v/>
       </c>
       <c r="F229" t="str">
+        <v/>
+      </c>
+      <c r="G229" t="str">
+        <v/>
+      </c>
+      <c r="H229" t="str">
+        <v/>
+      </c>
+      <c r="I229" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -4996,6 +7057,15 @@
         <v/>
       </c>
       <c r="F230" t="str">
+        <v/>
+      </c>
+      <c r="G230" t="str">
+        <v/>
+      </c>
+      <c r="H230" t="str">
+        <v/>
+      </c>
+      <c r="I230" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5016,6 +7086,15 @@
         <v/>
       </c>
       <c r="F231" t="str">
+        <v/>
+      </c>
+      <c r="G231" t="str">
+        <v/>
+      </c>
+      <c r="H231" t="str">
+        <v/>
+      </c>
+      <c r="I231" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5036,6 +7115,15 @@
         <v/>
       </c>
       <c r="F232" t="str">
+        <v/>
+      </c>
+      <c r="G232" t="str">
+        <v/>
+      </c>
+      <c r="H232" t="str">
+        <v/>
+      </c>
+      <c r="I232" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5056,6 +7144,15 @@
         <v/>
       </c>
       <c r="F233" t="str">
+        <v/>
+      </c>
+      <c r="G233" t="str">
+        <v/>
+      </c>
+      <c r="H233" t="str">
+        <v/>
+      </c>
+      <c r="I233" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5076,6 +7173,15 @@
         <v/>
       </c>
       <c r="F234" t="str">
+        <v/>
+      </c>
+      <c r="G234" t="str">
+        <v/>
+      </c>
+      <c r="H234" t="str">
+        <v/>
+      </c>
+      <c r="I234" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -5096,6 +7202,15 @@
         <v/>
       </c>
       <c r="F235" t="str">
+        <v/>
+      </c>
+      <c r="G235" t="str">
+        <v/>
+      </c>
+      <c r="H235" t="str">
+        <v/>
+      </c>
+      <c r="I235" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -5116,6 +7231,15 @@
         <v/>
       </c>
       <c r="F236" t="str">
+        <v/>
+      </c>
+      <c r="G236" t="str">
+        <v/>
+      </c>
+      <c r="H236" t="str">
+        <v/>
+      </c>
+      <c r="I236" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -5136,6 +7260,15 @@
         <v/>
       </c>
       <c r="F237" t="str">
+        <v/>
+      </c>
+      <c r="G237" t="str">
+        <v/>
+      </c>
+      <c r="H237" t="str">
+        <v/>
+      </c>
+      <c r="I237" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5156,6 +7289,15 @@
         <v/>
       </c>
       <c r="F238" t="str">
+        <v/>
+      </c>
+      <c r="G238" t="str">
+        <v/>
+      </c>
+      <c r="H238" t="str">
+        <v/>
+      </c>
+      <c r="I238" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5176,6 +7318,15 @@
         <v/>
       </c>
       <c r="F239" t="str">
+        <v/>
+      </c>
+      <c r="G239" t="str">
+        <v/>
+      </c>
+      <c r="H239" t="str">
+        <v/>
+      </c>
+      <c r="I239" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5196,6 +7347,15 @@
         <v/>
       </c>
       <c r="F240" t="str">
+        <v/>
+      </c>
+      <c r="G240" t="str">
+        <v/>
+      </c>
+      <c r="H240" t="str">
+        <v/>
+      </c>
+      <c r="I240" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5216,6 +7376,15 @@
         <v/>
       </c>
       <c r="F241" t="str">
+        <v/>
+      </c>
+      <c r="G241" t="str">
+        <v/>
+      </c>
+      <c r="H241" t="str">
+        <v/>
+      </c>
+      <c r="I241" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -5236,6 +7405,15 @@
         <v/>
       </c>
       <c r="F242" t="str">
+        <v/>
+      </c>
+      <c r="G242" t="str">
+        <v/>
+      </c>
+      <c r="H242" t="str">
+        <v/>
+      </c>
+      <c r="I242" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -5256,6 +7434,15 @@
         <v/>
       </c>
       <c r="F243" t="str">
+        <v/>
+      </c>
+      <c r="G243" t="str">
+        <v/>
+      </c>
+      <c r="H243" t="str">
+        <v/>
+      </c>
+      <c r="I243" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -5276,6 +7463,15 @@
         <v/>
       </c>
       <c r="F244" t="str">
+        <v/>
+      </c>
+      <c r="G244" t="str">
+        <v/>
+      </c>
+      <c r="H244" t="str">
+        <v/>
+      </c>
+      <c r="I244" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5296,6 +7492,15 @@
         <v/>
       </c>
       <c r="F245" t="str">
+        <v/>
+      </c>
+      <c r="G245" t="str">
+        <v/>
+      </c>
+      <c r="H245" t="str">
+        <v/>
+      </c>
+      <c r="I245" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5316,6 +7521,15 @@
         <v/>
       </c>
       <c r="F246" t="str">
+        <v/>
+      </c>
+      <c r="G246" t="str">
+        <v/>
+      </c>
+      <c r="H246" t="str">
+        <v/>
+      </c>
+      <c r="I246" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5336,6 +7550,15 @@
         <v/>
       </c>
       <c r="F247" t="str">
+        <v/>
+      </c>
+      <c r="G247" t="str">
+        <v/>
+      </c>
+      <c r="H247" t="str">
+        <v/>
+      </c>
+      <c r="I247" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5356,6 +7579,15 @@
         <v/>
       </c>
       <c r="F248" t="str">
+        <v/>
+      </c>
+      <c r="G248" t="str">
+        <v/>
+      </c>
+      <c r="H248" t="str">
+        <v/>
+      </c>
+      <c r="I248" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -5376,6 +7608,15 @@
         <v/>
       </c>
       <c r="F249" t="str">
+        <v/>
+      </c>
+      <c r="G249" t="str">
+        <v/>
+      </c>
+      <c r="H249" t="str">
+        <v/>
+      </c>
+      <c r="I249" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -5396,6 +7637,15 @@
         <v/>
       </c>
       <c r="F250" t="str">
+        <v/>
+      </c>
+      <c r="G250" t="str">
+        <v/>
+      </c>
+      <c r="H250" t="str">
+        <v/>
+      </c>
+      <c r="I250" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -5416,6 +7666,15 @@
         <v/>
       </c>
       <c r="F251" t="str">
+        <v/>
+      </c>
+      <c r="G251" t="str">
+        <v/>
+      </c>
+      <c r="H251" t="str">
+        <v/>
+      </c>
+      <c r="I251" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -5436,6 +7695,15 @@
         <v/>
       </c>
       <c r="F252" t="str">
+        <v/>
+      </c>
+      <c r="G252" t="str">
+        <v/>
+      </c>
+      <c r="H252" t="str">
+        <v/>
+      </c>
+      <c r="I252" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -5456,6 +7724,15 @@
         <v/>
       </c>
       <c r="F253" t="str">
+        <v/>
+      </c>
+      <c r="G253" t="str">
+        <v/>
+      </c>
+      <c r="H253" t="str">
+        <v/>
+      </c>
+      <c r="I253" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -5476,6 +7753,15 @@
         <v/>
       </c>
       <c r="F254" t="str">
+        <v/>
+      </c>
+      <c r="G254" t="str">
+        <v/>
+      </c>
+      <c r="H254" t="str">
+        <v/>
+      </c>
+      <c r="I254" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -5496,6 +7782,15 @@
         <v/>
       </c>
       <c r="F255" t="str">
+        <v/>
+      </c>
+      <c r="G255" t="str">
+        <v/>
+      </c>
+      <c r="H255" t="str">
+        <v/>
+      </c>
+      <c r="I255" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -5513,9 +7808,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E256" t="str">
+        <v/>
+      </c>
+      <c r="F256" t="str">
+        <v/>
+      </c>
+      <c r="G256" t="str">
+        <v/>
+      </c>
+      <c r="H256" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F256" t="str">
+      <c r="I256" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -5533,9 +7837,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E257" t="str">
+        <v/>
+      </c>
+      <c r="F257" t="str">
+        <v/>
+      </c>
+      <c r="G257" t="str">
+        <v/>
+      </c>
+      <c r="H257" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F257" t="str">
+      <c r="I257" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -5553,9 +7866,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E258" t="str">
+        <v/>
+      </c>
+      <c r="F258" t="str">
+        <v/>
+      </c>
+      <c r="G258" t="str">
+        <v/>
+      </c>
+      <c r="H258" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F258" t="str">
+      <c r="I258" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -5573,9 +7895,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E259" t="str">
+        <v/>
+      </c>
+      <c r="F259" t="str">
+        <v/>
+      </c>
+      <c r="G259" t="str">
+        <v/>
+      </c>
+      <c r="H259" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F259" t="str">
+      <c r="I259" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5593,9 +7924,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E260" t="str">
+        <v/>
+      </c>
+      <c r="F260" t="str">
+        <v/>
+      </c>
+      <c r="G260" t="str">
+        <v/>
+      </c>
+      <c r="H260" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F260" t="str">
+      <c r="I260" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -5613,9 +7953,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E261" t="str">
+        <v/>
+      </c>
+      <c r="F261" t="str">
+        <v/>
+      </c>
+      <c r="G261" t="str">
+        <v/>
+      </c>
+      <c r="H261" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F261" t="str">
+      <c r="I261" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -5633,9 +7982,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E262" t="str">
+        <v/>
+      </c>
+      <c r="F262" t="str">
+        <v/>
+      </c>
+      <c r="G262" t="str">
+        <v/>
+      </c>
+      <c r="H262" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F262" t="str">
+      <c r="I262" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -5656,6 +8014,15 @@
         <v/>
       </c>
       <c r="F263" t="str">
+        <v/>
+      </c>
+      <c r="G263" t="str">
+        <v/>
+      </c>
+      <c r="H263" t="str">
+        <v/>
+      </c>
+      <c r="I263" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5676,6 +8043,15 @@
         <v/>
       </c>
       <c r="F264" t="str">
+        <v/>
+      </c>
+      <c r="G264" t="str">
+        <v/>
+      </c>
+      <c r="H264" t="str">
+        <v/>
+      </c>
+      <c r="I264" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5696,6 +8072,15 @@
         <v/>
       </c>
       <c r="F265" t="str">
+        <v/>
+      </c>
+      <c r="G265" t="str">
+        <v/>
+      </c>
+      <c r="H265" t="str">
+        <v/>
+      </c>
+      <c r="I265" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5716,6 +8101,15 @@
         <v/>
       </c>
       <c r="F266" t="str">
+        <v/>
+      </c>
+      <c r="G266" t="str">
+        <v/>
+      </c>
+      <c r="H266" t="str">
+        <v/>
+      </c>
+      <c r="I266" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5736,6 +8130,15 @@
         <v/>
       </c>
       <c r="F267" t="str">
+        <v/>
+      </c>
+      <c r="G267" t="str">
+        <v/>
+      </c>
+      <c r="H267" t="str">
+        <v/>
+      </c>
+      <c r="I267" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5756,6 +8159,15 @@
         <v/>
       </c>
       <c r="F268" t="str">
+        <v/>
+      </c>
+      <c r="G268" t="str">
+        <v/>
+      </c>
+      <c r="H268" t="str">
+        <v/>
+      </c>
+      <c r="I268" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5776,6 +8188,15 @@
         <v/>
       </c>
       <c r="F269" t="str">
+        <v/>
+      </c>
+      <c r="G269" t="str">
+        <v/>
+      </c>
+      <c r="H269" t="str">
+        <v/>
+      </c>
+      <c r="I269" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5796,6 +8217,15 @@
         <v/>
       </c>
       <c r="F270" t="str">
+        <v/>
+      </c>
+      <c r="G270" t="str">
+        <v/>
+      </c>
+      <c r="H270" t="str">
+        <v/>
+      </c>
+      <c r="I270" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5816,6 +8246,15 @@
         <v/>
       </c>
       <c r="F271" t="str">
+        <v/>
+      </c>
+      <c r="G271" t="str">
+        <v/>
+      </c>
+      <c r="H271" t="str">
+        <v/>
+      </c>
+      <c r="I271" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -5833,9 +8272,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E272" t="str">
+        <v/>
+      </c>
+      <c r="F272" t="str">
+        <v/>
+      </c>
+      <c r="G272" t="str">
+        <v/>
+      </c>
+      <c r="H272" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F272" t="str">
+      <c r="I272" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -5853,9 +8301,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E273" t="str">
+        <v/>
+      </c>
+      <c r="F273" t="str">
+        <v/>
+      </c>
+      <c r="G273" t="str">
+        <v/>
+      </c>
+      <c r="H273" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F273" t="str">
+      <c r="I273" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -5873,9 +8330,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E274" t="str">
+        <v/>
+      </c>
+      <c r="F274" t="str">
+        <v/>
+      </c>
+      <c r="G274" t="str">
+        <v/>
+      </c>
+      <c r="H274" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F274" t="str">
+      <c r="I274" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -5893,9 +8359,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E275" t="str">
+        <v/>
+      </c>
+      <c r="F275" t="str">
+        <v/>
+      </c>
+      <c r="G275" t="str">
+        <v/>
+      </c>
+      <c r="H275" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F275" t="str">
+      <c r="I275" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5913,9 +8388,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E276" t="str">
+        <v/>
+      </c>
+      <c r="F276" t="str">
+        <v/>
+      </c>
+      <c r="G276" t="str">
+        <v/>
+      </c>
+      <c r="H276" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F276" t="str">
+      <c r="I276" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -5933,9 +8417,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E277" t="str">
+        <v/>
+      </c>
+      <c r="F277" t="str">
+        <v/>
+      </c>
+      <c r="G277" t="str">
+        <v/>
+      </c>
+      <c r="H277" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F277" t="str">
+      <c r="I277" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -5953,9 +8446,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E278" t="str">
+        <v/>
+      </c>
+      <c r="F278" t="str">
+        <v/>
+      </c>
+      <c r="G278" t="str">
+        <v/>
+      </c>
+      <c r="H278" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F278" t="str">
+      <c r="I278" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -5973,9 +8475,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E279" t="str">
+        <v/>
+      </c>
+      <c r="F279" t="str">
+        <v/>
+      </c>
+      <c r="G279" t="str">
+        <v/>
+      </c>
+      <c r="H279" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F279" t="str">
+      <c r="I279" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -5993,9 +8504,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E280" t="str">
+        <v/>
+      </c>
+      <c r="F280" t="str">
+        <v/>
+      </c>
+      <c r="G280" t="str">
+        <v/>
+      </c>
+      <c r="H280" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F280" t="str">
+      <c r="I280" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -6013,9 +8533,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E281" t="str">
+        <v/>
+      </c>
+      <c r="F281" t="str">
+        <v/>
+      </c>
+      <c r="G281" t="str">
+        <v/>
+      </c>
+      <c r="H281" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F281" t="str">
+      <c r="I281" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -6033,9 +8562,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E282" t="str">
+        <v/>
+      </c>
+      <c r="F282" t="str">
+        <v/>
+      </c>
+      <c r="G282" t="str">
+        <v/>
+      </c>
+      <c r="H282" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F282" t="str">
+      <c r="I282" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6053,9 +8591,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E283" t="str">
+        <v/>
+      </c>
+      <c r="F283" t="str">
+        <v/>
+      </c>
+      <c r="G283" t="str">
+        <v/>
+      </c>
+      <c r="H283" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F283" t="str">
+      <c r="I283" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -6073,9 +8620,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E284" t="str">
+        <v/>
+      </c>
+      <c r="F284" t="str">
+        <v/>
+      </c>
+      <c r="G284" t="str">
+        <v/>
+      </c>
+      <c r="H284" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F284" t="str">
+      <c r="I284" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -6093,9 +8649,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E285" t="str">
+        <v/>
+      </c>
+      <c r="F285" t="str">
+        <v/>
+      </c>
+      <c r="G285" t="str">
+        <v/>
+      </c>
+      <c r="H285" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F285" t="str">
+      <c r="I285" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -6116,6 +8681,15 @@
         <v/>
       </c>
       <c r="F286" t="str">
+        <v/>
+      </c>
+      <c r="G286" t="str">
+        <v/>
+      </c>
+      <c r="H286" t="str">
+        <v/>
+      </c>
+      <c r="I286" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -6136,6 +8710,15 @@
         <v/>
       </c>
       <c r="F287" t="str">
+        <v/>
+      </c>
+      <c r="G287" t="str">
+        <v/>
+      </c>
+      <c r="H287" t="str">
+        <v/>
+      </c>
+      <c r="I287" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -6156,6 +8739,15 @@
         <v/>
       </c>
       <c r="F288" t="str">
+        <v/>
+      </c>
+      <c r="G288" t="str">
+        <v/>
+      </c>
+      <c r="H288" t="str">
+        <v/>
+      </c>
+      <c r="I288" t="str">
         <v>VW_D_FILIAL</v>
       </c>
     </row>
@@ -6176,6 +8768,15 @@
         <v/>
       </c>
       <c r="F289" t="str">
+        <v/>
+      </c>
+      <c r="G289" t="str">
+        <v/>
+      </c>
+      <c r="H289" t="str">
+        <v/>
+      </c>
+      <c r="I289" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -6193,9 +8794,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E290" t="str">
+        <v/>
+      </c>
+      <c r="F290" t="str">
+        <v/>
+      </c>
+      <c r="G290" t="str">
+        <v/>
+      </c>
+      <c r="H290" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F290" t="str">
+      <c r="I290" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -6216,6 +8826,15 @@
         <v/>
       </c>
       <c r="F291" t="str">
+        <v/>
+      </c>
+      <c r="G291" t="str">
+        <v/>
+      </c>
+      <c r="H291" t="str">
+        <v/>
+      </c>
+      <c r="I291" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -6233,9 +8852,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E292" t="str">
+        <v/>
+      </c>
+      <c r="F292" t="str">
+        <v/>
+      </c>
+      <c r="G292" t="str">
+        <v/>
+      </c>
+      <c r="H292" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F292" t="str">
+      <c r="I292" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -6253,9 +8881,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E293" t="str">
+        <v/>
+      </c>
+      <c r="F293" t="str">
+        <v/>
+      </c>
+      <c r="G293" t="str">
+        <v/>
+      </c>
+      <c r="H293" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F293" t="str">
+      <c r="I293" t="str">
         <v>d_filial_complemento</v>
       </c>
     </row>
@@ -6273,9 +8910,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E294" t="str">
+        <v/>
+      </c>
+      <c r="F294" t="str">
+        <v/>
+      </c>
+      <c r="G294" t="str">
+        <v/>
+      </c>
+      <c r="H294" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F294" t="str">
+      <c r="I294" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -6296,6 +8942,15 @@
         <v/>
       </c>
       <c r="F295" t="str">
+        <v/>
+      </c>
+      <c r="G295" t="str">
+        <v/>
+      </c>
+      <c r="H295" t="str">
+        <v/>
+      </c>
+      <c r="I295" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -6316,6 +8971,15 @@
         <v/>
       </c>
       <c r="F296" t="str">
+        <v/>
+      </c>
+      <c r="G296" t="str">
+        <v/>
+      </c>
+      <c r="H296" t="str">
+        <v/>
+      </c>
+      <c r="I296" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -6336,6 +9000,15 @@
         <v/>
       </c>
       <c r="F297" t="str">
+        <v/>
+      </c>
+      <c r="G297" t="str">
+        <v/>
+      </c>
+      <c r="H297" t="str">
+        <v/>
+      </c>
+      <c r="I297" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -6356,6 +9029,15 @@
         <v/>
       </c>
       <c r="F298" t="str">
+        <v/>
+      </c>
+      <c r="G298" t="str">
+        <v/>
+      </c>
+      <c r="H298" t="str">
+        <v/>
+      </c>
+      <c r="I298" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -6376,6 +9058,15 @@
         <v/>
       </c>
       <c r="F299" t="str">
+        <v/>
+      </c>
+      <c r="G299" t="str">
+        <v/>
+      </c>
+      <c r="H299" t="str">
+        <v/>
+      </c>
+      <c r="I299" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -6396,6 +9087,15 @@
         <v/>
       </c>
       <c r="F300" t="str">
+        <v/>
+      </c>
+      <c r="G300" t="str">
+        <v/>
+      </c>
+      <c r="H300" t="str">
+        <v/>
+      </c>
+      <c r="I300" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -6416,6 +9116,15 @@
         <v/>
       </c>
       <c r="F301" t="str">
+        <v/>
+      </c>
+      <c r="G301" t="str">
+        <v/>
+      </c>
+      <c r="H301" t="str">
+        <v/>
+      </c>
+      <c r="I301" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -6436,6 +9145,15 @@
         <v/>
       </c>
       <c r="F302" t="str">
+        <v/>
+      </c>
+      <c r="G302" t="str">
+        <v/>
+      </c>
+      <c r="H302" t="str">
+        <v/>
+      </c>
+      <c r="I302" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -6456,6 +9174,15 @@
         <v/>
       </c>
       <c r="F303" t="str">
+        <v/>
+      </c>
+      <c r="G303" t="str">
+        <v/>
+      </c>
+      <c r="H303" t="str">
+        <v/>
+      </c>
+      <c r="I303" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -6476,6 +9203,15 @@
         <v/>
       </c>
       <c r="F304" t="str">
+        <v/>
+      </c>
+      <c r="G304" t="str">
+        <v/>
+      </c>
+      <c r="H304" t="str">
+        <v/>
+      </c>
+      <c r="I304" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -6496,6 +9232,15 @@
         <v/>
       </c>
       <c r="F305" t="str">
+        <v/>
+      </c>
+      <c r="G305" t="str">
+        <v/>
+      </c>
+      <c r="H305" t="str">
+        <v/>
+      </c>
+      <c r="I305" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -6516,6 +9261,15 @@
         <v/>
       </c>
       <c r="F306" t="str">
+        <v/>
+      </c>
+      <c r="G306" t="str">
+        <v/>
+      </c>
+      <c r="H306" t="str">
+        <v/>
+      </c>
+      <c r="I306" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -6533,9 +9287,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E307" t="str">
+        <v/>
+      </c>
+      <c r="F307" t="str">
+        <v/>
+      </c>
+      <c r="G307" t="str">
+        <v/>
+      </c>
+      <c r="H307" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F307" t="str">
+      <c r="I307" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -6553,9 +9316,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E308" t="str">
+        <v/>
+      </c>
+      <c r="F308" t="str">
+        <v/>
+      </c>
+      <c r="G308" t="str">
+        <v/>
+      </c>
+      <c r="H308" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F308" t="str">
+      <c r="I308" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -6573,9 +9345,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E309" t="str">
+        <v/>
+      </c>
+      <c r="F309" t="str">
+        <v/>
+      </c>
+      <c r="G309" t="str">
+        <v/>
+      </c>
+      <c r="H309" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F309" t="str">
+      <c r="I309" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -6593,9 +9374,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E310" t="str">
+        <v/>
+      </c>
+      <c r="F310" t="str">
+        <v/>
+      </c>
+      <c r="G310" t="str">
+        <v/>
+      </c>
+      <c r="H310" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F310" t="str">
+      <c r="I310" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6613,9 +9403,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E311" t="str">
+        <v/>
+      </c>
+      <c r="F311" t="str">
+        <v/>
+      </c>
+      <c r="G311" t="str">
+        <v/>
+      </c>
+      <c r="H311" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F311" t="str">
+      <c r="I311" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -6633,9 +9432,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E312" t="str">
+        <v/>
+      </c>
+      <c r="F312" t="str">
+        <v/>
+      </c>
+      <c r="G312" t="str">
+        <v/>
+      </c>
+      <c r="H312" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F312" t="str">
+      <c r="I312" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -6653,9 +9461,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E313" t="str">
+        <v/>
+      </c>
+      <c r="F313" t="str">
+        <v/>
+      </c>
+      <c r="G313" t="str">
+        <v/>
+      </c>
+      <c r="H313" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F313" t="str">
+      <c r="I313" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -6673,9 +9490,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E314" t="str">
+        <v/>
+      </c>
+      <c r="F314" t="str">
+        <v/>
+      </c>
+      <c r="G314" t="str">
+        <v/>
+      </c>
+      <c r="H314" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F314" t="str">
+      <c r="I314" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -6693,9 +9519,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E315" t="str">
+        <v/>
+      </c>
+      <c r="F315" t="str">
+        <v/>
+      </c>
+      <c r="G315" t="str">
+        <v/>
+      </c>
+      <c r="H315" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F315" t="str">
+      <c r="I315" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -6713,9 +9548,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E316" t="str">
+        <v/>
+      </c>
+      <c r="F316" t="str">
+        <v/>
+      </c>
+      <c r="G316" t="str">
+        <v/>
+      </c>
+      <c r="H316" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F316" t="str">
+      <c r="I316" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -6733,9 +9577,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E317" t="str">
+        <v/>
+      </c>
+      <c r="F317" t="str">
+        <v/>
+      </c>
+      <c r="G317" t="str">
+        <v/>
+      </c>
+      <c r="H317" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F317" t="str">
+      <c r="I317" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6753,9 +9606,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E318" t="str">
+        <v/>
+      </c>
+      <c r="F318" t="str">
+        <v/>
+      </c>
+      <c r="G318" t="str">
+        <v/>
+      </c>
+      <c r="H318" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F318" t="str">
+      <c r="I318" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -6773,9 +9635,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E319" t="str">
+        <v/>
+      </c>
+      <c r="F319" t="str">
+        <v/>
+      </c>
+      <c r="G319" t="str">
+        <v/>
+      </c>
+      <c r="H319" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F319" t="str">
+      <c r="I319" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -6793,9 +9664,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E320" t="str">
+        <v/>
+      </c>
+      <c r="F320" t="str">
+        <v/>
+      </c>
+      <c r="G320" t="str">
+        <v/>
+      </c>
+      <c r="H320" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F320" t="str">
+      <c r="I320" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -6816,6 +9696,15 @@
         <v/>
       </c>
       <c r="F321" t="str">
+        <v/>
+      </c>
+      <c r="G321" t="str">
+        <v/>
+      </c>
+      <c r="H321" t="str">
+        <v/>
+      </c>
+      <c r="I321" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -6836,6 +9725,15 @@
         <v/>
       </c>
       <c r="F322" t="str">
+        <v/>
+      </c>
+      <c r="G322" t="str">
+        <v/>
+      </c>
+      <c r="H322" t="str">
+        <v/>
+      </c>
+      <c r="I322" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -6856,6 +9754,15 @@
         <v/>
       </c>
       <c r="F323" t="str">
+        <v/>
+      </c>
+      <c r="G323" t="str">
+        <v/>
+      </c>
+      <c r="H323" t="str">
+        <v/>
+      </c>
+      <c r="I323" t="str">
         <v>VW_D_FILIAL</v>
       </c>
     </row>
@@ -6876,6 +9783,15 @@
         <v/>
       </c>
       <c r="F324" t="str">
+        <v/>
+      </c>
+      <c r="G324" t="str">
+        <v/>
+      </c>
+      <c r="H324" t="str">
+        <v/>
+      </c>
+      <c r="I324" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -6893,9 +9809,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E325" t="str">
+        <v/>
+      </c>
+      <c r="F325" t="str">
+        <v/>
+      </c>
+      <c r="G325" t="str">
+        <v/>
+      </c>
+      <c r="H325" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F325" t="str">
+      <c r="I325" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -6916,6 +9841,15 @@
         <v/>
       </c>
       <c r="F326" t="str">
+        <v/>
+      </c>
+      <c r="G326" t="str">
+        <v/>
+      </c>
+      <c r="H326" t="str">
+        <v/>
+      </c>
+      <c r="I326" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -6933,9 +9867,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E327" t="str">
+        <v/>
+      </c>
+      <c r="F327" t="str">
+        <v/>
+      </c>
+      <c r="G327" t="str">
+        <v/>
+      </c>
+      <c r="H327" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F327" t="str">
+      <c r="I327" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -6953,9 +9896,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E328" t="str">
+        <v/>
+      </c>
+      <c r="F328" t="str">
+        <v/>
+      </c>
+      <c r="G328" t="str">
+        <v/>
+      </c>
+      <c r="H328" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F328" t="str">
+      <c r="I328" t="str">
         <v>d_filial_complemento</v>
       </c>
     </row>
@@ -6973,9 +9925,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E329" t="str">
+        <v/>
+      </c>
+      <c r="F329" t="str">
+        <v/>
+      </c>
+      <c r="G329" t="str">
+        <v/>
+      </c>
+      <c r="H329" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F329" t="str">
+      <c r="I329" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -6996,6 +9957,15 @@
         <v/>
       </c>
       <c r="F330" t="str">
+        <v/>
+      </c>
+      <c r="G330" t="str">
+        <v/>
+      </c>
+      <c r="H330" t="str">
+        <v/>
+      </c>
+      <c r="I330" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7016,6 +9986,15 @@
         <v/>
       </c>
       <c r="F331" t="str">
+        <v/>
+      </c>
+      <c r="G331" t="str">
+        <v/>
+      </c>
+      <c r="H331" t="str">
+        <v/>
+      </c>
+      <c r="I331" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -7036,6 +10015,15 @@
         <v/>
       </c>
       <c r="F332" t="str">
+        <v/>
+      </c>
+      <c r="G332" t="str">
+        <v/>
+      </c>
+      <c r="H332" t="str">
+        <v/>
+      </c>
+      <c r="I332" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -7056,6 +10044,15 @@
         <v/>
       </c>
       <c r="F333" t="str">
+        <v/>
+      </c>
+      <c r="G333" t="str">
+        <v/>
+      </c>
+      <c r="H333" t="str">
+        <v/>
+      </c>
+      <c r="I333" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -7076,6 +10073,15 @@
         <v/>
       </c>
       <c r="F334" t="str">
+        <v/>
+      </c>
+      <c r="G334" t="str">
+        <v/>
+      </c>
+      <c r="H334" t="str">
+        <v/>
+      </c>
+      <c r="I334" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -7096,6 +10102,15 @@
         <v/>
       </c>
       <c r="F335" t="str">
+        <v/>
+      </c>
+      <c r="G335" t="str">
+        <v/>
+      </c>
+      <c r="H335" t="str">
+        <v/>
+      </c>
+      <c r="I335" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -7116,6 +10131,15 @@
         <v/>
       </c>
       <c r="F336" t="str">
+        <v/>
+      </c>
+      <c r="G336" t="str">
+        <v/>
+      </c>
+      <c r="H336" t="str">
+        <v/>
+      </c>
+      <c r="I336" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7136,6 +10160,15 @@
         <v/>
       </c>
       <c r="F337" t="str">
+        <v/>
+      </c>
+      <c r="G337" t="str">
+        <v/>
+      </c>
+      <c r="H337" t="str">
+        <v/>
+      </c>
+      <c r="I337" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -7156,6 +10189,15 @@
         <v/>
       </c>
       <c r="F338" t="str">
+        <v/>
+      </c>
+      <c r="G338" t="str">
+        <v/>
+      </c>
+      <c r="H338" t="str">
+        <v/>
+      </c>
+      <c r="I338" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -7176,6 +10218,15 @@
         <v/>
       </c>
       <c r="F339" t="str">
+        <v/>
+      </c>
+      <c r="G339" t="str">
+        <v/>
+      </c>
+      <c r="H339" t="str">
+        <v/>
+      </c>
+      <c r="I339" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -7196,6 +10247,15 @@
         <v/>
       </c>
       <c r="F340" t="str">
+        <v/>
+      </c>
+      <c r="G340" t="str">
+        <v/>
+      </c>
+      <c r="H340" t="str">
+        <v/>
+      </c>
+      <c r="I340" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -7216,6 +10276,15 @@
         <v/>
       </c>
       <c r="F341" t="str">
+        <v/>
+      </c>
+      <c r="G341" t="str">
+        <v/>
+      </c>
+      <c r="H341" t="str">
+        <v/>
+      </c>
+      <c r="I341" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -7233,9 +10302,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage</v>
       </c>
       <c r="E342" t="str">
+        <v/>
+      </c>
+      <c r="F342" t="str">
+        <v/>
+      </c>
+      <c r="G342" t="str">
+        <v/>
+      </c>
+      <c r="H342" t="str">
         <v>PORTALBI</v>
       </c>
-      <c r="F342" t="str">
+      <c r="I342" t="str">
         <v>filial_endereco</v>
       </c>
     </row>
@@ -7253,9 +10331,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage</v>
       </c>
       <c r="E343" t="str">
+        <v/>
+      </c>
+      <c r="F343" t="str">
+        <v/>
+      </c>
+      <c r="G343" t="str">
+        <v/>
+      </c>
+      <c r="H343" t="str">
         <v>PORTALBI</v>
       </c>
-      <c r="F343" t="str">
+      <c r="I343" t="str">
         <v>filial_endereco@tecnisaw</v>
       </c>
     </row>
@@ -7273,9 +10360,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E344" t="str">
+        <v/>
+      </c>
+      <c r="F344" t="str">
+        <v/>
+      </c>
+      <c r="G344" t="str">
+        <v/>
+      </c>
+      <c r="H344" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F344" t="str">
+      <c r="I344" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -7293,9 +10389,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E345" t="str">
+        <v/>
+      </c>
+      <c r="F345" t="str">
+        <v/>
+      </c>
+      <c r="G345" t="str">
+        <v/>
+      </c>
+      <c r="H345" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F345" t="str">
+      <c r="I345" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -7313,9 +10418,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E346" t="str">
+        <v/>
+      </c>
+      <c r="F346" t="str">
+        <v/>
+      </c>
+      <c r="G346" t="str">
+        <v/>
+      </c>
+      <c r="H346" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F346" t="str">
+      <c r="I346" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -7333,9 +10447,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E347" t="str">
+        <v/>
+      </c>
+      <c r="F347" t="str">
+        <v/>
+      </c>
+      <c r="G347" t="str">
+        <v/>
+      </c>
+      <c r="H347" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F347" t="str">
+      <c r="I347" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -7353,9 +10476,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E348" t="str">
+        <v/>
+      </c>
+      <c r="F348" t="str">
+        <v/>
+      </c>
+      <c r="G348" t="str">
+        <v/>
+      </c>
+      <c r="H348" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F348" t="str">
+      <c r="I348" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -7373,9 +10505,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E349" t="str">
+        <v/>
+      </c>
+      <c r="F349" t="str">
+        <v/>
+      </c>
+      <c r="G349" t="str">
+        <v/>
+      </c>
+      <c r="H349" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F349" t="str">
+      <c r="I349" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -7393,9 +10534,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E350" t="str">
+        <v/>
+      </c>
+      <c r="F350" t="str">
+        <v/>
+      </c>
+      <c r="G350" t="str">
+        <v/>
+      </c>
+      <c r="H350" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F350" t="str">
+      <c r="I350" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -7413,9 +10563,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
       </c>
       <c r="E351" t="str">
+        <v/>
+      </c>
+      <c r="F351" t="str">
+        <v/>
+      </c>
+      <c r="G351" t="str">
+        <v/>
+      </c>
+      <c r="H351" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F351" t="str">
+      <c r="I351" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7436,6 +10595,15 @@
         <v/>
       </c>
       <c r="F352" t="str">
+        <v/>
+      </c>
+      <c r="G352" t="str">
+        <v/>
+      </c>
+      <c r="H352" t="str">
+        <v/>
+      </c>
+      <c r="I352" t="str">
         <v>VW_APDATA_STEP_ABERTURA_VAGAS</v>
       </c>
     </row>
@@ -7453,9 +10621,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E353" t="str">
+        <v/>
+      </c>
+      <c r="F353" t="str">
+        <v/>
+      </c>
+      <c r="G353" t="str">
+        <v/>
+      </c>
+      <c r="H353" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F353" t="str">
+      <c r="I353" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -7473,9 +10650,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E354" t="str">
+        <v/>
+      </c>
+      <c r="F354" t="str">
+        <v/>
+      </c>
+      <c r="G354" t="str">
+        <v/>
+      </c>
+      <c r="H354" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F354" t="str">
+      <c r="I354" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -7493,9 +10679,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E355" t="str">
+        <v/>
+      </c>
+      <c r="F355" t="str">
+        <v/>
+      </c>
+      <c r="G355" t="str">
+        <v/>
+      </c>
+      <c r="H355" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F355" t="str">
+      <c r="I355" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -7513,9 +10708,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E356" t="str">
+        <v/>
+      </c>
+      <c r="F356" t="str">
+        <v/>
+      </c>
+      <c r="G356" t="str">
+        <v/>
+      </c>
+      <c r="H356" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F356" t="str">
+      <c r="I356" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -7533,9 +10737,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E357" t="str">
+        <v/>
+      </c>
+      <c r="F357" t="str">
+        <v/>
+      </c>
+      <c r="G357" t="str">
+        <v/>
+      </c>
+      <c r="H357" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F357" t="str">
+      <c r="I357" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -7553,9 +10766,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E358" t="str">
+        <v/>
+      </c>
+      <c r="F358" t="str">
+        <v/>
+      </c>
+      <c r="G358" t="str">
+        <v/>
+      </c>
+      <c r="H358" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F358" t="str">
+      <c r="I358" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -7573,9 +10795,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E359" t="str">
+        <v/>
+      </c>
+      <c r="F359" t="str">
+        <v/>
+      </c>
+      <c r="G359" t="str">
+        <v/>
+      </c>
+      <c r="H359" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F359" t="str">
+      <c r="I359" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -7596,6 +10827,15 @@
         <v/>
       </c>
       <c r="F360" t="str">
+        <v/>
+      </c>
+      <c r="G360" t="str">
+        <v/>
+      </c>
+      <c r="H360" t="str">
+        <v/>
+      </c>
+      <c r="I360" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7616,6 +10856,15 @@
         <v/>
       </c>
       <c r="F361" t="str">
+        <v/>
+      </c>
+      <c r="G361" t="str">
+        <v/>
+      </c>
+      <c r="H361" t="str">
+        <v/>
+      </c>
+      <c r="I361" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -7636,6 +10885,15 @@
         <v/>
       </c>
       <c r="F362" t="str">
+        <v/>
+      </c>
+      <c r="G362" t="str">
+        <v/>
+      </c>
+      <c r="H362" t="str">
+        <v/>
+      </c>
+      <c r="I362" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7656,6 +10914,15 @@
         <v/>
       </c>
       <c r="F363" t="str">
+        <v/>
+      </c>
+      <c r="G363" t="str">
+        <v/>
+      </c>
+      <c r="H363" t="str">
+        <v/>
+      </c>
+      <c r="I363" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -7673,9 +10940,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E364" t="str">
+        <v/>
+      </c>
+      <c r="F364" t="str">
+        <v/>
+      </c>
+      <c r="G364" t="str">
+        <v/>
+      </c>
+      <c r="H364" t="str">
         <v>bicompras</v>
       </c>
-      <c r="F364" t="str">
+      <c r="I364" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -7693,9 +10969,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E365" t="str">
+        <v/>
+      </c>
+      <c r="F365" t="str">
+        <v/>
+      </c>
+      <c r="G365" t="str">
+        <v/>
+      </c>
+      <c r="H365" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F365" t="str">
+      <c r="I365" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -7713,9 +10998,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E366" t="str">
+        <v/>
+      </c>
+      <c r="F366" t="str">
+        <v/>
+      </c>
+      <c r="G366" t="str">
+        <v/>
+      </c>
+      <c r="H366" t="str">
         <v>DPESSOAL</v>
       </c>
-      <c r="F366" t="str">
+      <c r="I366" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -7733,9 +11027,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E367" t="str">
+        <v/>
+      </c>
+      <c r="F367" t="str">
+        <v/>
+      </c>
+      <c r="G367" t="str">
+        <v/>
+      </c>
+      <c r="H367" t="str">
         <v>dpessoal</v>
       </c>
-      <c r="F367" t="str">
+      <c r="I367" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -7753,9 +11056,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E368" t="str">
+        <v/>
+      </c>
+      <c r="F368" t="str">
+        <v/>
+      </c>
+      <c r="G368" t="str">
+        <v/>
+      </c>
+      <c r="H368" t="str">
         <v>portalbi</v>
       </c>
-      <c r="F368" t="str">
+      <c r="I368" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -7773,9 +11085,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E369" t="str">
+        <v/>
+      </c>
+      <c r="F369" t="str">
+        <v/>
+      </c>
+      <c r="G369" t="str">
+        <v/>
+      </c>
+      <c r="H369" t="str">
         <v>bisilver</v>
       </c>
-      <c r="F369" t="str">
+      <c r="I369" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -7793,9 +11114,18 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E370" t="str">
+        <v/>
+      </c>
+      <c r="F370" t="str">
+        <v/>
+      </c>
+      <c r="G370" t="str">
+        <v/>
+      </c>
+      <c r="H370" t="str">
         <v>ciscorp</v>
       </c>
-      <c r="F370" t="str">
+      <c r="I370" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -7818,10 +11148,19 @@
       <c r="F371" t="str">
         <v/>
       </c>
+      <c r="G371" t="str">
+        <v/>
+      </c>
+      <c r="H371" t="str">
+        <v/>
+      </c>
+      <c r="I371" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F371"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I371"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/downloads/hr/output_automacao_hr.xlsx
+++ b/downloads/hr/output_automacao_hr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I371"/>
+  <dimension ref="A1:I367"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,10 +445,10 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H2" t="str">
         <v>bicompras</v>
@@ -474,10 +474,10 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H3" t="str">
         <v>DPESSOAL</v>
@@ -503,10 +503,10 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H4" t="str">
         <v>DPESSOAL</v>
@@ -532,10 +532,10 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H5" t="str">
         <v>dpessoal</v>
@@ -561,10 +561,10 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H6" t="str">
         <v>portalbi</v>
@@ -590,10 +590,10 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H7" t="str">
         <v>bisilver</v>
@@ -619,10 +619,10 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H8" t="str">
         <v>ciscorp</v>
@@ -645,13 +645,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1057/lineage</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -674,13 +674,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1057/lineage</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -703,13 +703,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1057/lineage</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -732,13 +732,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1057/lineage</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -764,10 +764,10 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H13" t="str">
         <v>bicompras</v>
@@ -793,10 +793,10 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H14" t="str">
         <v>DPESSOAL</v>
@@ -822,10 +822,10 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H15" t="str">
         <v>DPESSOAL</v>
@@ -851,10 +851,10 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H16" t="str">
         <v>dpessoal</v>
@@ -880,10 +880,10 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H17" t="str">
         <v>portalbi</v>
@@ -909,10 +909,10 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H18" t="str">
         <v>bisilver</v>
@@ -938,10 +938,10 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H19" t="str">
         <v>ciscorp</v>
@@ -964,13 +964,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -993,13 +993,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -1022,13 +1022,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -1051,13 +1051,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -1080,13 +1080,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E24" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1109,13 +1109,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -1138,13 +1138,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -1167,13 +1167,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1196,13 +1196,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1225,13 +1225,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -1257,10 +1257,10 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -1286,10 +1286,10 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -1315,10 +1315,10 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -1344,10 +1344,10 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -1373,10 +1373,10 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -1402,10 +1402,10 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G35" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H35" t="str">
         <v/>
@@ -1431,10 +1431,10 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G36" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H36" t="str">
         <v/>
@@ -1460,10 +1460,10 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G37" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -1489,10 +1489,10 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -1518,10 +1518,10 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G39" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -1544,13 +1544,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E40" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F40" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G40" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -1573,13 +1573,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G41" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -1602,13 +1602,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H42" t="str">
         <v/>
@@ -1631,13 +1631,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -1660,13 +1660,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -1689,13 +1689,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F45" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G45" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -1718,13 +1718,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E46" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F46" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -1747,13 +1747,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H47" t="str">
         <v/>
@@ -1776,13 +1776,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E48" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F48" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G48" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -1805,13 +1805,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F49" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -1834,13 +1834,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E50" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F50" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G50" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -1863,13 +1863,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E51" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F51" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -1892,13 +1892,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E52" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F52" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G52" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -1921,13 +1921,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E53" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F53" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G53" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -1950,13 +1950,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F54" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G54" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -1979,13 +1979,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F55" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G55" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -2008,13 +2008,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E56" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F56" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G56" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -2037,13 +2037,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F57" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G57" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -2066,13 +2066,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F58" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G58" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H58" t="str">
         <v/>
@@ -2095,13 +2095,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F59" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G59" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -2124,13 +2124,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E60" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F60" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G60" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -2153,13 +2153,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F61" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -2182,13 +2182,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F62" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G62" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H62" t="str">
         <v/>
@@ -2211,13 +2211,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F63" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G63" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -2240,13 +2240,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F64" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G64" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H64" t="str">
         <v/>
@@ -2269,13 +2269,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E65" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F65" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -2298,13 +2298,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E66" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F66" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G66" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -2327,13 +2327,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E67" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F67" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G67" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -2356,13 +2356,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E68" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F68" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G68" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -2385,13 +2385,13 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F69" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G69" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -2417,10 +2417,10 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G70" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H70" t="str">
         <v>bicompras</v>
@@ -2446,10 +2446,10 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G71" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H71" t="str">
         <v>DPESSOAL</v>
@@ -2475,10 +2475,10 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G72" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H72" t="str">
         <v>DPESSOAL</v>
@@ -2504,10 +2504,10 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G73" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H73" t="str">
         <v>dpessoal</v>
@@ -2533,10 +2533,10 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G74" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H74" t="str">
         <v>portalbi</v>
@@ -2562,10 +2562,10 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G75" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H75" t="str">
         <v>bisilver</v>
@@ -2591,10 +2591,10 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G76" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H76" t="str">
         <v>ciscorp</v>
@@ -2611,7 +2611,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C77" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D77" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
@@ -2620,10 +2620,10 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G77" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H77" t="str">
         <v>bicompras</v>
@@ -2640,7 +2640,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C78" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D78" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
@@ -2649,10 +2649,10 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G78" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H78" t="str">
         <v>DPESSOAL</v>
@@ -2669,7 +2669,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C79" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D79" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
@@ -2678,10 +2678,10 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G79" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H79" t="str">
         <v>DPESSOAL</v>
@@ -2698,7 +2698,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C80" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D80" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
@@ -2707,10 +2707,10 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G80" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H80" t="str">
         <v>dpessoal</v>
@@ -2727,7 +2727,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C81" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D81" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
@@ -2736,10 +2736,10 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G81" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H81" t="str">
         <v>portalbi</v>
@@ -2756,7 +2756,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C82" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D82" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
@@ -2765,10 +2765,10 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G82" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H82" t="str">
         <v>bisilver</v>
@@ -2785,7 +2785,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C83" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D83" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
@@ -2794,10 +2794,10 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G83" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H83" t="str">
         <v>ciscorp</v>
@@ -2823,10 +2823,10 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v/>
+        <v>Bairro; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Motivo Alteracao Grade; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; CEP; Cidade; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; Deficiencia; Dlg Dlsdesligamento</v>
       </c>
       <c r="G84" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H84" t="str">
         <v>PORTALBI</v>
@@ -2852,10 +2852,10 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v/>
+        <v>Bairro; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Motivo Alteracao Grade; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; CEP; Cidade; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; Deficiencia; Dlg Dlsdesligamento</v>
       </c>
       <c r="G85" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H85" t="str">
         <v>DPESSOAL</v>
@@ -2881,10 +2881,10 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v/>
+        <v>Bairro; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Motivo Alteracao Grade; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; CEP; Cidade; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; Deficiencia; Dlg Dlsdesligamento</v>
       </c>
       <c r="G86" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H86" t="str">
         <v>PORTALBI</v>
@@ -2901,19 +2901,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C87" t="str">
-        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
+        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
       </c>
       <c r="D87" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E87" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F87" t="str">
-        <v/>
+        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
       </c>
       <c r="G87" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H87" t="str">
         <v/>
@@ -2930,19 +2930,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C88" t="str">
-        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
+        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
       </c>
       <c r="D88" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E88" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F88" t="str">
-        <v/>
+        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
       </c>
       <c r="G88" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -2959,19 +2959,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C89" t="str">
-        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
+        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
       </c>
       <c r="D89" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E89" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F89" t="str">
-        <v/>
+        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
       </c>
       <c r="G89" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H89" t="str">
         <v/>
@@ -2988,19 +2988,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C90" t="str">
-        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
+        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
       </c>
       <c r="D90" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E90" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F90" t="str">
-        <v/>
+        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
       </c>
       <c r="G90" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H90" t="str">
         <v/>
@@ -3017,19 +3017,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C91" t="str">
-        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
+        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
       </c>
       <c r="D91" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E91" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F91" t="str">
-        <v/>
+        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
       </c>
       <c r="G91" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -3040,147 +3040,147 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Indicadores DE&amp;I</v>
+        <v>Book de Indicadores de Pessoas</v>
       </c>
       <c r="B92" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
       </c>
       <c r="C92" t="str">
-        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D92" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G92" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H92" t="str">
-        <v/>
+        <v>bicompras</v>
       </c>
       <c r="I92" t="str">
-        <v>D_COLABORADOR</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Indicadores DE&amp;I</v>
+        <v>Book de Indicadores de Pessoas</v>
       </c>
       <c r="B93" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
       </c>
       <c r="C93" t="str">
-        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D93" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G93" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H93" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I93" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Indicadores DE&amp;I</v>
+        <v>Book de Indicadores de Pessoas</v>
       </c>
       <c r="B94" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
       </c>
       <c r="C94" t="str">
-        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D94" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G94" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H94" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I94" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Indicadores DE&amp;I</v>
+        <v>Book de Indicadores de Pessoas</v>
       </c>
       <c r="B95" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
       </c>
       <c r="C95" t="str">
-        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D95" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G95" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H95" t="str">
-        <v/>
+        <v>dpessoal</v>
       </c>
       <c r="I95" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Indicadores DE&amp;I</v>
+        <v>Book de Indicadores de Pessoas</v>
       </c>
       <c r="B96" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
       </c>
       <c r="C96" t="str">
-        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D96" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G96" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H96" t="str">
-        <v/>
+        <v>portalbi</v>
       </c>
       <c r="I96" t="str">
-        <v>F_PROMOCAO</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="97">
@@ -3200,16 +3200,16 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G97" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H97" t="str">
-        <v>bicompras</v>
+        <v>bisilver</v>
       </c>
       <c r="I97" t="str">
-        <v>d_filial</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="98">
@@ -3229,161 +3229,161 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G98" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H98" t="str">
-        <v>DPESSOAL</v>
+        <v>ciscorp</v>
       </c>
       <c r="I98" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Book de Indicadores de Pessoas</v>
+        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
       </c>
       <c r="B99" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
       </c>
       <c r="C99" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Ponto Analitico RLS V2</v>
       </c>
       <c r="D99" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v/>
+        <v>Cálculo1; Cálculo2; CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO</v>
       </c>
       <c r="G99" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H99" t="str">
         <v>DPESSOAL</v>
       </c>
       <c r="I99" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>VW_EVT_RH_PONTO_ANALITICO</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Book de Indicadores de Pessoas</v>
+        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
       </c>
       <c r="B100" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
       </c>
       <c r="C100" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Ponto Analitico RLS V2</v>
       </c>
       <c r="D100" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v/>
+        <v>Cálculo1; Cálculo2; CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO</v>
       </c>
       <c r="G100" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H100" t="str">
-        <v>dpessoal</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="I100" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>D_USUARIO_FILIAL</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Book de Indicadores de Pessoas</v>
+        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
       </c>
       <c r="B101" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
       </c>
       <c r="C101" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Ponto Sintetico RLS</v>
       </c>
       <c r="D101" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v/>
+        <v>CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO</v>
       </c>
       <c r="G101" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H101" t="str">
-        <v>portalbi</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="I101" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Book de Indicadores de Pessoas</v>
+        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
       </c>
       <c r="B102" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
       </c>
       <c r="C102" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Ponto Sintetico RLS</v>
       </c>
       <c r="D102" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v/>
+        <v>CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H102" t="str">
-        <v>bisilver</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="I102" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>D_USUARIO_FILIAL</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Book de Indicadores de Pessoas</v>
+        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
       </c>
       <c r="B103" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
       </c>
       <c r="C103" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>Ondas_Projeto_Ponto</v>
       </c>
       <c r="D103" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
       </c>
       <c r="E103" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F103" t="str">
-        <v/>
+        <v>CL; Clbr; Onda; Planilha1 (Count)</v>
       </c>
       <c r="G103" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H103" t="str">
-        <v>ciscorp</v>
+        <v/>
       </c>
       <c r="I103" t="str">
-        <v>filial</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="104">
@@ -3394,25 +3394,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
       </c>
       <c r="C104" t="str">
-        <v>RH - Colaborador Ponto Analitico RLS V2</v>
+        <v>Ondas_Projeto_Ponto</v>
       </c>
       <c r="D104" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
       </c>
       <c r="E104" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F104" t="str">
-        <v/>
+        <v>CL; Clbr; Onda; Planilha1 (Count)</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H104" t="str">
-        <v>DPESSOAL</v>
+        <v/>
       </c>
       <c r="I104" t="str">
-        <v>VW_EVT_RH_PONTO_ANALITICO</v>
+        <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
       </c>
     </row>
     <row r="105">
@@ -3423,51 +3423,51 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
       </c>
       <c r="C105" t="str">
-        <v>RH - Colaborador Ponto Analitico RLS V2</v>
+        <v>Ondas_Projeto_Ponto</v>
       </c>
       <c r="D105" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
       </c>
       <c r="E105" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F105" t="str">
-        <v/>
+        <v>CL; Clbr; Onda; Planilha1 (Count)</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H105" t="str">
-        <v>DPESSOAL</v>
+        <v/>
       </c>
       <c r="I105" t="str">
-        <v>D_USUARIO_FILIAL</v>
+        <v>VW_EVT_RH_PONTO_ANALITICO</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
+        <v>Base de Férias em Aberto</v>
       </c>
       <c r="B106" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
       </c>
       <c r="C106" t="str">
-        <v>RH - Colaborador Ponto Sintetico RLS</v>
+        <v>RH - Colaborador Ponto Sintetico</v>
       </c>
       <c r="D106" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/17222/lineage</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v/>
+        <v>CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H106" t="str">
-        <v>DPESSOAL</v>
+        <v/>
       </c>
       <c r="I106" t="str">
         <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
@@ -3475,54 +3475,54 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
+        <v>Base de Férias em Aberto</v>
       </c>
       <c r="B107" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
       </c>
       <c r="C107" t="str">
-        <v>RH - Colaborador Ponto Sintetico RLS</v>
+        <v>RH - Programação de Férias</v>
       </c>
       <c r="D107" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H107" t="str">
-        <v>DPESSOAL</v>
+        <v/>
       </c>
       <c r="I107" t="str">
-        <v>D_USUARIO_FILIAL</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
+        <v>Base de Férias em Aberto</v>
       </c>
       <c r="B108" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
       </c>
       <c r="C108" t="str">
-        <v>Ondas_Projeto_Ponto</v>
+        <v>RH - Programação de Férias</v>
       </c>
       <c r="D108" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H108" t="str">
         <v/>
@@ -3533,205 +3533,205 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
+        <v>Base de Férias em Aberto</v>
       </c>
       <c r="B109" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
       </c>
       <c r="C109" t="str">
-        <v>Ondas_Projeto_Ponto</v>
+        <v>RH - Programação de Férias</v>
       </c>
       <c r="D109" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H109" t="str">
         <v/>
       </c>
       <c r="I109" t="str">
-        <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
+        <v>VW_D_FILIAL</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
+        <v>Base de Férias em Aberto</v>
       </c>
       <c r="B110" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
       </c>
       <c r="C110" t="str">
-        <v>Ondas_Projeto_Ponto</v>
+        <v>RH - Programação de Férias</v>
       </c>
       <c r="D110" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H110" t="str">
         <v/>
       </c>
       <c r="I110" t="str">
-        <v>VW_EVT_RH_PONTO_ANALITICO</v>
+        <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Base de Férias em Aberto</v>
+        <v>Modelo de Trabalho</v>
       </c>
       <c r="B111" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
       </c>
       <c r="C111" t="str">
-        <v>RH - Colaborador Ponto Sintetico</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D111" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/17222/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H111" t="str">
-        <v/>
+        <v>bicompras</v>
       </c>
       <c r="I111" t="str">
-        <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Base de Férias em Aberto</v>
+        <v>Modelo de Trabalho</v>
       </c>
       <c r="B112" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
       </c>
       <c r="C112" t="str">
-        <v>RH - Programação de Férias</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D112" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G112" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H112" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I112" t="str">
-        <v>D_COLABORADOR</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Base de Férias em Aberto</v>
+        <v>Modelo de Trabalho</v>
       </c>
       <c r="B113" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
       </c>
       <c r="C113" t="str">
-        <v>RH - Programação de Férias</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D113" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H113" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I113" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Base de Férias em Aberto</v>
+        <v>Modelo de Trabalho</v>
       </c>
       <c r="B114" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
       </c>
       <c r="C114" t="str">
-        <v>RH - Programação de Férias</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D114" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G114" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H114" t="str">
-        <v/>
+        <v>dpessoal</v>
       </c>
       <c r="I114" t="str">
-        <v>VW_D_FILIAL</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Base de Férias em Aberto</v>
+        <v>Modelo de Trabalho</v>
       </c>
       <c r="B115" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
       </c>
       <c r="C115" t="str">
-        <v>RH - Programação de Férias</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D115" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G115" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H115" t="str">
-        <v/>
+        <v>portalbi</v>
       </c>
       <c r="I115" t="str">
-        <v>F_PROGRAMACAO_FERIAS</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="116">
@@ -3751,16 +3751,16 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G116" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H116" t="str">
-        <v>bicompras</v>
+        <v>bisilver</v>
       </c>
       <c r="I116" t="str">
-        <v>d_filial</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="117">
@@ -3780,24 +3780,24 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G117" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H117" t="str">
-        <v>DPESSOAL</v>
+        <v>ciscorp</v>
       </c>
       <c r="I117" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Modelo de Trabalho</v>
+        <v>Banco de Horas</v>
       </c>
       <c r="B118" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
       </c>
       <c r="C118" t="str">
         <v>RH - Colaborador Folha</v>
@@ -3809,24 +3809,24 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G118" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H118" t="str">
-        <v>DPESSOAL</v>
+        <v>bicompras</v>
       </c>
       <c r="I118" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Modelo de Trabalho</v>
+        <v>Banco de Horas</v>
       </c>
       <c r="B119" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
       </c>
       <c r="C119" t="str">
         <v>RH - Colaborador Folha</v>
@@ -3838,24 +3838,24 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G119" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H119" t="str">
-        <v>dpessoal</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="I119" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Modelo de Trabalho</v>
+        <v>Banco de Horas</v>
       </c>
       <c r="B120" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
       </c>
       <c r="C120" t="str">
         <v>RH - Colaborador Folha</v>
@@ -3867,24 +3867,24 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G120" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H120" t="str">
-        <v>portalbi</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="I120" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Modelo de Trabalho</v>
+        <v>Banco de Horas</v>
       </c>
       <c r="B121" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
       </c>
       <c r="C121" t="str">
         <v>RH - Colaborador Folha</v>
@@ -3896,24 +3896,24 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G121" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H121" t="str">
-        <v>bisilver</v>
+        <v>dpessoal</v>
       </c>
       <c r="I121" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Modelo de Trabalho</v>
+        <v>Banco de Horas</v>
       </c>
       <c r="B122" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
       </c>
       <c r="C122" t="str">
         <v>RH - Colaborador Folha</v>
@@ -3925,16 +3925,16 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G122" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H122" t="str">
-        <v>ciscorp</v>
+        <v>portalbi</v>
       </c>
       <c r="I122" t="str">
-        <v>filial</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="123">
@@ -3954,16 +3954,16 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G123" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H123" t="str">
-        <v>bicompras</v>
+        <v>bisilver</v>
       </c>
       <c r="I123" t="str">
-        <v>d_filial</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="124">
@@ -3983,24 +3983,24 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G124" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H124" t="str">
-        <v>DPESSOAL</v>
+        <v>ciscorp</v>
       </c>
       <c r="I124" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Banco de Horas</v>
+        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
       </c>
       <c r="B125" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C125" t="str">
         <v>RH - Colaborador Folha</v>
@@ -4012,24 +4012,24 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G125" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H125" t="str">
-        <v>DPESSOAL</v>
+        <v>bicompras</v>
       </c>
       <c r="I125" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Banco de Horas</v>
+        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
       </c>
       <c r="B126" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C126" t="str">
         <v>RH - Colaborador Folha</v>
@@ -4041,24 +4041,24 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G126" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H126" t="str">
-        <v>dpessoal</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="I126" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Banco de Horas</v>
+        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
       </c>
       <c r="B127" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C127" t="str">
         <v>RH - Colaborador Folha</v>
@@ -4070,24 +4070,24 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G127" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H127" t="str">
-        <v>portalbi</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="I127" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Banco de Horas</v>
+        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
       </c>
       <c r="B128" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C128" t="str">
         <v>RH - Colaborador Folha</v>
@@ -4099,24 +4099,24 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G128" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H128" t="str">
-        <v>bisilver</v>
+        <v>dpessoal</v>
       </c>
       <c r="I128" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Banco de Horas</v>
+        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
       </c>
       <c r="B129" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C129" t="str">
         <v>RH - Colaborador Folha</v>
@@ -4128,16 +4128,16 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G129" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H129" t="str">
-        <v>ciscorp</v>
+        <v>portalbi</v>
       </c>
       <c r="I129" t="str">
-        <v>filial</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="130">
@@ -4157,16 +4157,16 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G130" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H130" t="str">
-        <v>bicompras</v>
+        <v>bisilver</v>
       </c>
       <c r="I130" t="str">
-        <v>d_filial</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="131">
@@ -4186,16 +4186,16 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G131" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H131" t="str">
-        <v>DPESSOAL</v>
+        <v>ciscorp</v>
       </c>
       <c r="I131" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="132">
@@ -4206,25 +4206,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C132" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D132" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E132" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F132" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G132" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H132" t="str">
-        <v>DPESSOAL</v>
+        <v/>
       </c>
       <c r="I132" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="133">
@@ -4235,22 +4235,22 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C133" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D133" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E133" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F133" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G133" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H133" t="str">
-        <v>dpessoal</v>
+        <v/>
       </c>
       <c r="I133" t="str">
         <v>F_COLABORADOR_FOLHA</v>
@@ -4264,25 +4264,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C134" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D134" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E134" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F134" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G134" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H134" t="str">
-        <v>portalbi</v>
+        <v/>
       </c>
       <c r="I134" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="135">
@@ -4293,25 +4293,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C135" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D135" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E135" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F135" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G135" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H135" t="str">
-        <v>bisilver</v>
+        <v/>
       </c>
       <c r="I135" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="136">
@@ -4322,25 +4322,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C136" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D136" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E136" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F136" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G136" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H136" t="str">
-        <v>ciscorp</v>
+        <v/>
       </c>
       <c r="I136" t="str">
-        <v>filial</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="137">
@@ -4357,19 +4357,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E137" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F137" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G137" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H137" t="str">
         <v/>
       </c>
       <c r="I137" t="str">
-        <v>D_COLABORADOR</v>
+        <v>Absenteismo_Days</v>
       </c>
     </row>
     <row r="138">
@@ -4386,19 +4386,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E138" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F138" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G138" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H138" t="str">
         <v/>
       </c>
       <c r="I138" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
     <row r="139">
@@ -4415,19 +4415,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E139" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F139" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G139" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H139" t="str">
         <v/>
       </c>
       <c r="I139" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>'Women Leardership$'</v>
       </c>
     </row>
     <row r="140">
@@ -4444,19 +4444,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E140" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F140" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G140" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H140" t="str">
         <v/>
       </c>
       <c r="I140" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>Promoções_Internas</v>
       </c>
     </row>
     <row r="141">
@@ -4473,19 +4473,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E141" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F141" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G141" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H141" t="str">
         <v/>
       </c>
       <c r="I141" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>METAS</v>
       </c>
     </row>
     <row r="142">
@@ -4502,19 +4502,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E142" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F142" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G142" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H142" t="str">
         <v/>
       </c>
       <c r="I142" t="str">
-        <v>Absenteismo_Days</v>
+        <v>Other_KPIs_HR</v>
       </c>
     </row>
     <row r="143">
@@ -4531,19 +4531,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E143" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F143" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G143" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H143" t="str">
         <v/>
       </c>
       <c r="I143" t="str">
-        <v>'Elegiveis cota aprendiz$'</v>
+        <v>Extract</v>
       </c>
     </row>
     <row r="144">
@@ -4560,19 +4560,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E144" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F144" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G144" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H144" t="str">
         <v/>
       </c>
       <c r="I144" t="str">
-        <v>'Women Leardership$'</v>
+        <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
     <row r="145">
@@ -4583,7 +4583,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C145" t="str">
-        <v>Elegiveis cota aprendiz (Tableau)</v>
+        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
       </c>
       <c r="D145" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
@@ -4592,16 +4592,16 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G145" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H145" t="str">
         <v/>
       </c>
       <c r="I145" t="str">
-        <v>Promoções_Internas</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="146">
@@ -4612,7 +4612,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C146" t="str">
-        <v>Elegiveis cota aprendiz (Tableau)</v>
+        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
       </c>
       <c r="D146" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
@@ -4621,16 +4621,16 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G146" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H146" t="str">
         <v/>
       </c>
       <c r="I146" t="str">
-        <v>METAS</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="147">
@@ -4641,7 +4641,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C147" t="str">
-        <v>Elegiveis cota aprendiz (Tableau)</v>
+        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
       </c>
       <c r="D147" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
@@ -4650,16 +4650,16 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G147" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H147" t="str">
         <v/>
       </c>
       <c r="I147" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="148">
@@ -4670,7 +4670,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C148" t="str">
-        <v>Elegiveis cota aprendiz (Tableau)</v>
+        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
       </c>
       <c r="D148" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
@@ -4679,16 +4679,16 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G148" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H148" t="str">
         <v/>
       </c>
       <c r="I148" t="str">
-        <v>Extract</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="149">
@@ -4699,7 +4699,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C149" t="str">
-        <v>Elegiveis cota aprendiz (Tableau)</v>
+        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
       </c>
       <c r="D149" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
@@ -4708,16 +4708,16 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G149" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H149" t="str">
         <v/>
       </c>
       <c r="I149" t="str">
-        <v>Absenteismo_Days_Segmentos</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="150">
@@ -4737,16 +4737,16 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G150" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H150" t="str">
         <v/>
       </c>
       <c r="I150" t="str">
-        <v>D_COLABORADOR</v>
+        <v>Absenteismo_Days</v>
       </c>
     </row>
     <row r="151">
@@ -4766,16 +4766,16 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G151" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H151" t="str">
         <v/>
       </c>
       <c r="I151" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
     <row r="152">
@@ -4795,16 +4795,16 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G152" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H152" t="str">
         <v/>
       </c>
       <c r="I152" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>'Women Leardership$'</v>
       </c>
     </row>
     <row r="153">
@@ -4824,16 +4824,16 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G153" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H153" t="str">
         <v/>
       </c>
       <c r="I153" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>Promoções_Internas</v>
       </c>
     </row>
     <row r="154">
@@ -4853,16 +4853,16 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G154" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H154" t="str">
         <v/>
       </c>
       <c r="I154" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>METAS</v>
       </c>
     </row>
     <row r="155">
@@ -4882,16 +4882,16 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G155" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H155" t="str">
         <v/>
       </c>
       <c r="I155" t="str">
-        <v>Absenteismo_Days</v>
+        <v>Other_KPIs_HR</v>
       </c>
     </row>
     <row r="156">
@@ -4911,16 +4911,16 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G156" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H156" t="str">
         <v/>
       </c>
       <c r="I156" t="str">
-        <v>'Elegiveis cota aprendiz$'</v>
+        <v>Extract</v>
       </c>
     </row>
     <row r="157">
@@ -4940,16 +4940,16 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G157" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H157" t="str">
         <v/>
       </c>
       <c r="I157" t="str">
-        <v>'Women Leardership$'</v>
+        <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
     <row r="158">
@@ -4960,25 +4960,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C158" t="str">
-        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
+        <v>METAS_HE_ABSENTEISMO</v>
       </c>
       <c r="D158" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E158" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F158" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G158" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H158" t="str">
         <v/>
       </c>
       <c r="I158" t="str">
-        <v>Promoções_Internas</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="159">
@@ -4989,25 +4989,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C159" t="str">
-        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
+        <v>METAS_HE_ABSENTEISMO</v>
       </c>
       <c r="D159" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E159" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F159" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G159" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H159" t="str">
         <v/>
       </c>
       <c r="I159" t="str">
-        <v>METAS</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="160">
@@ -5018,25 +5018,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C160" t="str">
-        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
+        <v>METAS_HE_ABSENTEISMO</v>
       </c>
       <c r="D160" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E160" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F160" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G160" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H160" t="str">
         <v/>
       </c>
       <c r="I160" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="161">
@@ -5047,25 +5047,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C161" t="str">
-        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
+        <v>METAS_HE_ABSENTEISMO</v>
       </c>
       <c r="D161" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E161" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F161" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G161" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H161" t="str">
         <v/>
       </c>
       <c r="I161" t="str">
-        <v>Extract</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="162">
@@ -5076,25 +5076,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C162" t="str">
-        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
+        <v>METAS_HE_ABSENTEISMO</v>
       </c>
       <c r="D162" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E162" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F162" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G162" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H162" t="str">
         <v/>
       </c>
       <c r="I162" t="str">
-        <v>Absenteismo_Days_Segmentos</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="163">
@@ -5111,19 +5111,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E163" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F163" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G163" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H163" t="str">
         <v/>
       </c>
       <c r="I163" t="str">
-        <v>D_COLABORADOR</v>
+        <v>Absenteismo_Days</v>
       </c>
     </row>
     <row r="164">
@@ -5140,19 +5140,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E164" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F164" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G164" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H164" t="str">
         <v/>
       </c>
       <c r="I164" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
     <row r="165">
@@ -5169,19 +5169,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E165" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F165" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G165" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H165" t="str">
         <v/>
       </c>
       <c r="I165" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>'Women Leardership$'</v>
       </c>
     </row>
     <row r="166">
@@ -5198,19 +5198,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E166" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F166" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G166" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H166" t="str">
         <v/>
       </c>
       <c r="I166" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>Promoções_Internas</v>
       </c>
     </row>
     <row r="167">
@@ -5227,19 +5227,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E167" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F167" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G167" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H167" t="str">
         <v/>
       </c>
       <c r="I167" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>METAS</v>
       </c>
     </row>
     <row r="168">
@@ -5256,19 +5256,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E168" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F168" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G168" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H168" t="str">
         <v/>
       </c>
       <c r="I168" t="str">
-        <v>Absenteismo_Days</v>
+        <v>Other_KPIs_HR</v>
       </c>
     </row>
     <row r="169">
@@ -5285,19 +5285,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E169" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F169" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G169" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H169" t="str">
         <v/>
       </c>
       <c r="I169" t="str">
-        <v>'Elegiveis cota aprendiz$'</v>
+        <v>Extract</v>
       </c>
     </row>
     <row r="170">
@@ -5314,19 +5314,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E170" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F170" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G170" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H170" t="str">
         <v/>
       </c>
       <c r="I170" t="str">
-        <v>'Women Leardership$'</v>
+        <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
     <row r="171">
@@ -5337,25 +5337,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C171" t="str">
-        <v>METAS_HE_ABSENTEISMO</v>
+        <v>Other_KPIs_HR</v>
       </c>
       <c r="D171" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E171" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F171" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G171" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H171" t="str">
         <v/>
       </c>
       <c r="I171" t="str">
-        <v>Promoções_Internas</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="172">
@@ -5366,25 +5366,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C172" t="str">
-        <v>METAS_HE_ABSENTEISMO</v>
+        <v>Other_KPIs_HR</v>
       </c>
       <c r="D172" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E172" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F172" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G172" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H172" t="str">
         <v/>
       </c>
       <c r="I172" t="str">
-        <v>METAS</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="173">
@@ -5395,25 +5395,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C173" t="str">
-        <v>METAS_HE_ABSENTEISMO</v>
+        <v>Other_KPIs_HR</v>
       </c>
       <c r="D173" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E173" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F173" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G173" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H173" t="str">
         <v/>
       </c>
       <c r="I173" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="174">
@@ -5424,25 +5424,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C174" t="str">
-        <v>METAS_HE_ABSENTEISMO</v>
+        <v>Other_KPIs_HR</v>
       </c>
       <c r="D174" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E174" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F174" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G174" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H174" t="str">
         <v/>
       </c>
       <c r="I174" t="str">
-        <v>Extract</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="175">
@@ -5453,25 +5453,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C175" t="str">
-        <v>METAS_HE_ABSENTEISMO</v>
+        <v>Other_KPIs_HR</v>
       </c>
       <c r="D175" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E175" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F175" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G175" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H175" t="str">
         <v/>
       </c>
       <c r="I175" t="str">
-        <v>Absenteismo_Days_Segmentos</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="176">
@@ -5488,19 +5488,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E176" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F176" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G176" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H176" t="str">
         <v/>
       </c>
       <c r="I176" t="str">
-        <v>D_COLABORADOR</v>
+        <v>Absenteismo_Days</v>
       </c>
     </row>
     <row r="177">
@@ -5517,19 +5517,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E177" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F177" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G177" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H177" t="str">
         <v/>
       </c>
       <c r="I177" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
     <row r="178">
@@ -5546,19 +5546,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E178" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F178" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G178" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H178" t="str">
         <v/>
       </c>
       <c r="I178" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>'Women Leardership$'</v>
       </c>
     </row>
     <row r="179">
@@ -5575,19 +5575,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E179" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F179" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G179" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H179" t="str">
         <v/>
       </c>
       <c r="I179" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>Promoções_Internas</v>
       </c>
     </row>
     <row r="180">
@@ -5604,19 +5604,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E180" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F180" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G180" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H180" t="str">
         <v/>
       </c>
       <c r="I180" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>METAS</v>
       </c>
     </row>
     <row r="181">
@@ -5633,19 +5633,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E181" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F181" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G181" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H181" t="str">
         <v/>
       </c>
       <c r="I181" t="str">
-        <v>Absenteismo_Days</v>
+        <v>Other_KPIs_HR</v>
       </c>
     </row>
     <row r="182">
@@ -5662,19 +5662,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E182" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F182" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G182" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H182" t="str">
         <v/>
       </c>
       <c r="I182" t="str">
-        <v>'Elegiveis cota aprendiz$'</v>
+        <v>Extract</v>
       </c>
     </row>
     <row r="183">
@@ -5691,19 +5691,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E183" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F183" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G183" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H183" t="str">
         <v/>
       </c>
       <c r="I183" t="str">
-        <v>'Women Leardership$'</v>
+        <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
     <row r="184">
@@ -5714,25 +5714,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C184" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>Promoções_Internas</v>
       </c>
       <c r="D184" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E184" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F184" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G184" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H184" t="str">
         <v/>
       </c>
       <c r="I184" t="str">
-        <v>Promoções_Internas</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="185">
@@ -5743,25 +5743,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C185" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>Promoções_Internas</v>
       </c>
       <c r="D185" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E185" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F185" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G185" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H185" t="str">
         <v/>
       </c>
       <c r="I185" t="str">
-        <v>METAS</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="186">
@@ -5772,25 +5772,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C186" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>Promoções_Internas</v>
       </c>
       <c r="D186" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E186" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F186" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G186" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H186" t="str">
         <v/>
       </c>
       <c r="I186" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="187">
@@ -5801,25 +5801,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C187" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>Promoções_Internas</v>
       </c>
       <c r="D187" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E187" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F187" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G187" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H187" t="str">
         <v/>
       </c>
       <c r="I187" t="str">
-        <v>Extract</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="188">
@@ -5830,25 +5830,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C188" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>Promoções_Internas</v>
       </c>
       <c r="D188" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E188" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F188" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G188" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H188" t="str">
         <v/>
       </c>
       <c r="I188" t="str">
-        <v>Absenteismo_Days_Segmentos</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="189">
@@ -5865,19 +5865,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E189" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F189" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G189" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H189" t="str">
         <v/>
       </c>
       <c r="I189" t="str">
-        <v>D_COLABORADOR</v>
+        <v>Absenteismo_Days</v>
       </c>
     </row>
     <row r="190">
@@ -5894,19 +5894,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E190" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F190" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G190" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H190" t="str">
         <v/>
       </c>
       <c r="I190" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
     <row r="191">
@@ -5923,19 +5923,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E191" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F191" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G191" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H191" t="str">
         <v/>
       </c>
       <c r="I191" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>'Women Leardership$'</v>
       </c>
     </row>
     <row r="192">
@@ -5952,19 +5952,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E192" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F192" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G192" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H192" t="str">
         <v/>
       </c>
       <c r="I192" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>Promoções_Internas</v>
       </c>
     </row>
     <row r="193">
@@ -5981,19 +5981,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E193" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F193" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G193" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H193" t="str">
         <v/>
       </c>
       <c r="I193" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>METAS</v>
       </c>
     </row>
     <row r="194">
@@ -6010,19 +6010,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E194" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F194" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G194" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H194" t="str">
         <v/>
       </c>
       <c r="I194" t="str">
-        <v>Absenteismo_Days</v>
+        <v>Other_KPIs_HR</v>
       </c>
     </row>
     <row r="195">
@@ -6039,19 +6039,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E195" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F195" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G195" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H195" t="str">
         <v/>
       </c>
       <c r="I195" t="str">
-        <v>'Elegiveis cota aprendiz$'</v>
+        <v>Extract</v>
       </c>
     </row>
     <row r="196">
@@ -6068,33 +6068,33 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E196" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F196" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G196" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H196" t="str">
         <v/>
       </c>
       <c r="I196" t="str">
-        <v>'Women Leardership$'</v>
+        <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
+        <v>Metas Turnover FY26 - Regrettable e Demissional</v>
       </c>
       <c r="B197" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY26-RegrettableeDemissional/MetasdeRHFY26</v>
       </c>
       <c r="C197" t="str">
-        <v>Promoções_Internas</v>
+        <v/>
       </c>
       <c r="D197" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -6109,21 +6109,21 @@
         <v/>
       </c>
       <c r="I197" t="str">
-        <v>Promoções_Internas</v>
+        <v/>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
+        <v>Women Leadership</v>
       </c>
       <c r="B198" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
       </c>
       <c r="C198" t="str">
-        <v>Promoções_Internas</v>
+        <v/>
       </c>
       <c r="D198" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
+        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -6138,94 +6138,94 @@
         <v/>
       </c>
       <c r="I198" t="str">
-        <v>METAS</v>
+        <v/>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
+        <v>Wokforce Planning</v>
       </c>
       <c r="B199" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C199" t="str">
-        <v>Promoções_Internas</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D199" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G199" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H199" t="str">
-        <v/>
+        <v>bicompras</v>
       </c>
       <c r="I199" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
+        <v>Wokforce Planning</v>
       </c>
       <c r="B200" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C200" t="str">
-        <v>Promoções_Internas</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D200" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G200" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H200" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I200" t="str">
-        <v>Extract</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
+        <v>Wokforce Planning</v>
       </c>
       <c r="B201" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C201" t="str">
-        <v>Promoções_Internas</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D201" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G201" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H201" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I201" t="str">
-        <v>Absenteismo_Days_Segmentos</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="202">
@@ -6245,16 +6245,16 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G202" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H202" t="str">
-        <v>bicompras</v>
+        <v>dpessoal</v>
       </c>
       <c r="I202" t="str">
-        <v>d_filial</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="203">
@@ -6274,16 +6274,16 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G203" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H203" t="str">
-        <v>DPESSOAL</v>
+        <v>portalbi</v>
       </c>
       <c r="I203" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="204">
@@ -6303,16 +6303,16 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G204" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H204" t="str">
-        <v>DPESSOAL</v>
+        <v>bisilver</v>
       </c>
       <c r="I204" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="205">
@@ -6332,16 +6332,16 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G205" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H205" t="str">
-        <v>dpessoal</v>
+        <v>ciscorp</v>
       </c>
       <c r="I205" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="206">
@@ -6352,25 +6352,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C206" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>DE-PARA_BU</v>
       </c>
       <c r="D206" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E206" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F206" t="str">
-        <v/>
+        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
       </c>
       <c r="G206" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H206" t="str">
-        <v>portalbi</v>
+        <v/>
       </c>
       <c r="I206" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="207">
@@ -6381,25 +6381,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C207" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>DE-PARA_BU</v>
       </c>
       <c r="D207" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E207" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F207" t="str">
-        <v/>
+        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
       </c>
       <c r="G207" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H207" t="str">
-        <v>bisilver</v>
+        <v/>
       </c>
       <c r="I207" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="208">
@@ -6410,25 +6410,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C208" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>DE-PARA_BU</v>
       </c>
       <c r="D208" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E208" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F208" t="str">
-        <v/>
+        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
       </c>
       <c r="G208" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H208" t="str">
-        <v>ciscorp</v>
+        <v/>
       </c>
       <c r="I208" t="str">
-        <v>filial</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="209">
@@ -6445,19 +6445,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E209" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F209" t="str">
-        <v/>
+        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
       </c>
       <c r="G209" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H209" t="str">
         <v/>
       </c>
       <c r="I209" t="str">
-        <v>D_COLABORADOR</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="210">
@@ -6474,19 +6474,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E210" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F210" t="str">
-        <v/>
+        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
       </c>
       <c r="G210" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H210" t="str">
         <v/>
       </c>
       <c r="I210" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="211">
@@ -6503,19 +6503,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E211" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F211" t="str">
-        <v/>
+        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
       </c>
       <c r="G211" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H211" t="str">
         <v/>
       </c>
       <c r="I211" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="212">
@@ -6532,19 +6532,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E212" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F212" t="str">
-        <v/>
+        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
       </c>
       <c r="G212" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H212" t="str">
         <v/>
       </c>
       <c r="I212" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>'DE PARA$'</v>
       </c>
     </row>
     <row r="213">
@@ -6555,25 +6555,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C213" t="str">
-        <v>DE-PARA_BU</v>
+        <v>Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D213" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E213" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F213" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G213" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H213" t="str">
         <v/>
       </c>
       <c r="I213" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="214">
@@ -6584,25 +6584,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C214" t="str">
-        <v>DE-PARA_BU</v>
+        <v>Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D214" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E214" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F214" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G214" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H214" t="str">
         <v/>
       </c>
       <c r="I214" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="215">
@@ -6613,25 +6613,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C215" t="str">
-        <v>DE-PARA_BU</v>
+        <v>Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D215" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E215" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F215" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G215" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H215" t="str">
         <v/>
       </c>
       <c r="I215" t="str">
-        <v>'DE PARA$'</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="216">
@@ -6648,19 +6648,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E216" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F216" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G216" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H216" t="str">
         <v/>
       </c>
       <c r="I216" t="str">
-        <v>D_COLABORADOR</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="217">
@@ -6677,19 +6677,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E217" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F217" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G217" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H217" t="str">
         <v/>
       </c>
       <c r="I217" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="218">
@@ -6706,19 +6706,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E218" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F218" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G218" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H218" t="str">
         <v/>
       </c>
       <c r="I218" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="219">
@@ -6735,19 +6735,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E219" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F219" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G219" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H219" t="str">
         <v/>
       </c>
       <c r="I219" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>'DE PARA$'</v>
       </c>
     </row>
     <row r="220">
@@ -6758,7 +6758,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C220" t="str">
-        <v>Elegiveis cota aprendiz (Tableau)</v>
+        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
       </c>
       <c r="D220" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
@@ -6767,16 +6767,16 @@
         <v/>
       </c>
       <c r="F220" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G220" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H220" t="str">
         <v/>
       </c>
       <c r="I220" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="221">
@@ -6787,7 +6787,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C221" t="str">
-        <v>Elegiveis cota aprendiz (Tableau)</v>
+        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
       </c>
       <c r="D221" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
@@ -6796,16 +6796,16 @@
         <v/>
       </c>
       <c r="F221" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G221" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H221" t="str">
         <v/>
       </c>
       <c r="I221" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="222">
@@ -6816,7 +6816,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C222" t="str">
-        <v>Elegiveis cota aprendiz (Tableau)</v>
+        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
       </c>
       <c r="D222" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
@@ -6825,16 +6825,16 @@
         <v/>
       </c>
       <c r="F222" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G222" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H222" t="str">
         <v/>
       </c>
       <c r="I222" t="str">
-        <v>'DE PARA$'</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="223">
@@ -6854,16 +6854,16 @@
         <v/>
       </c>
       <c r="F223" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G223" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H223" t="str">
         <v/>
       </c>
       <c r="I223" t="str">
-        <v>D_COLABORADOR</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="224">
@@ -6883,16 +6883,16 @@
         <v/>
       </c>
       <c r="F224" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G224" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H224" t="str">
         <v/>
       </c>
       <c r="I224" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="225">
@@ -6912,16 +6912,16 @@
         <v/>
       </c>
       <c r="F225" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G225" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H225" t="str">
         <v/>
       </c>
       <c r="I225" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="226">
@@ -6941,16 +6941,16 @@
         <v/>
       </c>
       <c r="F226" t="str">
-        <v/>
+        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
       </c>
       <c r="G226" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H226" t="str">
         <v/>
       </c>
       <c r="I226" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>'DE PARA$'</v>
       </c>
     </row>
     <row r="227">
@@ -6961,25 +6961,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C227" t="str">
-        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
+        <v>METAS_HE_ABSENTEISMO</v>
       </c>
       <c r="D227" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E227" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F227" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G227" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H227" t="str">
         <v/>
       </c>
       <c r="I227" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="228">
@@ -6990,25 +6990,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C228" t="str">
-        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
+        <v>METAS_HE_ABSENTEISMO</v>
       </c>
       <c r="D228" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E228" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F228" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G228" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H228" t="str">
         <v/>
       </c>
       <c r="I228" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="229">
@@ -7019,25 +7019,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C229" t="str">
-        <v>EXPURGO_PEDIDO_DEMISSAO_FY24 Extração</v>
+        <v>METAS_HE_ABSENTEISMO</v>
       </c>
       <c r="D229" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E229" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F229" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G229" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H229" t="str">
         <v/>
       </c>
       <c r="I229" t="str">
-        <v>'DE PARA$'</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="230">
@@ -7054,19 +7054,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E230" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F230" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G230" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H230" t="str">
         <v/>
       </c>
       <c r="I230" t="str">
-        <v>D_COLABORADOR</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="231">
@@ -7083,19 +7083,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E231" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F231" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G231" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H231" t="str">
         <v/>
       </c>
       <c r="I231" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="232">
@@ -7112,19 +7112,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E232" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F232" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G232" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H232" t="str">
         <v/>
       </c>
       <c r="I232" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="233">
@@ -7141,19 +7141,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E233" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F233" t="str">
-        <v/>
+        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
       </c>
       <c r="G233" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H233" t="str">
         <v/>
       </c>
       <c r="I233" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>'DE PARA$'</v>
       </c>
     </row>
     <row r="234">
@@ -7164,25 +7164,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C234" t="str">
-        <v>METAS_HE_ABSENTEISMO</v>
+        <v>Other_KPIs_HR</v>
       </c>
       <c r="D234" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E234" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F234" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G234" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H234" t="str">
         <v/>
       </c>
       <c r="I234" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="235">
@@ -7193,25 +7193,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C235" t="str">
-        <v>METAS_HE_ABSENTEISMO</v>
+        <v>Other_KPIs_HR</v>
       </c>
       <c r="D235" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E235" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F235" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G235" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H235" t="str">
         <v/>
       </c>
       <c r="I235" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="236">
@@ -7222,25 +7222,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C236" t="str">
-        <v>METAS_HE_ABSENTEISMO</v>
+        <v>Other_KPIs_HR</v>
       </c>
       <c r="D236" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E236" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F236" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G236" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H236" t="str">
         <v/>
       </c>
       <c r="I236" t="str">
-        <v>'DE PARA$'</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="237">
@@ -7257,19 +7257,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E237" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F237" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G237" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H237" t="str">
         <v/>
       </c>
       <c r="I237" t="str">
-        <v>D_COLABORADOR</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="238">
@@ -7286,19 +7286,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E238" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F238" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G238" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H238" t="str">
         <v/>
       </c>
       <c r="I238" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="239">
@@ -7315,19 +7315,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E239" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F239" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G239" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H239" t="str">
         <v/>
       </c>
       <c r="I239" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="240">
@@ -7344,19 +7344,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E240" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F240" t="str">
-        <v/>
+        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
       </c>
       <c r="G240" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H240" t="str">
         <v/>
       </c>
       <c r="I240" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>'DE PARA$'</v>
       </c>
     </row>
     <row r="241">
@@ -7367,25 +7367,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C241" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>Promoções_Internas</v>
       </c>
       <c r="D241" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E241" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F241" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G241" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H241" t="str">
         <v/>
       </c>
       <c r="I241" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="242">
@@ -7396,25 +7396,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C242" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>Promoções_Internas</v>
       </c>
       <c r="D242" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E242" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F242" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G242" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H242" t="str">
         <v/>
       </c>
       <c r="I242" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="243">
@@ -7425,25 +7425,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C243" t="str">
-        <v>Other_KPIs_HR</v>
+        <v>Promoções_Internas</v>
       </c>
       <c r="D243" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E243" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F243" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G243" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H243" t="str">
         <v/>
       </c>
       <c r="I243" t="str">
-        <v>'DE PARA$'</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="244">
@@ -7460,19 +7460,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E244" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F244" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G244" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H244" t="str">
         <v/>
       </c>
       <c r="I244" t="str">
-        <v>D_COLABORADOR</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="245">
@@ -7489,19 +7489,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E245" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F245" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G245" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H245" t="str">
         <v/>
       </c>
       <c r="I245" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="246">
@@ -7518,19 +7518,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E246" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F246" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G246" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H246" t="str">
         <v/>
       </c>
       <c r="I246" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="247">
@@ -7547,106 +7547,106 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E247" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F247" t="str">
-        <v/>
+        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
       </c>
       <c r="G247" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H247" t="str">
         <v/>
       </c>
       <c r="I247" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>'DE PARA$'</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Wokforce Planning</v>
+        <v>Indicadores de Chamados e Workflows</v>
       </c>
       <c r="B248" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
       </c>
       <c r="C248" t="str">
-        <v>Promoções_Internas</v>
+        <v>dCalendario</v>
       </c>
       <c r="D248" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E248" t="str">
         <v/>
       </c>
       <c r="F248" t="str">
-        <v/>
+        <v>Ano; Ano Fiscal; Data; Dia; Dia da Semana; Dia da Semana ID; Extract (Count); Fiscal Year; Mês; Mês Abr; Mês Fiscal; Mês ID; Mês/Ano; Mês/Ano ID; Período Fiscal ID; Período/FY; Período/FY ID; Semana do Ano; Semana do Ano ID; Semana Fiscal do Ano; Semana Fiscal do Ano ID; Semana Fiscal/Ano ID; Semana/Ano; Semana/Ano ID; Semestre Fiscal / Ano ID; Semestre Fiscal do Ano; Semestre ID; Trimestre Fiscal; Trimestre Fiscal/Ano; Trimestre Fiscal/Ano ID</v>
       </c>
       <c r="G248" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H248" t="str">
         <v/>
       </c>
       <c r="I248" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>Extract</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Wokforce Planning</v>
+        <v>Indicadores de Chamados e Workflows</v>
       </c>
       <c r="B249" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
       </c>
       <c r="C249" t="str">
-        <v>Promoções_Internas</v>
+        <v>fChamadosEmAberto</v>
       </c>
       <c r="D249" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E249" t="str">
         <v/>
       </c>
       <c r="F249" t="str">
-        <v/>
+        <v>Assunto; Atribuído ao Usuário; Criador; Data de Conclusão Alvo; Data de Criação; Data Referência; Em nome de; Equipe Atribuída; Extract (Count); Fila Atribuída; Fonte; Horas SLA; ID do caso; ID do Caso Relacionado; Prioridade; Solicitado por; Status do caso; Subtópico de RH; Tema de RH</v>
       </c>
       <c r="G249" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H249" t="str">
         <v/>
       </c>
       <c r="I249" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>Extract</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Wokforce Planning</v>
+        <v>Indicadores de Chamados e Workflows</v>
       </c>
       <c r="B250" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
       </c>
       <c r="C250" t="str">
-        <v>Promoções_Internas</v>
+        <v>fChamadosResolvidos</v>
       </c>
       <c r="D250" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E250" t="str">
         <v/>
       </c>
       <c r="F250" t="str">
-        <v/>
+        <v>% No Prazo; :Measure Names; Ano Fiscal; Assunto; Atingiu a Meta; Atribuído ao Usuário; Criador; Data de Conclusão Alvo; Data de Conclusão Alvo Ajustada; Data de Criação; Data de reabertura; Data Referência Resolução; Data/Hora da Primeira Resposta; Data/Hora Resolvida; Dia da Semana Criação; Em nome de; Equipe Atribuída; Extract (Count); Fila Atribuída (Subequipe); Fonte; Horas SLA; ID do Caso Relacionado; Meta; Número do chamado; Período Fiscal; Prioridade; Qtde Em Atraso; Qtde No Prazo; Reabertos; Solicitado por; Status do chamado; Status Prazo Primeiro Atendimento; Subtópico de RH; Tema de RH; Tempo de Resolução do Caso (Dias Úteis); Tempo de Trabalho em Dias Úteis; Tempo de trabalho em horas úteis (até agora); Total Atendimentos</v>
       </c>
       <c r="G250" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H250" t="str">
         <v/>
       </c>
       <c r="I250" t="str">
-        <v>'DE PARA$'</v>
+        <v>Extract</v>
       </c>
     </row>
     <row r="251">
@@ -7657,7 +7657,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
       </c>
       <c r="C251" t="str">
-        <v>dCalendario</v>
+        <v>fWorkflowsEmAberto</v>
       </c>
       <c r="D251" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
@@ -7666,10 +7666,10 @@
         <v/>
       </c>
       <c r="F251" t="str">
-        <v/>
+        <v>Data da Etapa; Data prazo atendimento; Data Referencia; Data/hora início da transação; Dentro do prazo?; Equipe; Etapa de Workflow; Extract (Count); Feriado; Formulário de Workflow; Id etapa de workflow; Id Formulário de Workflow; Id Lançamento de Workflow; Nome do Usuário; Referência; Solicitante; Subequipe</v>
       </c>
       <c r="G251" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H251" t="str">
         <v/>
@@ -7686,7 +7686,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
       </c>
       <c r="C252" t="str">
-        <v>fChamadosEmAberto</v>
+        <v>fWorkflowsResolvidos</v>
       </c>
       <c r="D252" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
@@ -7695,10 +7695,10 @@
         <v/>
       </c>
       <c r="F252" t="str">
-        <v/>
+        <v>% Dentro do Prazo; :Measure Names; Ano Fiscal; Atendido Em; Categoria Dia Entrada Wf; Categoria Dia Prazo Atend; Data Prazo Atendimento; Data Prazo Atendimento 2; Data Referencia; Data Rescisão; Dentro Prazo?; Efetivado?; Entrada Wf; Entrada Wf 2; Equipe; Etapa Destino; Etapa Origem; Etapa Wf - Destino; Etapa Wf - Origem; Extract (Count); Formulário Wf; Grupo Usuário; Id Formulário Wf; Id Grupo Usuário; Id Log Transação Wf; Id Workflow; Meta WFs; Nome Usuário; Novo Status Dentro Prazo; Período Fiscal; Prazo Atendimento 1º Dia Útil Próximo Mês; Prazo Atendimento Exceto Abertura Fim De Mês; Qtde Dentro do Prazo; Qtde Fora do Prazo; Status da Meta; Subequipe; Superior Hierárquico; Tempo Atendim Horas Uteis; Tempo Atendimento Hr; Total Atendimentos</v>
       </c>
       <c r="G252" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H252" t="str">
         <v/>
@@ -7709,89 +7709,89 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Indicadores de Chamados e Workflows</v>
+        <v>Visão consolidada</v>
       </c>
       <c r="B253" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
       </c>
       <c r="C253" t="str">
-        <v>fChamadosResolvidos</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D253" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E253" t="str">
         <v/>
       </c>
       <c r="F253" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G253" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H253" t="str">
-        <v/>
+        <v>bicompras</v>
       </c>
       <c r="I253" t="str">
-        <v>Extract</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Indicadores de Chamados e Workflows</v>
+        <v>Visão consolidada</v>
       </c>
       <c r="B254" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
       </c>
       <c r="C254" t="str">
-        <v>fWorkflowsEmAberto</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D254" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E254" t="str">
         <v/>
       </c>
       <c r="F254" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G254" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H254" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I254" t="str">
-        <v>Extract</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Indicadores de Chamados e Workflows</v>
+        <v>Visão consolidada</v>
       </c>
       <c r="B255" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
       </c>
       <c r="C255" t="str">
-        <v>fWorkflowsResolvidos</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D255" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E255" t="str">
         <v/>
       </c>
       <c r="F255" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G255" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H255" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I255" t="str">
-        <v>Extract</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="256">
@@ -7811,16 +7811,16 @@
         <v/>
       </c>
       <c r="F256" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G256" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H256" t="str">
-        <v>bicompras</v>
+        <v>dpessoal</v>
       </c>
       <c r="I256" t="str">
-        <v>d_filial</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="257">
@@ -7840,16 +7840,16 @@
         <v/>
       </c>
       <c r="F257" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G257" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H257" t="str">
-        <v>DPESSOAL</v>
+        <v>portalbi</v>
       </c>
       <c r="I257" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="258">
@@ -7869,16 +7869,16 @@
         <v/>
       </c>
       <c r="F258" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G258" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H258" t="str">
-        <v>DPESSOAL</v>
+        <v>bisilver</v>
       </c>
       <c r="I258" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="259">
@@ -7898,16 +7898,16 @@
         <v/>
       </c>
       <c r="F259" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G259" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H259" t="str">
-        <v>dpessoal</v>
+        <v>ciscorp</v>
       </c>
       <c r="I259" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="260">
@@ -7918,25 +7918,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
       </c>
       <c r="C260" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D260" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E260" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F260" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G260" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H260" t="str">
-        <v>portalbi</v>
+        <v/>
       </c>
       <c r="I260" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="261">
@@ -7947,25 +7947,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
       </c>
       <c r="C261" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D261" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E261" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F261" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G261" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H261" t="str">
-        <v>bisilver</v>
+        <v/>
       </c>
       <c r="I261" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="262">
@@ -7976,25 +7976,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
       </c>
       <c r="C262" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D262" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E262" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F262" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G262" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H262" t="str">
-        <v>ciscorp</v>
+        <v/>
       </c>
       <c r="I262" t="str">
-        <v>filial</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="263">
@@ -8011,19 +8011,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E263" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F263" t="str">
-        <v/>
+        <v>Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
       <c r="G263" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H263" t="str">
         <v/>
       </c>
       <c r="I263" t="str">
-        <v>D_COLABORADOR</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="264">
@@ -8034,25 +8034,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
       </c>
       <c r="C264" t="str">
-        <v>Elegiveis cota aprendiz (Tableau)</v>
+        <v>PCD (Tableau)</v>
       </c>
       <c r="D264" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E264" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F264" t="str">
-        <v/>
+        <v>Matrícula; PCD (Count); Qtd. Pcd</v>
       </c>
       <c r="G264" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H264" t="str">
         <v/>
       </c>
       <c r="I264" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="265">
@@ -8063,25 +8063,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
       </c>
       <c r="C265" t="str">
-        <v>Elegiveis cota aprendiz (Tableau)</v>
+        <v>PCD (Tableau)</v>
       </c>
       <c r="D265" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E265" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F265" t="str">
-        <v/>
+        <v>Matrícula; PCD (Count); Qtd. Pcd</v>
       </c>
       <c r="G265" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H265" t="str">
         <v/>
       </c>
       <c r="I265" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="266">
@@ -8092,25 +8092,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
       </c>
       <c r="C266" t="str">
-        <v>Elegiveis cota aprendiz (Tableau)</v>
+        <v>PCD (Tableau)</v>
       </c>
       <c r="D266" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E266" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F266" t="str">
-        <v/>
+        <v>Matrícula; PCD (Count); Qtd. Pcd</v>
       </c>
       <c r="G266" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H266" t="str">
         <v/>
       </c>
       <c r="I266" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
     <row r="267">
@@ -8127,106 +8127,106 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E267" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F267" t="str">
-        <v/>
+        <v>Matrícula; PCD (Count); Qtd. Pcd</v>
       </c>
       <c r="G267" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H267" t="str">
         <v/>
       </c>
       <c r="I267" t="str">
-        <v>D_COLABORADOR</v>
+        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Visão consolidada</v>
+        <v>Zona Posicionamento Salarial</v>
       </c>
       <c r="B268" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
       </c>
       <c r="C268" t="str">
-        <v>PCD (Tableau)</v>
+        <v>RH - Base_Enios_Tableau</v>
       </c>
       <c r="D268" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/52187/lineage</v>
       </c>
       <c r="E268" t="str">
         <v/>
       </c>
       <c r="F268" t="str">
-        <v/>
+        <v>Admissão; Cargo; CL; Colaborador; Cpf; Dados gerados em; Diretoria; Dt Competencia; Dt inic cargo atual; Dt nasc; Gênero; Gestor; Grade; HR Reporting; Matrícula; Munic. cl; Nome do cl; Portfolio; Posição Faixa; Região cl; Segmento; Situação; Tipo cl; Uf cl; Zona posicionamento</v>
       </c>
       <c r="G268" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H268" t="str">
         <v/>
       </c>
       <c r="I268" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>Extract</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Visão consolidada</v>
+        <v>Zona Posicionamento Salarial</v>
       </c>
       <c r="B269" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
       </c>
       <c r="C269" t="str">
-        <v>PCD (Tableau)</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D269" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E269" t="str">
         <v/>
       </c>
       <c r="F269" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G269" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H269" t="str">
-        <v/>
+        <v>bicompras</v>
       </c>
       <c r="I269" t="str">
-        <v>F_COLABORADOR_FOLHA_SAL</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Visão consolidada</v>
+        <v>Zona Posicionamento Salarial</v>
       </c>
       <c r="B270" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
       </c>
       <c r="C270" t="str">
-        <v>PCD (Tableau)</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D270" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E270" t="str">
         <v/>
       </c>
       <c r="F270" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G270" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H270" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I270" t="str">
-        <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="271">
@@ -8237,25 +8237,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
       </c>
       <c r="C271" t="str">
-        <v>RH - Base_Enios_Tableau</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D271" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/52187/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E271" t="str">
         <v/>
       </c>
       <c r="F271" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G271" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H271" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I271" t="str">
-        <v>Extract</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="272">
@@ -8275,16 +8275,16 @@
         <v/>
       </c>
       <c r="F272" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G272" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H272" t="str">
-        <v>bicompras</v>
+        <v>dpessoal</v>
       </c>
       <c r="I272" t="str">
-        <v>d_filial</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="273">
@@ -8304,16 +8304,16 @@
         <v/>
       </c>
       <c r="F273" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G273" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H273" t="str">
-        <v>DPESSOAL</v>
+        <v>portalbi</v>
       </c>
       <c r="I273" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="274">
@@ -8333,16 +8333,16 @@
         <v/>
       </c>
       <c r="F274" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G274" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H274" t="str">
-        <v>DPESSOAL</v>
+        <v>bisilver</v>
       </c>
       <c r="I274" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="275">
@@ -8362,24 +8362,24 @@
         <v/>
       </c>
       <c r="F275" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G275" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H275" t="str">
-        <v>dpessoal</v>
+        <v>ciscorp</v>
       </c>
       <c r="I275" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Zona Posicionamento Salarial</v>
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B276" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C276" t="str">
         <v>RH - Colaborador Folha</v>
@@ -8391,24 +8391,24 @@
         <v/>
       </c>
       <c r="F276" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G276" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H276" t="str">
-        <v>portalbi</v>
+        <v>bicompras</v>
       </c>
       <c r="I276" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Zona Posicionamento Salarial</v>
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B277" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C277" t="str">
         <v>RH - Colaborador Folha</v>
@@ -8420,24 +8420,24 @@
         <v/>
       </c>
       <c r="F277" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G277" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H277" t="str">
-        <v>bisilver</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="I277" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Zona Posicionamento Salarial</v>
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B278" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C278" t="str">
         <v>RH - Colaborador Folha</v>
@@ -8449,16 +8449,16 @@
         <v/>
       </c>
       <c r="F278" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G278" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H278" t="str">
-        <v>ciscorp</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="I278" t="str">
-        <v>filial</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="279">
@@ -8478,16 +8478,16 @@
         <v/>
       </c>
       <c r="F279" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G279" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H279" t="str">
-        <v>bicompras</v>
+        <v>dpessoal</v>
       </c>
       <c r="I279" t="str">
-        <v>d_filial</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="280">
@@ -8507,16 +8507,16 @@
         <v/>
       </c>
       <c r="F280" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G280" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H280" t="str">
-        <v>DPESSOAL</v>
+        <v>portalbi</v>
       </c>
       <c r="I280" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="281">
@@ -8536,16 +8536,16 @@
         <v/>
       </c>
       <c r="F281" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G281" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H281" t="str">
-        <v>DPESSOAL</v>
+        <v>bisilver</v>
       </c>
       <c r="I281" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="282">
@@ -8565,16 +8565,16 @@
         <v/>
       </c>
       <c r="F282" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G282" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H282" t="str">
-        <v>dpessoal</v>
+        <v>ciscorp</v>
       </c>
       <c r="I282" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="283">
@@ -8585,25 +8585,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C283" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Programação de Férias</v>
       </c>
       <c r="D283" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E283" t="str">
         <v/>
       </c>
       <c r="F283" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G283" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H283" t="str">
-        <v>portalbi</v>
+        <v/>
       </c>
       <c r="I283" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="284">
@@ -8614,25 +8614,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C284" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Programação de Férias</v>
       </c>
       <c r="D284" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E284" t="str">
         <v/>
       </c>
       <c r="F284" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G284" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H284" t="str">
-        <v>bisilver</v>
+        <v/>
       </c>
       <c r="I284" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="285">
@@ -8643,25 +8643,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C285" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Programação de Férias</v>
       </c>
       <c r="D285" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E285" t="str">
         <v/>
       </c>
       <c r="F285" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G285" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H285" t="str">
-        <v>ciscorp</v>
+        <v/>
       </c>
       <c r="I285" t="str">
-        <v>filial</v>
+        <v>VW_D_FILIAL</v>
       </c>
     </row>
     <row r="286">
@@ -8681,16 +8681,16 @@
         <v/>
       </c>
       <c r="F286" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G286" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H286" t="str">
         <v/>
       </c>
       <c r="I286" t="str">
-        <v>D_COLABORADOR</v>
+        <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
     <row r="287">
@@ -8701,25 +8701,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C287" t="str">
-        <v>RH - Programação de Férias</v>
+        <v>RH STEP Afastamento</v>
       </c>
       <c r="D287" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E287" t="str">
         <v/>
       </c>
       <c r="F287" t="str">
-        <v/>
+        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
       </c>
       <c r="G287" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H287" t="str">
-        <v/>
+        <v>bicompras</v>
       </c>
       <c r="I287" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="288">
@@ -8730,25 +8730,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C288" t="str">
-        <v>RH - Programação de Férias</v>
+        <v>RH STEP Afastamento</v>
       </c>
       <c r="D288" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E288" t="str">
         <v/>
       </c>
       <c r="F288" t="str">
-        <v/>
+        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
       </c>
       <c r="G288" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H288" t="str">
         <v/>
       </c>
       <c r="I288" t="str">
-        <v>VW_D_FILIAL</v>
+        <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
     <row r="289">
@@ -8759,25 +8759,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C289" t="str">
-        <v>RH - Programação de Férias</v>
+        <v>RH STEP Afastamento</v>
       </c>
       <c r="D289" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E289" t="str">
         <v/>
       </c>
       <c r="F289" t="str">
-        <v/>
+        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
       </c>
       <c r="G289" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H289" t="str">
-        <v/>
+        <v>portalbi</v>
       </c>
       <c r="I289" t="str">
-        <v>F_PROGRAMACAO_FERIAS</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="290">
@@ -8797,16 +8797,16 @@
         <v/>
       </c>
       <c r="F290" t="str">
-        <v/>
+        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
       </c>
       <c r="G290" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H290" t="str">
         <v>bicompras</v>
       </c>
       <c r="I290" t="str">
-        <v>d_filial</v>
+        <v>d_filial_complemento</v>
       </c>
     </row>
     <row r="291">
@@ -8826,16 +8826,16 @@
         <v/>
       </c>
       <c r="F291" t="str">
-        <v/>
+        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
       </c>
       <c r="G291" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H291" t="str">
-        <v/>
+        <v>ciscorp</v>
       </c>
       <c r="I291" t="str">
-        <v>VW_APDATA_STEP_AFASTAMENTO</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="292">
@@ -8846,25 +8846,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C292" t="str">
-        <v>RH STEP Afastamento</v>
+        <v>Base_Catracas</v>
       </c>
       <c r="D292" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E292" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F292" t="str">
-        <v/>
+        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
       </c>
       <c r="G292" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H292" t="str">
-        <v>portalbi</v>
+        <v/>
       </c>
       <c r="I292" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="293">
@@ -8875,25 +8875,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C293" t="str">
-        <v>RH STEP Afastamento</v>
+        <v>Base_Catracas</v>
       </c>
       <c r="D293" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E293" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F293" t="str">
-        <v/>
+        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
       </c>
       <c r="G293" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H293" t="str">
-        <v>bicompras</v>
+        <v/>
       </c>
       <c r="I293" t="str">
-        <v>d_filial_complemento</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="294">
@@ -8904,25 +8904,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C294" t="str">
-        <v>RH STEP Afastamento</v>
+        <v>Base_Catracas</v>
       </c>
       <c r="D294" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E294" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F294" t="str">
-        <v/>
+        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
       </c>
       <c r="G294" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H294" t="str">
-        <v>ciscorp</v>
+        <v/>
       </c>
       <c r="I294" t="str">
-        <v>filial</v>
+        <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
     <row r="295">
@@ -8933,25 +8933,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C295" t="str">
-        <v>Base_Tableau</v>
+        <v>Base_Catracas</v>
       </c>
       <c r="D295" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E295" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F295" t="str">
-        <v/>
+        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
       </c>
       <c r="G295" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H295" t="str">
         <v/>
       </c>
       <c r="I295" t="str">
-        <v>D_COLABORADOR</v>
+        <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
     <row r="296">
@@ -8962,25 +8962,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C296" t="str">
-        <v>Base_Tableau</v>
+        <v>Base_Catracas</v>
       </c>
       <c r="D296" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E296" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F296" t="str">
-        <v/>
+        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
       </c>
       <c r="G296" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H296" t="str">
         <v/>
       </c>
       <c r="I296" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>Planilha1</v>
       </c>
     </row>
     <row r="297">
@@ -8991,25 +8991,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C297" t="str">
-        <v>Base_Tableau</v>
+        <v>Base_Catracas</v>
       </c>
       <c r="D297" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E297" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F297" t="str">
-        <v/>
+        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
       </c>
       <c r="G297" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H297" t="str">
         <v/>
       </c>
       <c r="I297" t="str">
-        <v>F_PROGRAMACAO_FERIAS</v>
+        <v>Base_Tableau</v>
       </c>
     </row>
     <row r="298">
@@ -9020,25 +9020,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C298" t="str">
-        <v>Base_Tableau</v>
+        <v>Base_Catracas</v>
       </c>
       <c r="D298" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E298" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F298" t="str">
-        <v/>
+        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
       </c>
       <c r="G298" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H298" t="str">
         <v/>
       </c>
       <c r="I298" t="str">
-        <v>VW_APDATA_STEP_AFASTAMENTO</v>
+        <v>Plan1</v>
       </c>
     </row>
     <row r="299">
@@ -9055,19 +9055,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E299" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F299" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G299" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H299" t="str">
         <v/>
       </c>
       <c r="I299" t="str">
-        <v>Base_Tableau</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="300">
@@ -9084,19 +9084,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E300" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F300" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G300" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H300" t="str">
         <v/>
       </c>
       <c r="I300" t="str">
-        <v>Plan1</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="301">
@@ -9107,25 +9107,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C301" t="str">
-        <v>reserva_mesas_por_colaborador geral</v>
+        <v>Base_Tableau</v>
       </c>
       <c r="D301" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E301" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F301" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G301" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H301" t="str">
         <v/>
       </c>
       <c r="I301" t="str">
-        <v>D_COLABORADOR</v>
+        <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
     <row r="302">
@@ -9136,25 +9136,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C302" t="str">
-        <v>reserva_mesas_por_colaborador geral</v>
+        <v>Base_Tableau</v>
       </c>
       <c r="D302" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E302" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F302" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G302" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H302" t="str">
         <v/>
       </c>
       <c r="I302" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
     <row r="303">
@@ -9165,25 +9165,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C303" t="str">
-        <v>reserva_mesas_por_colaborador geral</v>
+        <v>Base_Tableau</v>
       </c>
       <c r="D303" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E303" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F303" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G303" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H303" t="str">
         <v/>
       </c>
       <c r="I303" t="str">
-        <v>F_PROGRAMACAO_FERIAS</v>
+        <v>Planilha1</v>
       </c>
     </row>
     <row r="304">
@@ -9194,25 +9194,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C304" t="str">
-        <v>reserva_mesas_por_colaborador geral</v>
+        <v>Base_Tableau</v>
       </c>
       <c r="D304" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E304" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F304" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G304" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H304" t="str">
         <v/>
       </c>
       <c r="I304" t="str">
-        <v>VW_APDATA_STEP_AFASTAMENTO</v>
+        <v>Base_Tableau</v>
       </c>
     </row>
     <row r="305">
@@ -9223,25 +9223,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C305" t="str">
-        <v>reserva_mesas_por_colaborador geral</v>
+        <v>Base_Tableau</v>
       </c>
       <c r="D305" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E305" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F305" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G305" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H305" t="str">
         <v/>
       </c>
       <c r="I305" t="str">
-        <v>Base_Tableau</v>
+        <v>Plan1</v>
       </c>
     </row>
     <row r="306">
@@ -9258,193 +9258,193 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E306" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F306" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G306" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H306" t="str">
         <v/>
       </c>
       <c r="I306" t="str">
-        <v>Plan1</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Indicadores de Promoções Internas</v>
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B307" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C307" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D307" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E307" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F307" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G307" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H307" t="str">
-        <v>bicompras</v>
+        <v/>
       </c>
       <c r="I307" t="str">
-        <v>d_filial</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Indicadores de Promoções Internas</v>
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B308" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C308" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D308" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E308" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F308" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G308" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H308" t="str">
-        <v>DPESSOAL</v>
+        <v/>
       </c>
       <c r="I308" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Indicadores de Promoções Internas</v>
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B309" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C309" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D309" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E309" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F309" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G309" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H309" t="str">
-        <v>DPESSOAL</v>
+        <v/>
       </c>
       <c r="I309" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Indicadores de Promoções Internas</v>
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B310" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C310" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D310" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E310" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F310" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G310" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H310" t="str">
-        <v>dpessoal</v>
+        <v/>
       </c>
       <c r="I310" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>Planilha1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Indicadores de Promoções Internas</v>
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B311" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C311" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D311" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E311" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F311" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G311" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H311" t="str">
-        <v>portalbi</v>
+        <v/>
       </c>
       <c r="I311" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>Base_Tableau</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Indicadores de Promoções Internas</v>
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B312" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C312" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D312" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E312" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F312" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G312" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H312" t="str">
-        <v>bisilver</v>
+        <v/>
       </c>
       <c r="I312" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>Plan1</v>
       </c>
     </row>
     <row r="313">
@@ -9464,24 +9464,24 @@
         <v/>
       </c>
       <c r="F313" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G313" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H313" t="str">
-        <v>ciscorp</v>
+        <v>bicompras</v>
       </c>
       <c r="I313" t="str">
-        <v>filial</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Indicadores de Modelo de Trabalho - Home Office</v>
+        <v>Indicadores de Promoções Internas</v>
       </c>
       <c r="B314" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
       </c>
       <c r="C314" t="str">
         <v>RH - Colaborador Folha</v>
@@ -9493,24 +9493,24 @@
         <v/>
       </c>
       <c r="F314" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G314" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H314" t="str">
-        <v>bicompras</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="I314" t="str">
-        <v>d_filial</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Indicadores de Modelo de Trabalho - Home Office</v>
+        <v>Indicadores de Promoções Internas</v>
       </c>
       <c r="B315" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
       </c>
       <c r="C315" t="str">
         <v>RH - Colaborador Folha</v>
@@ -9522,24 +9522,24 @@
         <v/>
       </c>
       <c r="F315" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G315" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H315" t="str">
         <v>DPESSOAL</v>
       </c>
       <c r="I315" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Indicadores de Modelo de Trabalho - Home Office</v>
+        <v>Indicadores de Promoções Internas</v>
       </c>
       <c r="B316" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
       </c>
       <c r="C316" t="str">
         <v>RH - Colaborador Folha</v>
@@ -9551,24 +9551,24 @@
         <v/>
       </c>
       <c r="F316" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G316" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H316" t="str">
-        <v>DPESSOAL</v>
+        <v>dpessoal</v>
       </c>
       <c r="I316" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Indicadores de Modelo de Trabalho - Home Office</v>
+        <v>Indicadores de Promoções Internas</v>
       </c>
       <c r="B317" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
       </c>
       <c r="C317" t="str">
         <v>RH - Colaborador Folha</v>
@@ -9580,24 +9580,24 @@
         <v/>
       </c>
       <c r="F317" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G317" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H317" t="str">
-        <v>dpessoal</v>
+        <v>portalbi</v>
       </c>
       <c r="I317" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Indicadores de Modelo de Trabalho - Home Office</v>
+        <v>Indicadores de Promoções Internas</v>
       </c>
       <c r="B318" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
       </c>
       <c r="C318" t="str">
         <v>RH - Colaborador Folha</v>
@@ -9609,24 +9609,24 @@
         <v/>
       </c>
       <c r="F318" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G318" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H318" t="str">
-        <v>portalbi</v>
+        <v>bisilver</v>
       </c>
       <c r="I318" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Indicadores de Modelo de Trabalho - Home Office</v>
+        <v>Indicadores de Promoções Internas</v>
       </c>
       <c r="B319" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
       </c>
       <c r="C319" t="str">
         <v>RH - Colaborador Folha</v>
@@ -9638,16 +9638,16 @@
         <v/>
       </c>
       <c r="F319" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G319" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H319" t="str">
-        <v>bisilver</v>
+        <v>ciscorp</v>
       </c>
       <c r="I319" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="320">
@@ -9667,16 +9667,16 @@
         <v/>
       </c>
       <c r="F320" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G320" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H320" t="str">
-        <v>ciscorp</v>
+        <v>bicompras</v>
       </c>
       <c r="I320" t="str">
-        <v>filial</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="321">
@@ -9687,25 +9687,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C321" t="str">
-        <v>RH - Programação de Férias</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D321" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E321" t="str">
         <v/>
       </c>
       <c r="F321" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G321" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H321" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I321" t="str">
-        <v>D_COLABORADOR</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="322">
@@ -9716,25 +9716,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C322" t="str">
-        <v>RH - Programação de Férias</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D322" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E322" t="str">
         <v/>
       </c>
       <c r="F322" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G322" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H322" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I322" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="323">
@@ -9745,25 +9745,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C323" t="str">
-        <v>RH - Programação de Férias</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D323" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E323" t="str">
         <v/>
       </c>
       <c r="F323" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G323" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H323" t="str">
-        <v/>
+        <v>dpessoal</v>
       </c>
       <c r="I323" t="str">
-        <v>VW_D_FILIAL</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="324">
@@ -9774,25 +9774,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C324" t="str">
-        <v>RH - Programação de Férias</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D324" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E324" t="str">
         <v/>
       </c>
       <c r="F324" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G324" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H324" t="str">
-        <v/>
+        <v>portalbi</v>
       </c>
       <c r="I324" t="str">
-        <v>F_PROGRAMACAO_FERIAS</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="325">
@@ -9803,25 +9803,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C325" t="str">
-        <v>RH STEP Afastamento</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D325" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E325" t="str">
         <v/>
       </c>
       <c r="F325" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G325" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H325" t="str">
-        <v>bicompras</v>
+        <v>bisilver</v>
       </c>
       <c r="I325" t="str">
-        <v>d_filial</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="326">
@@ -9832,25 +9832,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C326" t="str">
-        <v>RH STEP Afastamento</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D326" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E326" t="str">
         <v/>
       </c>
       <c r="F326" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G326" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H326" t="str">
-        <v/>
+        <v>ciscorp</v>
       </c>
       <c r="I326" t="str">
-        <v>VW_APDATA_STEP_AFASTAMENTO</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="327">
@@ -9861,25 +9861,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C327" t="str">
-        <v>RH STEP Afastamento</v>
+        <v>RH - Programação de Férias</v>
       </c>
       <c r="D327" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E327" t="str">
         <v/>
       </c>
       <c r="F327" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G327" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H327" t="str">
-        <v>portalbi</v>
+        <v/>
       </c>
       <c r="I327" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="328">
@@ -9890,25 +9890,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C328" t="str">
-        <v>RH STEP Afastamento</v>
+        <v>RH - Programação de Férias</v>
       </c>
       <c r="D328" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E328" t="str">
         <v/>
       </c>
       <c r="F328" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G328" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H328" t="str">
-        <v>bicompras</v>
+        <v/>
       </c>
       <c r="I328" t="str">
-        <v>d_filial_complemento</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="329">
@@ -9919,25 +9919,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C329" t="str">
-        <v>RH STEP Afastamento</v>
+        <v>RH - Programação de Férias</v>
       </c>
       <c r="D329" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E329" t="str">
         <v/>
       </c>
       <c r="F329" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G329" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H329" t="str">
-        <v>ciscorp</v>
+        <v/>
       </c>
       <c r="I329" t="str">
-        <v>filial</v>
+        <v>VW_D_FILIAL</v>
       </c>
     </row>
     <row r="330">
@@ -9948,25 +9948,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C330" t="str">
-        <v>Base_Tableau</v>
+        <v>RH - Programação de Férias</v>
       </c>
       <c r="D330" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E330" t="str">
         <v/>
       </c>
       <c r="F330" t="str">
-        <v/>
+        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="G330" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H330" t="str">
         <v/>
       </c>
       <c r="I330" t="str">
-        <v>D_COLABORADOR</v>
+        <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
     <row r="331">
@@ -9977,25 +9977,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C331" t="str">
-        <v>Base_Tableau</v>
+        <v>RH STEP Afastamento</v>
       </c>
       <c r="D331" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E331" t="str">
         <v/>
       </c>
       <c r="F331" t="str">
-        <v/>
+        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
       </c>
       <c r="G331" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H331" t="str">
-        <v/>
+        <v>bicompras</v>
       </c>
       <c r="I331" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="332">
@@ -10006,25 +10006,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C332" t="str">
-        <v>Base_Tableau</v>
+        <v>RH STEP Afastamento</v>
       </c>
       <c r="D332" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E332" t="str">
         <v/>
       </c>
       <c r="F332" t="str">
-        <v/>
+        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
       </c>
       <c r="G332" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H332" t="str">
         <v/>
       </c>
       <c r="I332" t="str">
-        <v>F_PROGRAMACAO_FERIAS</v>
+        <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
     <row r="333">
@@ -10035,25 +10035,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C333" t="str">
-        <v>Base_Tableau</v>
+        <v>RH STEP Afastamento</v>
       </c>
       <c r="D333" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E333" t="str">
         <v/>
       </c>
       <c r="F333" t="str">
-        <v/>
+        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
       </c>
       <c r="G333" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H333" t="str">
-        <v/>
+        <v>portalbi</v>
       </c>
       <c r="I333" t="str">
-        <v>VW_APDATA_STEP_AFASTAMENTO</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="334">
@@ -10064,25 +10064,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C334" t="str">
-        <v>Base_Tableau</v>
+        <v>RH STEP Afastamento</v>
       </c>
       <c r="D334" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E334" t="str">
         <v/>
       </c>
       <c r="F334" t="str">
-        <v/>
+        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
       </c>
       <c r="G334" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H334" t="str">
-        <v/>
+        <v>bicompras</v>
       </c>
       <c r="I334" t="str">
-        <v>Base_Tableau</v>
+        <v>d_filial_complemento</v>
       </c>
     </row>
     <row r="335">
@@ -10093,25 +10093,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C335" t="str">
-        <v>Base_Tableau</v>
+        <v>RH STEP Afastamento</v>
       </c>
       <c r="D335" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E335" t="str">
         <v/>
       </c>
       <c r="F335" t="str">
-        <v/>
+        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
       </c>
       <c r="G335" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H335" t="str">
-        <v/>
+        <v>ciscorp</v>
       </c>
       <c r="I335" t="str">
-        <v>Plan1</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="336">
@@ -10122,19 +10122,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C336" t="str">
-        <v>reserva_mesas_por_colaborador geral</v>
+        <v>Base_Tableau</v>
       </c>
       <c r="D336" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E336" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F336" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G336" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H336" t="str">
         <v/>
@@ -10151,19 +10151,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C337" t="str">
-        <v>reserva_mesas_por_colaborador geral</v>
+        <v>Base_Tableau</v>
       </c>
       <c r="D337" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E337" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F337" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G337" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H337" t="str">
         <v/>
@@ -10180,19 +10180,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C338" t="str">
-        <v>reserva_mesas_por_colaborador geral</v>
+        <v>Base_Tableau</v>
       </c>
       <c r="D338" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E338" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F338" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G338" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H338" t="str">
         <v/>
@@ -10209,19 +10209,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C339" t="str">
-        <v>reserva_mesas_por_colaborador geral</v>
+        <v>Base_Tableau</v>
       </c>
       <c r="D339" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E339" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F339" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G339" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H339" t="str">
         <v/>
@@ -10238,19 +10238,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C340" t="str">
-        <v>reserva_mesas_por_colaborador geral</v>
+        <v>Base_Tableau</v>
       </c>
       <c r="D340" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E340" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F340" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G340" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H340" t="str">
         <v/>
@@ -10267,19 +10267,19 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C341" t="str">
-        <v>reserva_mesas_por_colaborador geral</v>
+        <v>Base_Tableau</v>
       </c>
       <c r="D341" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E341" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F341" t="str">
-        <v/>
+        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
       </c>
       <c r="G341" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H341" t="str">
         <v/>
@@ -10290,176 +10290,176 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Painel de Vagas Operacionais</v>
+        <v>Indicadores de Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B342" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C342" t="str">
-        <v>BIVARREDURA - Filial</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D342" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E342" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F342" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G342" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H342" t="str">
-        <v>PORTALBI</v>
+        <v/>
       </c>
       <c r="I342" t="str">
-        <v>filial_endereco</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Painel de Vagas Operacionais</v>
+        <v>Indicadores de Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B343" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C343" t="str">
-        <v>BIVARREDURA - Filial</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D343" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E343" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F343" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G343" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H343" t="str">
-        <v>PORTALBI</v>
+        <v/>
       </c>
       <c r="I343" t="str">
-        <v>filial_endereco@tecnisaw</v>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Painel de Vagas Operacionais</v>
+        <v>Indicadores de Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B344" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C344" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D344" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E344" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F344" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G344" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H344" t="str">
-        <v>bicompras</v>
+        <v/>
       </c>
       <c r="I344" t="str">
-        <v>d_filial</v>
+        <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Painel de Vagas Operacionais</v>
+        <v>Indicadores de Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B345" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C345" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D345" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E345" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F345" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G345" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H345" t="str">
-        <v>DPESSOAL</v>
+        <v/>
       </c>
       <c r="I345" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Painel de Vagas Operacionais</v>
+        <v>Indicadores de Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B346" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C346" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D346" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E346" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F346" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G346" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H346" t="str">
-        <v>DPESSOAL</v>
+        <v/>
       </c>
       <c r="I346" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>Base_Tableau</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Painel de Vagas Operacionais</v>
+        <v>Indicadores de Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B347" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C347" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D347" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E347" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F347" t="str">
-        <v/>
+        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
       <c r="G347" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H347" t="str">
-        <v>dpessoal</v>
+        <v/>
       </c>
       <c r="I347" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>Plan1</v>
       </c>
     </row>
     <row r="348">
@@ -10470,25 +10470,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
       </c>
       <c r="C348" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>BIVARREDURA - Filial</v>
       </c>
       <c r="D348" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage</v>
       </c>
       <c r="E348" t="str">
         <v/>
       </c>
       <c r="F348" t="str">
-        <v/>
+        <v>[END] Bairro; [END] CEP; [END] Cidade; [END] LATITUDE; [END] Logadouro; [END] LONGITUDE; [END] UF; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_BUSINESS_UNIT; Dados migrados (Count); Dt Abertura; Dt Encerramento; Fili Email; Fl Ficticia; Inscricaoestadual; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Diretor Operacional; Nm Diretoria; Nm Empresa Sodexo; Nm Filial; Nm Gerente Area; Nm Gerente Regional</v>
       </c>
       <c r="G348" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H348" t="str">
-        <v>portalbi</v>
+        <v>PORTALBI</v>
       </c>
       <c r="I348" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>filial_endereco</v>
       </c>
     </row>
     <row r="349">
@@ -10499,25 +10499,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
       </c>
       <c r="C349" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>BIVARREDURA - Filial</v>
       </c>
       <c r="D349" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage</v>
       </c>
       <c r="E349" t="str">
         <v/>
       </c>
       <c r="F349" t="str">
-        <v/>
+        <v>[END] Bairro; [END] CEP; [END] Cidade; [END] LATITUDE; [END] Logadouro; [END] LONGITUDE; [END] UF; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_BUSINESS_UNIT; Dados migrados (Count); Dt Abertura; Dt Encerramento; Fili Email; Fl Ficticia; Inscricaoestadual; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Diretor Operacional; Nm Diretoria; Nm Empresa Sodexo; Nm Filial; Nm Gerente Area; Nm Gerente Regional</v>
       </c>
       <c r="G349" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H349" t="str">
-        <v>bisilver</v>
+        <v>PORTALBI</v>
       </c>
       <c r="I349" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>filial_endereco@tecnisaw</v>
       </c>
     </row>
     <row r="350">
@@ -10537,16 +10537,16 @@
         <v/>
       </c>
       <c r="F350" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G350" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H350" t="str">
-        <v>ciscorp</v>
+        <v>bicompras</v>
       </c>
       <c r="I350" t="str">
-        <v>filial</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="351">
@@ -10557,25 +10557,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
       </c>
       <c r="C351" t="str">
-        <v>RH STEP Abertura de Vagas</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D351" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E351" t="str">
         <v/>
       </c>
       <c r="F351" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G351" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H351" t="str">
         <v>DPESSOAL</v>
       </c>
       <c r="I351" t="str">
-        <v>D_COLABORADOR</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="352">
@@ -10586,33 +10586,33 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
       </c>
       <c r="C352" t="str">
-        <v>RH STEP Abertura de Vagas</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D352" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E352" t="str">
         <v/>
       </c>
       <c r="F352" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G352" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H352" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I352" t="str">
-        <v>VW_APDATA_STEP_ABERTURA_VAGAS</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Pin People On e Off</v>
+        <v>Painel de Vagas Operacionais</v>
       </c>
       <c r="B353" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
       </c>
       <c r="C353" t="str">
         <v>RH - Colaborador Folha</v>
@@ -10624,24 +10624,24 @@
         <v/>
       </c>
       <c r="F353" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G353" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H353" t="str">
-        <v>bicompras</v>
+        <v>dpessoal</v>
       </c>
       <c r="I353" t="str">
-        <v>d_filial</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Pin People On e Off</v>
+        <v>Painel de Vagas Operacionais</v>
       </c>
       <c r="B354" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
       </c>
       <c r="C354" t="str">
         <v>RH - Colaborador Folha</v>
@@ -10653,24 +10653,24 @@
         <v/>
       </c>
       <c r="F354" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G354" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H354" t="str">
-        <v>DPESSOAL</v>
+        <v>portalbi</v>
       </c>
       <c r="I354" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Pin People On e Off</v>
+        <v>Painel de Vagas Operacionais</v>
       </c>
       <c r="B355" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
       </c>
       <c r="C355" t="str">
         <v>RH - Colaborador Folha</v>
@@ -10682,24 +10682,24 @@
         <v/>
       </c>
       <c r="F355" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G355" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H355" t="str">
-        <v>DPESSOAL</v>
+        <v>bisilver</v>
       </c>
       <c r="I355" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Pin People On e Off</v>
+        <v>Painel de Vagas Operacionais</v>
       </c>
       <c r="B356" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
       </c>
       <c r="C356" t="str">
         <v>RH - Colaborador Folha</v>
@@ -10711,74 +10711,74 @@
         <v/>
       </c>
       <c r="F356" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G356" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H356" t="str">
-        <v>dpessoal</v>
+        <v>ciscorp</v>
       </c>
       <c r="I356" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Pin People On e Off</v>
+        <v>Painel de Vagas Operacionais</v>
       </c>
       <c r="B357" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
       </c>
       <c r="C357" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH STEP Abertura de Vagas</v>
       </c>
       <c r="D357" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
       </c>
       <c r="E357" t="str">
         <v/>
       </c>
       <c r="F357" t="str">
-        <v/>
+        <v>CBO; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Portfolio; Cd Segmento; Cd Site; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_CARGO; CD_CARGO_HR_REPORTING; CD_CARGO_VAGA; CD_COTA_APRENDIZ_CBO; CD_ESTR_HIERAR; CD_ESTR_HIERAR_COLAB; CD_FILIAL_COLABORADOR; CD_FILIAL_VAGA; CD_FLEXIVEL_VAGA; CD_HORARIO; CD_SINDICATO; CD_SITUACAO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; CD_VAGA; CLASSIFICACAO_HR_REPORTING; COR_PELE; CPF; CTPS</v>
       </c>
       <c r="G357" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H357" t="str">
-        <v>portalbi</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="I357" t="str">
-        <v>filial_complemento@tecnisaw</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Pin People On e Off</v>
+        <v>Painel de Vagas Operacionais</v>
       </c>
       <c r="B358" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
       </c>
       <c r="C358" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH STEP Abertura de Vagas</v>
       </c>
       <c r="D358" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
       </c>
       <c r="E358" t="str">
         <v/>
       </c>
       <c r="F358" t="str">
-        <v/>
+        <v>CBO; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Portfolio; Cd Segmento; Cd Site; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_CARGO; CD_CARGO_HR_REPORTING; CD_CARGO_VAGA; CD_COTA_APRENDIZ_CBO; CD_ESTR_HIERAR; CD_ESTR_HIERAR_COLAB; CD_FILIAL_COLABORADOR; CD_FILIAL_VAGA; CD_FLEXIVEL_VAGA; CD_HORARIO; CD_SINDICATO; CD_SITUACAO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; CD_VAGA; CLASSIFICACAO_HR_REPORTING; COR_PELE; CPF; CTPS</v>
       </c>
       <c r="G358" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
       <c r="H358" t="str">
-        <v>bisilver</v>
+        <v/>
       </c>
       <c r="I358" t="str">
-        <v>vw_estrutra_gerencial</v>
+        <v>VW_APDATA_STEP_ABERTURA_VAGAS</v>
       </c>
     </row>
     <row r="359">
@@ -10789,7 +10789,7 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
       </c>
       <c r="C359" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D359" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
@@ -10798,16 +10798,16 @@
         <v/>
       </c>
       <c r="F359" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G359" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H359" t="str">
-        <v>ciscorp</v>
+        <v>bicompras</v>
       </c>
       <c r="I359" t="str">
-        <v>filial</v>
+        <v>d_filial</v>
       </c>
     </row>
     <row r="360">
@@ -10821,22 +10821,22 @@
         <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D360" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E360" t="str">
         <v/>
       </c>
       <c r="F360" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G360" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H360" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I360" t="str">
-        <v>D_COLABORADOR</v>
+        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
     <row r="361">
@@ -10850,22 +10850,22 @@
         <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D361" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E361" t="str">
         <v/>
       </c>
       <c r="F361" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G361" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H361" t="str">
-        <v/>
+        <v>DPESSOAL</v>
       </c>
       <c r="I361" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
     <row r="362">
@@ -10876,25 +10876,25 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
       </c>
       <c r="C362" t="str">
-        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D362" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E362" t="str">
         <v/>
       </c>
       <c r="F362" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G362" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H362" t="str">
-        <v/>
+        <v>dpessoal</v>
       </c>
       <c r="I362" t="str">
-        <v>D_COLABORADOR</v>
+        <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
     <row r="363">
@@ -10905,36 +10905,36 @@
         <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
       </c>
       <c r="C363" t="str">
-        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D363" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E363" t="str">
         <v/>
       </c>
       <c r="F363" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G363" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H363" t="str">
-        <v/>
+        <v>portalbi</v>
       </c>
       <c r="I363" t="str">
-        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
+        <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Women Leadership</v>
+        <v>Pin People On e Off</v>
       </c>
       <c r="B364" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
       </c>
       <c r="C364" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D364" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
@@ -10943,27 +10943,27 @@
         <v/>
       </c>
       <c r="F364" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G364" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H364" t="str">
-        <v>bicompras</v>
+        <v>bisilver</v>
       </c>
       <c r="I364" t="str">
-        <v>d_filial</v>
+        <v>vw_estrutra_gerencial</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Women Leadership</v>
+        <v>Pin People On e Off</v>
       </c>
       <c r="B365" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
       </c>
       <c r="C365" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa</v>
       </c>
       <c r="D365" t="str">
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
@@ -10972,195 +10972,79 @@
         <v/>
       </c>
       <c r="F365" t="str">
-        <v/>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="G365" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H365" t="str">
-        <v>DPESSOAL</v>
+        <v>ciscorp</v>
       </c>
       <c r="I365" t="str">
-        <v>F_APDATA_ABERTURA_VAGA_STEP</v>
+        <v>filial</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Women Leadership</v>
+        <v>Pin People On e Off</v>
       </c>
       <c r="B366" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
       </c>
       <c r="C366" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
       </c>
       <c r="D366" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
       </c>
       <c r="E366" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F366" t="str">
-        <v/>
+        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
       </c>
       <c r="G366" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H366" t="str">
-        <v>DPESSOAL</v>
+        <v/>
       </c>
       <c r="I366" t="str">
-        <v>VW_D_COLABORADOR_GRADE</v>
+        <v>D_COLABORADOR</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Women Leadership</v>
+        <v>Pin People On e Off</v>
       </c>
       <c r="B367" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
       </c>
       <c r="C367" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
       </c>
       <c r="D367" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
       </c>
       <c r="E367" t="str">
-        <v/>
+        <v>Planilha</v>
       </c>
       <c r="F367" t="str">
-        <v/>
+        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
       </c>
       <c r="G367" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
       <c r="H367" t="str">
-        <v>dpessoal</v>
+        <v/>
       </c>
       <c r="I367" t="str">
-        <v>F_COLABORADOR_FOLHA</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="str">
-        <v>Women Leadership</v>
-      </c>
-      <c r="B368" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
-      </c>
-      <c r="C368" t="str">
-        <v>RH - Colaborador Folha</v>
-      </c>
-      <c r="D368" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
-      </c>
-      <c r="E368" t="str">
-        <v/>
-      </c>
-      <c r="F368" t="str">
-        <v/>
-      </c>
-      <c r="G368" t="str">
-        <v/>
-      </c>
-      <c r="H368" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I368" t="str">
-        <v>filial_complemento@tecnisaw</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="str">
-        <v>Women Leadership</v>
-      </c>
-      <c r="B369" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
-      </c>
-      <c r="C369" t="str">
-        <v>RH - Colaborador Folha</v>
-      </c>
-      <c r="D369" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
-      </c>
-      <c r="E369" t="str">
-        <v/>
-      </c>
-      <c r="F369" t="str">
-        <v/>
-      </c>
-      <c r="G369" t="str">
-        <v/>
-      </c>
-      <c r="H369" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I369" t="str">
-        <v>vw_estrutra_gerencial</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="str">
-        <v>Women Leadership</v>
-      </c>
-      <c r="B370" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
-      </c>
-      <c r="C370" t="str">
-        <v>RH - Colaborador Folha</v>
-      </c>
-      <c r="D370" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
-      </c>
-      <c r="E370" t="str">
-        <v/>
-      </c>
-      <c r="F370" t="str">
-        <v/>
-      </c>
-      <c r="G370" t="str">
-        <v/>
-      </c>
-      <c r="H370" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I370" t="str">
-        <v>filial</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="str">
-        <v>Metas Turnover FY26 - Regrettable e Demissional</v>
-      </c>
-      <c r="B371" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY26-RegrettableeDemissional/MetasdeRHFY26</v>
-      </c>
-      <c r="C371" t="str">
-        <v/>
-      </c>
-      <c r="D371" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E371" t="str">
-        <v/>
-      </c>
-      <c r="F371" t="str">
-        <v/>
-      </c>
-      <c r="G371" t="str">
-        <v/>
-      </c>
-      <c r="H371" t="str">
-        <v/>
-      </c>
-      <c r="I371" t="str">
-        <v/>
+        <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I371"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I367"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/downloads/hr/output_automacao_hr.xlsx
+++ b/downloads/hr/output_automacao_hr.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="output_automacao" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabelas" sheetId="1" r:id="rId1"/>
+    <sheet name="Campos" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I367"/>
+  <dimension ref="A1:G367"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,7 +408,7 @@
         <v>link_relatorio</v>
       </c>
       <c r="C1" t="str">
-        <v>datasource</v>
+        <v>data_source</v>
       </c>
       <c r="D1" t="str">
         <v>link_datasource</v>
@@ -416,15 +417,9 @@
         <v>origem</v>
       </c>
       <c r="F1" t="str">
-        <v>campos</v>
+        <v>schema</v>
       </c>
       <c r="G1" t="str">
-        <v>tipo_campo</v>
-      </c>
-      <c r="H1" t="str">
-        <v>schema</v>
-      </c>
-      <c r="I1" t="str">
         <v>tabela</v>
       </c>
     </row>
@@ -442,18 +437,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F2" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G2" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H2" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I2" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -471,18 +460,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F3" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G3" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H3" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I3" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -500,18 +483,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F4" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G4" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H4" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I4" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -529,18 +506,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F5" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G5" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H5" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I5" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -558,18 +529,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F6" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G6" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H6" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I6" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -587,18 +552,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F7" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G7" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H7" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I7" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -616,18 +575,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F8" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G8" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H8" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I8" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -648,15 +601,9 @@
         <v>Planilha</v>
       </c>
       <c r="F9" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -677,15 +624,9 @@
         <v>Planilha</v>
       </c>
       <c r="F10" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -706,15 +647,9 @@
         <v>Planilha</v>
       </c>
       <c r="F11" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -735,15 +670,9 @@
         <v>Planilha</v>
       </c>
       <c r="F12" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -761,18 +690,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F13" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G13" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H13" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I13" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -790,18 +713,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F14" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G14" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H14" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I14" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -819,18 +736,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F15" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G15" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H15" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I15" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -848,18 +759,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F16" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G16" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H16" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I16" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -877,18 +782,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F17" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G17" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H17" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I17" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -906,18 +805,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F18" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G18" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H18" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I18" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -935,18 +828,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F19" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G19" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H19" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I19" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -967,15 +854,9 @@
         <v>Planilha</v>
       </c>
       <c r="F20" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -996,15 +877,9 @@
         <v>Planilha</v>
       </c>
       <c r="F21" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1025,15 +900,9 @@
         <v>Planilha</v>
       </c>
       <c r="F22" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1054,15 +923,9 @@
         <v>Planilha</v>
       </c>
       <c r="F23" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1083,15 +946,9 @@
         <v>Planilha</v>
       </c>
       <c r="F24" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1112,15 +969,9 @@
         <v>Planilha</v>
       </c>
       <c r="F25" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1141,15 +992,9 @@
         <v>Planilha</v>
       </c>
       <c r="F26" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G26" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1170,15 +1015,9 @@
         <v>Planilha</v>
       </c>
       <c r="F27" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G27" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1199,15 +1038,9 @@
         <v>Planilha</v>
       </c>
       <c r="F28" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G28" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1228,15 +1061,9 @@
         <v>Planilha</v>
       </c>
       <c r="F29" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G29" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -1254,18 +1081,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F30" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G30" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
-      <c r="I30" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -1283,18 +1104,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F31" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G31" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1312,18 +1127,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F32" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G32" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1341,18 +1150,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F33" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G33" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H33" t="str">
-        <v/>
-      </c>
-      <c r="I33" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1370,18 +1173,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F34" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G34" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
-      <c r="I34" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1399,18 +1196,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E35" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F35" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G35" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H35" t="str">
-        <v/>
-      </c>
-      <c r="I35" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1428,18 +1219,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E36" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F36" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G36" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H36" t="str">
-        <v/>
-      </c>
-      <c r="I36" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1457,18 +1242,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E37" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F37" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G37" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H37" t="str">
-        <v/>
-      </c>
-      <c r="I37" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1486,18 +1265,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E38" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F38" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G38" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H38" t="str">
-        <v/>
-      </c>
-      <c r="I38" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1515,18 +1288,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E39" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F39" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G39" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H39" t="str">
-        <v/>
-      </c>
-      <c r="I39" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -1547,15 +1314,9 @@
         <v>Planilha</v>
       </c>
       <c r="F40" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G40" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H40" t="str">
-        <v/>
-      </c>
-      <c r="I40" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -1576,15 +1337,9 @@
         <v>Planilha</v>
       </c>
       <c r="F41" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G41" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
-      <c r="I41" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1605,15 +1360,9 @@
         <v>Planilha</v>
       </c>
       <c r="F42" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G42" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H42" t="str">
-        <v/>
-      </c>
-      <c r="I42" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1634,15 +1383,9 @@
         <v>Planilha</v>
       </c>
       <c r="F43" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G43" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H43" t="str">
-        <v/>
-      </c>
-      <c r="I43" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1663,15 +1406,9 @@
         <v>Planilha</v>
       </c>
       <c r="F44" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G44" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H44" t="str">
-        <v/>
-      </c>
-      <c r="I44" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1692,15 +1429,9 @@
         <v>Planilha</v>
       </c>
       <c r="F45" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G45" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H45" t="str">
-        <v/>
-      </c>
-      <c r="I45" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1721,15 +1452,9 @@
         <v>Planilha</v>
       </c>
       <c r="F46" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G46" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H46" t="str">
-        <v/>
-      </c>
-      <c r="I46" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1750,15 +1475,9 @@
         <v>Planilha</v>
       </c>
       <c r="F47" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G47" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H47" t="str">
-        <v/>
-      </c>
-      <c r="I47" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1779,15 +1498,9 @@
         <v>Planilha</v>
       </c>
       <c r="F48" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G48" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H48" t="str">
-        <v/>
-      </c>
-      <c r="I48" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1808,15 +1521,9 @@
         <v>Planilha</v>
       </c>
       <c r="F49" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G49" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H49" t="str">
-        <v/>
-      </c>
-      <c r="I49" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -1837,15 +1544,9 @@
         <v>Planilha</v>
       </c>
       <c r="F50" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G50" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H50" t="str">
-        <v/>
-      </c>
-      <c r="I50" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -1866,15 +1567,9 @@
         <v>Planilha</v>
       </c>
       <c r="F51" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G51" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H51" t="str">
-        <v/>
-      </c>
-      <c r="I51" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1895,15 +1590,9 @@
         <v>Planilha</v>
       </c>
       <c r="F52" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G52" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H52" t="str">
-        <v/>
-      </c>
-      <c r="I52" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1924,15 +1613,9 @@
         <v>Planilha</v>
       </c>
       <c r="F53" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G53" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H53" t="str">
-        <v/>
-      </c>
-      <c r="I53" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1953,15 +1636,9 @@
         <v>Planilha</v>
       </c>
       <c r="F54" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G54" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H54" t="str">
-        <v/>
-      </c>
-      <c r="I54" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1982,15 +1659,9 @@
         <v>Planilha</v>
       </c>
       <c r="F55" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G55" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H55" t="str">
-        <v/>
-      </c>
-      <c r="I55" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -2011,15 +1682,9 @@
         <v>Planilha</v>
       </c>
       <c r="F56" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G56" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H56" t="str">
-        <v/>
-      </c>
-      <c r="I56" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -2040,15 +1705,9 @@
         <v>Planilha</v>
       </c>
       <c r="F57" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G57" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H57" t="str">
-        <v/>
-      </c>
-      <c r="I57" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -2069,15 +1728,9 @@
         <v>Planilha</v>
       </c>
       <c r="F58" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G58" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H58" t="str">
-        <v/>
-      </c>
-      <c r="I58" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -2098,15 +1751,9 @@
         <v>Planilha</v>
       </c>
       <c r="F59" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G59" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H59" t="str">
-        <v/>
-      </c>
-      <c r="I59" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -2127,15 +1774,9 @@
         <v>Planilha</v>
       </c>
       <c r="F60" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G60" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H60" t="str">
-        <v/>
-      </c>
-      <c r="I60" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -2156,15 +1797,9 @@
         <v>Planilha</v>
       </c>
       <c r="F61" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G61" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H61" t="str">
-        <v/>
-      </c>
-      <c r="I61" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2185,15 +1820,9 @@
         <v>Planilha</v>
       </c>
       <c r="F62" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G62" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H62" t="str">
-        <v/>
-      </c>
-      <c r="I62" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -2214,15 +1843,9 @@
         <v>Planilha</v>
       </c>
       <c r="F63" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G63" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H63" t="str">
-        <v/>
-      </c>
-      <c r="I63" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -2243,15 +1866,9 @@
         <v>Planilha</v>
       </c>
       <c r="F64" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G64" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H64" t="str">
-        <v/>
-      </c>
-      <c r="I64" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -2272,15 +1889,9 @@
         <v>Planilha</v>
       </c>
       <c r="F65" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G65" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H65" t="str">
-        <v/>
-      </c>
-      <c r="I65" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -2301,15 +1912,9 @@
         <v>Planilha</v>
       </c>
       <c r="F66" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G66" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H66" t="str">
-        <v/>
-      </c>
-      <c r="I66" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -2330,15 +1935,9 @@
         <v>Planilha</v>
       </c>
       <c r="F67" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G67" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H67" t="str">
-        <v/>
-      </c>
-      <c r="I67" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -2359,15 +1958,9 @@
         <v>Planilha</v>
       </c>
       <c r="F68" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G68" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H68" t="str">
-        <v/>
-      </c>
-      <c r="I68" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -2388,15 +1981,9 @@
         <v>Planilha</v>
       </c>
       <c r="F69" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G69" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H69" t="str">
-        <v/>
-      </c>
-      <c r="I69" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -2414,18 +2001,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E70" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F70" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G70" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H70" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I70" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -2443,18 +2024,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E71" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F71" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G71" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H71" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I71" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -2472,18 +2047,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E72" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F72" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G72" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H72" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I72" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -2501,18 +2070,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E73" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F73" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G73" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H73" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I73" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2530,18 +2093,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E74" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F74" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G74" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H74" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I74" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -2559,18 +2116,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E75" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F75" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G75" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H75" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I75" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -2588,18 +2139,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E76" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F76" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G76" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H76" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I76" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -2617,18 +2162,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E77" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F77" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G77" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H77" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I77" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -2646,18 +2185,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E78" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F78" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G78" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H78" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I78" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -2675,18 +2208,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E79" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F79" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G79" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H79" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I79" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -2704,18 +2231,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E80" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F80" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G80" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H80" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I80" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2733,18 +2254,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E81" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F81" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G81" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H81" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I81" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -2762,18 +2277,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E82" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F82" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G82" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H82" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I82" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -2791,18 +2300,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E83" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F83" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G83" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H83" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I83" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -2820,18 +2323,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage</v>
       </c>
       <c r="E84" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F84" t="str">
-        <v>Bairro; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Motivo Alteracao Grade; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; CEP; Cidade; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; Deficiencia; Dlg Dlsdesligamento</v>
+        <v>PORTALBI</v>
       </c>
       <c r="G84" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H84" t="str">
-        <v>PORTALBI</v>
-      </c>
-      <c r="I84" t="str">
         <v>FILIAL_COMPLEMENTO</v>
       </c>
     </row>
@@ -2849,18 +2346,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage</v>
       </c>
       <c r="E85" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F85" t="str">
-        <v>Bairro; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Motivo Alteracao Grade; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; CEP; Cidade; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; Deficiencia; Dlg Dlsdesligamento</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G85" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H85" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I85" t="str">
         <v>F_PROMOCAO</v>
       </c>
     </row>
@@ -2878,18 +2369,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage</v>
       </c>
       <c r="E86" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F86" t="str">
-        <v>Bairro; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Motivo Alteracao Grade; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; CEP; Cidade; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; Deficiencia; Dlg Dlsdesligamento</v>
+        <v>PORTALBI</v>
       </c>
       <c r="G86" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H86" t="str">
-        <v>PORTALBI</v>
-      </c>
-      <c r="I86" t="str">
         <v>FILIAL_COMPLEMENTO@TECNISAW</v>
       </c>
     </row>
@@ -2910,15 +2395,9 @@
         <v>Planilha</v>
       </c>
       <c r="F87" t="str">
-        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+        <v/>
       </c>
       <c r="G87" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H87" t="str">
-        <v/>
-      </c>
-      <c r="I87" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -2939,15 +2418,9 @@
         <v>Planilha</v>
       </c>
       <c r="F88" t="str">
-        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+        <v/>
       </c>
       <c r="G88" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H88" t="str">
-        <v/>
-      </c>
-      <c r="I88" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2968,15 +2441,9 @@
         <v>Planilha</v>
       </c>
       <c r="F89" t="str">
-        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+        <v/>
       </c>
       <c r="G89" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H89" t="str">
-        <v/>
-      </c>
-      <c r="I89" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -2997,15 +2464,9 @@
         <v>Planilha</v>
       </c>
       <c r="F90" t="str">
-        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+        <v/>
       </c>
       <c r="G90" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H90" t="str">
-        <v/>
-      </c>
-      <c r="I90" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -3026,15 +2487,9 @@
         <v>Planilha</v>
       </c>
       <c r="F91" t="str">
-        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+        <v/>
       </c>
       <c r="G91" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H91" t="str">
-        <v/>
-      </c>
-      <c r="I91" t="str">
         <v>F_PROMOCAO</v>
       </c>
     </row>
@@ -3052,18 +2507,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E92" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F92" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G92" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H92" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I92" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -3081,18 +2530,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E93" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F93" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G93" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H93" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I93" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -3110,18 +2553,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E94" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F94" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G94" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H94" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I94" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -3139,18 +2576,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E95" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F95" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G95" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H95" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I95" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3168,18 +2599,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E96" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F96" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G96" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H96" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I96" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -3197,18 +2622,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E97" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F97" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G97" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H97" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I97" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -3226,18 +2645,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E98" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F98" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G98" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H98" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I98" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -3255,18 +2668,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage</v>
       </c>
       <c r="E99" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F99" t="str">
-        <v>Cálculo1; Cálculo2; CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G99" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H99" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I99" t="str">
         <v>VW_EVT_RH_PONTO_ANALITICO</v>
       </c>
     </row>
@@ -3284,18 +2691,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage</v>
       </c>
       <c r="E100" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F100" t="str">
-        <v>Cálculo1; Cálculo2; CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G100" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H100" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I100" t="str">
         <v>D_USUARIO_FILIAL</v>
       </c>
     </row>
@@ -3313,18 +2714,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage</v>
       </c>
       <c r="E101" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F101" t="str">
-        <v>CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G101" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H101" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I101" t="str">
         <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
       </c>
     </row>
@@ -3342,18 +2737,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage</v>
       </c>
       <c r="E102" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F102" t="str">
-        <v>CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G102" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H102" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I102" t="str">
         <v>D_USUARIO_FILIAL</v>
       </c>
     </row>
@@ -3374,15 +2763,9 @@
         <v>Planilha</v>
       </c>
       <c r="F103" t="str">
-        <v>CL; Clbr; Onda; Planilha1 (Count)</v>
+        <v/>
       </c>
       <c r="G103" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H103" t="str">
-        <v/>
-      </c>
-      <c r="I103" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -3403,15 +2786,9 @@
         <v>Planilha</v>
       </c>
       <c r="F104" t="str">
-        <v>CL; Clbr; Onda; Planilha1 (Count)</v>
+        <v/>
       </c>
       <c r="G104" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H104" t="str">
-        <v/>
-      </c>
-      <c r="I104" t="str">
         <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
       </c>
     </row>
@@ -3432,15 +2809,9 @@
         <v>Planilha</v>
       </c>
       <c r="F105" t="str">
-        <v>CL; Clbr; Onda; Planilha1 (Count)</v>
+        <v/>
       </c>
       <c r="G105" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H105" t="str">
-        <v/>
-      </c>
-      <c r="I105" t="str">
         <v>VW_EVT_RH_PONTO_ANALITICO</v>
       </c>
     </row>
@@ -3458,18 +2829,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/17222/lineage</v>
       </c>
       <c r="E106" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F106" t="str">
-        <v>CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO</v>
+        <v/>
       </c>
       <c r="G106" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H106" t="str">
-        <v/>
-      </c>
-      <c r="I106" t="str">
         <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
       </c>
     </row>
@@ -3487,18 +2852,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E107" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F107" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G107" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H107" t="str">
-        <v/>
-      </c>
-      <c r="I107" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -3516,18 +2875,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E108" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F108" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G108" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H108" t="str">
-        <v/>
-      </c>
-      <c r="I108" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -3545,18 +2898,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E109" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F109" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G109" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H109" t="str">
-        <v/>
-      </c>
-      <c r="I109" t="str">
         <v>VW_D_FILIAL</v>
       </c>
     </row>
@@ -3574,18 +2921,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E110" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F110" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G110" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H110" t="str">
-        <v/>
-      </c>
-      <c r="I110" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -3603,18 +2944,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E111" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F111" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G111" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H111" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I111" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -3632,18 +2967,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E112" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F112" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G112" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H112" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I112" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -3661,18 +2990,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E113" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F113" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G113" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H113" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I113" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -3690,18 +3013,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E114" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F114" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G114" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H114" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I114" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3719,18 +3036,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E115" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F115" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G115" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H115" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I115" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -3748,18 +3059,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E116" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F116" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G116" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H116" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I116" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -3777,18 +3082,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E117" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F117" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G117" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H117" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I117" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -3806,18 +3105,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E118" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F118" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G118" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H118" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I118" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -3835,18 +3128,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E119" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F119" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G119" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H119" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I119" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -3864,18 +3151,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E120" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F120" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G120" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H120" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I120" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -3893,18 +3174,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E121" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F121" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G121" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H121" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I121" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3922,18 +3197,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E122" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F122" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G122" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H122" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I122" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -3951,18 +3220,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E123" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F123" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G123" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H123" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I123" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -3980,18 +3243,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E124" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F124" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G124" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H124" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I124" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -4009,18 +3266,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E125" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F125" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G125" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H125" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I125" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -4038,18 +3289,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E126" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F126" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G126" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H126" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I126" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -4067,18 +3312,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E127" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F127" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G127" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H127" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I127" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -4096,18 +3335,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E128" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F128" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G128" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H128" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I128" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -4125,18 +3358,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E129" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F129" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G129" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H129" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I129" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -4154,18 +3381,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E130" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F130" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G130" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H130" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I130" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -4183,18 +3404,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E131" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F131" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G131" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H131" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I131" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -4215,15 +3430,9 @@
         <v>Planilha</v>
       </c>
       <c r="F132" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G132" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H132" t="str">
-        <v/>
-      </c>
-      <c r="I132" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -4244,15 +3453,9 @@
         <v>Planilha</v>
       </c>
       <c r="F133" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G133" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H133" t="str">
-        <v/>
-      </c>
-      <c r="I133" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -4273,15 +3476,9 @@
         <v>Planilha</v>
       </c>
       <c r="F134" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G134" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H134" t="str">
-        <v/>
-      </c>
-      <c r="I134" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -4302,15 +3499,9 @@
         <v>Planilha</v>
       </c>
       <c r="F135" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G135" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H135" t="str">
-        <v/>
-      </c>
-      <c r="I135" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -4331,15 +3522,9 @@
         <v>Planilha</v>
       </c>
       <c r="F136" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G136" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H136" t="str">
-        <v/>
-      </c>
-      <c r="I136" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -4360,15 +3545,9 @@
         <v>Planilha</v>
       </c>
       <c r="F137" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G137" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H137" t="str">
-        <v/>
-      </c>
-      <c r="I137" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -4389,15 +3568,9 @@
         <v>Planilha</v>
       </c>
       <c r="F138" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G138" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H138" t="str">
-        <v/>
-      </c>
-      <c r="I138" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -4418,15 +3591,9 @@
         <v>Planilha</v>
       </c>
       <c r="F139" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G139" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H139" t="str">
-        <v/>
-      </c>
-      <c r="I139" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -4447,15 +3614,9 @@
         <v>Planilha</v>
       </c>
       <c r="F140" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G140" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H140" t="str">
-        <v/>
-      </c>
-      <c r="I140" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -4476,15 +3637,9 @@
         <v>Planilha</v>
       </c>
       <c r="F141" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G141" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H141" t="str">
-        <v/>
-      </c>
-      <c r="I141" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -4505,15 +3660,9 @@
         <v>Planilha</v>
       </c>
       <c r="F142" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G142" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H142" t="str">
-        <v/>
-      </c>
-      <c r="I142" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -4534,15 +3683,9 @@
         <v>Planilha</v>
       </c>
       <c r="F143" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G143" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H143" t="str">
-        <v/>
-      </c>
-      <c r="I143" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -4563,15 +3706,9 @@
         <v>Planilha</v>
       </c>
       <c r="F144" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G144" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H144" t="str">
-        <v/>
-      </c>
-      <c r="I144" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -4589,18 +3726,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E145" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F145" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G145" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H145" t="str">
-        <v/>
-      </c>
-      <c r="I145" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -4618,18 +3749,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E146" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F146" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G146" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H146" t="str">
-        <v/>
-      </c>
-      <c r="I146" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -4647,18 +3772,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E147" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F147" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G147" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H147" t="str">
-        <v/>
-      </c>
-      <c r="I147" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -4676,18 +3795,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E148" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F148" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G148" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H148" t="str">
-        <v/>
-      </c>
-      <c r="I148" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -4705,18 +3818,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E149" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F149" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G149" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H149" t="str">
-        <v/>
-      </c>
-      <c r="I149" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -4734,18 +3841,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E150" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F150" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G150" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H150" t="str">
-        <v/>
-      </c>
-      <c r="I150" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -4763,18 +3864,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E151" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F151" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G151" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H151" t="str">
-        <v/>
-      </c>
-      <c r="I151" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -4792,18 +3887,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E152" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F152" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G152" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H152" t="str">
-        <v/>
-      </c>
-      <c r="I152" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -4821,18 +3910,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E153" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F153" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G153" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H153" t="str">
-        <v/>
-      </c>
-      <c r="I153" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -4850,18 +3933,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E154" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F154" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G154" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H154" t="str">
-        <v/>
-      </c>
-      <c r="I154" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -4879,18 +3956,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E155" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F155" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G155" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H155" t="str">
-        <v/>
-      </c>
-      <c r="I155" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -4908,18 +3979,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E156" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F156" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G156" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H156" t="str">
-        <v/>
-      </c>
-      <c r="I156" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -4937,18 +4002,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E157" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F157" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G157" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H157" t="str">
-        <v/>
-      </c>
-      <c r="I157" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -4969,15 +4028,9 @@
         <v>Planilha</v>
       </c>
       <c r="F158" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G158" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H158" t="str">
-        <v/>
-      </c>
-      <c r="I158" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -4998,15 +4051,9 @@
         <v>Planilha</v>
       </c>
       <c r="F159" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G159" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H159" t="str">
-        <v/>
-      </c>
-      <c r="I159" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5027,15 +4074,9 @@
         <v>Planilha</v>
       </c>
       <c r="F160" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G160" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H160" t="str">
-        <v/>
-      </c>
-      <c r="I160" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5056,15 +4097,9 @@
         <v>Planilha</v>
       </c>
       <c r="F161" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G161" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H161" t="str">
-        <v/>
-      </c>
-      <c r="I161" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5085,15 +4120,9 @@
         <v>Planilha</v>
       </c>
       <c r="F162" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G162" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H162" t="str">
-        <v/>
-      </c>
-      <c r="I162" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -5114,15 +4143,9 @@
         <v>Planilha</v>
       </c>
       <c r="F163" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G163" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H163" t="str">
-        <v/>
-      </c>
-      <c r="I163" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -5143,15 +4166,9 @@
         <v>Planilha</v>
       </c>
       <c r="F164" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G164" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H164" t="str">
-        <v/>
-      </c>
-      <c r="I164" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -5172,15 +4189,9 @@
         <v>Planilha</v>
       </c>
       <c r="F165" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G165" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H165" t="str">
-        <v/>
-      </c>
-      <c r="I165" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -5201,15 +4212,9 @@
         <v>Planilha</v>
       </c>
       <c r="F166" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G166" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H166" t="str">
-        <v/>
-      </c>
-      <c r="I166" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -5230,15 +4235,9 @@
         <v>Planilha</v>
       </c>
       <c r="F167" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G167" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H167" t="str">
-        <v/>
-      </c>
-      <c r="I167" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -5259,15 +4258,9 @@
         <v>Planilha</v>
       </c>
       <c r="F168" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G168" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H168" t="str">
-        <v/>
-      </c>
-      <c r="I168" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -5288,15 +4281,9 @@
         <v>Planilha</v>
       </c>
       <c r="F169" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G169" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H169" t="str">
-        <v/>
-      </c>
-      <c r="I169" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -5317,15 +4304,9 @@
         <v>Planilha</v>
       </c>
       <c r="F170" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G170" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H170" t="str">
-        <v/>
-      </c>
-      <c r="I170" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -5346,15 +4327,9 @@
         <v>Planilha</v>
       </c>
       <c r="F171" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G171" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H171" t="str">
-        <v/>
-      </c>
-      <c r="I171" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5375,15 +4350,9 @@
         <v>Planilha</v>
       </c>
       <c r="F172" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G172" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H172" t="str">
-        <v/>
-      </c>
-      <c r="I172" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5404,15 +4373,9 @@
         <v>Planilha</v>
       </c>
       <c r="F173" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G173" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H173" t="str">
-        <v/>
-      </c>
-      <c r="I173" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5433,15 +4396,9 @@
         <v>Planilha</v>
       </c>
       <c r="F174" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G174" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H174" t="str">
-        <v/>
-      </c>
-      <c r="I174" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5462,15 +4419,9 @@
         <v>Planilha</v>
       </c>
       <c r="F175" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G175" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H175" t="str">
-        <v/>
-      </c>
-      <c r="I175" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -5491,15 +4442,9 @@
         <v>Planilha</v>
       </c>
       <c r="F176" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G176" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H176" t="str">
-        <v/>
-      </c>
-      <c r="I176" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -5520,15 +4465,9 @@
         <v>Planilha</v>
       </c>
       <c r="F177" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G177" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H177" t="str">
-        <v/>
-      </c>
-      <c r="I177" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -5549,15 +4488,9 @@
         <v>Planilha</v>
       </c>
       <c r="F178" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G178" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H178" t="str">
-        <v/>
-      </c>
-      <c r="I178" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -5578,15 +4511,9 @@
         <v>Planilha</v>
       </c>
       <c r="F179" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G179" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H179" t="str">
-        <v/>
-      </c>
-      <c r="I179" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -5607,15 +4534,9 @@
         <v>Planilha</v>
       </c>
       <c r="F180" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G180" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H180" t="str">
-        <v/>
-      </c>
-      <c r="I180" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -5636,15 +4557,9 @@
         <v>Planilha</v>
       </c>
       <c r="F181" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G181" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H181" t="str">
-        <v/>
-      </c>
-      <c r="I181" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -5665,15 +4580,9 @@
         <v>Planilha</v>
       </c>
       <c r="F182" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G182" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H182" t="str">
-        <v/>
-      </c>
-      <c r="I182" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -5694,15 +4603,9 @@
         <v>Planilha</v>
       </c>
       <c r="F183" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G183" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H183" t="str">
-        <v/>
-      </c>
-      <c r="I183" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -5723,15 +4626,9 @@
         <v>Planilha</v>
       </c>
       <c r="F184" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G184" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H184" t="str">
-        <v/>
-      </c>
-      <c r="I184" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5752,15 +4649,9 @@
         <v>Planilha</v>
       </c>
       <c r="F185" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G185" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H185" t="str">
-        <v/>
-      </c>
-      <c r="I185" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5781,15 +4672,9 @@
         <v>Planilha</v>
       </c>
       <c r="F186" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G186" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H186" t="str">
-        <v/>
-      </c>
-      <c r="I186" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5810,15 +4695,9 @@
         <v>Planilha</v>
       </c>
       <c r="F187" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G187" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H187" t="str">
-        <v/>
-      </c>
-      <c r="I187" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5839,15 +4718,9 @@
         <v>Planilha</v>
       </c>
       <c r="F188" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G188" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H188" t="str">
-        <v/>
-      </c>
-      <c r="I188" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -5868,15 +4741,9 @@
         <v>Planilha</v>
       </c>
       <c r="F189" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G189" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H189" t="str">
-        <v/>
-      </c>
-      <c r="I189" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -5897,15 +4764,9 @@
         <v>Planilha</v>
       </c>
       <c r="F190" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G190" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H190" t="str">
-        <v/>
-      </c>
-      <c r="I190" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -5926,15 +4787,9 @@
         <v>Planilha</v>
       </c>
       <c r="F191" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G191" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H191" t="str">
-        <v/>
-      </c>
-      <c r="I191" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -5955,15 +4810,9 @@
         <v>Planilha</v>
       </c>
       <c r="F192" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G192" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H192" t="str">
-        <v/>
-      </c>
-      <c r="I192" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -5984,15 +4833,9 @@
         <v>Planilha</v>
       </c>
       <c r="F193" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G193" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H193" t="str">
-        <v/>
-      </c>
-      <c r="I193" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -6013,15 +4856,9 @@
         <v>Planilha</v>
       </c>
       <c r="F194" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G194" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H194" t="str">
-        <v/>
-      </c>
-      <c r="I194" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -6042,15 +4879,9 @@
         <v>Planilha</v>
       </c>
       <c r="F195" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G195" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H195" t="str">
-        <v/>
-      </c>
-      <c r="I195" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -6071,15 +4902,9 @@
         <v>Planilha</v>
       </c>
       <c r="F196" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G196" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H196" t="str">
-        <v/>
-      </c>
-      <c r="I196" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -6105,12 +4930,6 @@
       <c r="G197" t="str">
         <v/>
       </c>
-      <c r="H197" t="str">
-        <v/>
-      </c>
-      <c r="I197" t="str">
-        <v/>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -6134,12 +4953,6 @@
       <c r="G198" t="str">
         <v/>
       </c>
-      <c r="H198" t="str">
-        <v/>
-      </c>
-      <c r="I198" t="str">
-        <v/>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -6155,18 +4968,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E199" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F199" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G199" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H199" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I199" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -6184,18 +4991,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E200" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F200" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G200" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H200" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I200" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -6213,18 +5014,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E201" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F201" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G201" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H201" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I201" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -6242,18 +5037,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E202" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F202" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G202" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H202" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I202" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6271,18 +5060,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E203" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F203" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G203" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H203" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I203" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -6300,18 +5083,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E204" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F204" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G204" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H204" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I204" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -6329,18 +5106,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E205" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F205" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G205" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H205" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I205" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -6361,15 +5132,9 @@
         <v>Planilha</v>
       </c>
       <c r="F206" t="str">
-        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
+        <v/>
       </c>
       <c r="G206" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H206" t="str">
-        <v/>
-      </c>
-      <c r="I206" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -6390,15 +5155,9 @@
         <v>Planilha</v>
       </c>
       <c r="F207" t="str">
-        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
+        <v/>
       </c>
       <c r="G207" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H207" t="str">
-        <v/>
-      </c>
-      <c r="I207" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6419,15 +5178,9 @@
         <v>Planilha</v>
       </c>
       <c r="F208" t="str">
-        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
+        <v/>
       </c>
       <c r="G208" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H208" t="str">
-        <v/>
-      </c>
-      <c r="I208" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -6448,15 +5201,9 @@
         <v>Planilha</v>
       </c>
       <c r="F209" t="str">
-        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
+        <v/>
       </c>
       <c r="G209" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H209" t="str">
-        <v/>
-      </c>
-      <c r="I209" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -6477,15 +5224,9 @@
         <v>Planilha</v>
       </c>
       <c r="F210" t="str">
-        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
+        <v/>
       </c>
       <c r="G210" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H210" t="str">
-        <v/>
-      </c>
-      <c r="I210" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -6506,15 +5247,9 @@
         <v>Planilha</v>
       </c>
       <c r="F211" t="str">
-        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
+        <v/>
       </c>
       <c r="G211" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H211" t="str">
-        <v/>
-      </c>
-      <c r="I211" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -6535,15 +5270,9 @@
         <v>Planilha</v>
       </c>
       <c r="F212" t="str">
-        <v>CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento</v>
+        <v/>
       </c>
       <c r="G212" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H212" t="str">
-        <v/>
-      </c>
-      <c r="I212" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -6564,15 +5293,9 @@
         <v>Planilha</v>
       </c>
       <c r="F213" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G213" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H213" t="str">
-        <v/>
-      </c>
-      <c r="I213" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -6593,15 +5316,9 @@
         <v>Planilha</v>
       </c>
       <c r="F214" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G214" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H214" t="str">
-        <v/>
-      </c>
-      <c r="I214" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6622,15 +5339,9 @@
         <v>Planilha</v>
       </c>
       <c r="F215" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G215" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H215" t="str">
-        <v/>
-      </c>
-      <c r="I215" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -6651,15 +5362,9 @@
         <v>Planilha</v>
       </c>
       <c r="F216" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G216" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H216" t="str">
-        <v/>
-      </c>
-      <c r="I216" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -6680,15 +5385,9 @@
         <v>Planilha</v>
       </c>
       <c r="F217" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G217" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H217" t="str">
-        <v/>
-      </c>
-      <c r="I217" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -6709,15 +5408,9 @@
         <v>Planilha</v>
       </c>
       <c r="F218" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G218" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H218" t="str">
-        <v/>
-      </c>
-      <c r="I218" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -6738,15 +5431,9 @@
         <v>Planilha</v>
       </c>
       <c r="F219" t="str">
-        <v>Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G219" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H219" t="str">
-        <v/>
-      </c>
-      <c r="I219" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -6764,18 +5451,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E220" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F220" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G220" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H220" t="str">
-        <v/>
-      </c>
-      <c r="I220" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -6793,18 +5474,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E221" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F221" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G221" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H221" t="str">
-        <v/>
-      </c>
-      <c r="I221" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6822,18 +5497,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E222" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F222" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G222" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H222" t="str">
-        <v/>
-      </c>
-      <c r="I222" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -6851,18 +5520,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E223" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F223" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G223" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H223" t="str">
-        <v/>
-      </c>
-      <c r="I223" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -6880,18 +5543,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E224" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F224" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G224" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H224" t="str">
-        <v/>
-      </c>
-      <c r="I224" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -6909,18 +5566,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E225" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F225" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G225" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H225" t="str">
-        <v/>
-      </c>
-      <c r="I225" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -6938,18 +5589,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E226" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F226" t="str">
-        <v>Expurgo Pedido Demissao; Extract (Count); Matricula</v>
+        <v/>
       </c>
       <c r="G226" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H226" t="str">
-        <v/>
-      </c>
-      <c r="I226" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -6970,15 +5615,9 @@
         <v>Planilha</v>
       </c>
       <c r="F227" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G227" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H227" t="str">
-        <v/>
-      </c>
-      <c r="I227" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -6999,15 +5638,9 @@
         <v>Planilha</v>
       </c>
       <c r="F228" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G228" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H228" t="str">
-        <v/>
-      </c>
-      <c r="I228" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -7028,15 +5661,9 @@
         <v>Planilha</v>
       </c>
       <c r="F229" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G229" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H229" t="str">
-        <v/>
-      </c>
-      <c r="I229" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -7057,15 +5684,9 @@
         <v>Planilha</v>
       </c>
       <c r="F230" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G230" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H230" t="str">
-        <v/>
-      </c>
-      <c r="I230" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -7086,15 +5707,9 @@
         <v>Planilha</v>
       </c>
       <c r="F231" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G231" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H231" t="str">
-        <v/>
-      </c>
-      <c r="I231" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -7115,15 +5730,9 @@
         <v>Planilha</v>
       </c>
       <c r="F232" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G232" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H232" t="str">
-        <v/>
-      </c>
-      <c r="I232" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -7144,15 +5753,9 @@
         <v>Planilha</v>
       </c>
       <c r="F233" t="str">
-        <v>Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras</v>
+        <v/>
       </c>
       <c r="G233" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H233" t="str">
-        <v/>
-      </c>
-      <c r="I233" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -7173,15 +5776,9 @@
         <v>Planilha</v>
       </c>
       <c r="F234" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G234" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H234" t="str">
-        <v/>
-      </c>
-      <c r="I234" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7202,15 +5799,9 @@
         <v>Planilha</v>
       </c>
       <c r="F235" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G235" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H235" t="str">
-        <v/>
-      </c>
-      <c r="I235" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -7231,15 +5822,9 @@
         <v>Planilha</v>
       </c>
       <c r="F236" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G236" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H236" t="str">
-        <v/>
-      </c>
-      <c r="I236" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -7260,15 +5845,9 @@
         <v>Planilha</v>
       </c>
       <c r="F237" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G237" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H237" t="str">
-        <v/>
-      </c>
-      <c r="I237" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -7289,15 +5868,9 @@
         <v>Planilha</v>
       </c>
       <c r="F238" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G238" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H238" t="str">
-        <v/>
-      </c>
-      <c r="I238" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -7318,15 +5891,9 @@
         <v>Planilha</v>
       </c>
       <c r="F239" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G239" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H239" t="str">
-        <v/>
-      </c>
-      <c r="I239" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -7347,15 +5914,9 @@
         <v>Planilha</v>
       </c>
       <c r="F240" t="str">
-        <v>:Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); Segmento; TARGET; Total; TRANSVERSAL; Women Leardership (Count)</v>
+        <v/>
       </c>
       <c r="G240" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H240" t="str">
-        <v/>
-      </c>
-      <c r="I240" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -7376,15 +5937,9 @@
         <v>Planilha</v>
       </c>
       <c r="F241" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G241" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H241" t="str">
-        <v/>
-      </c>
-      <c r="I241" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7405,15 +5960,9 @@
         <v>Planilha</v>
       </c>
       <c r="F242" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G242" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H242" t="str">
-        <v/>
-      </c>
-      <c r="I242" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -7434,15 +5983,9 @@
         <v>Planilha</v>
       </c>
       <c r="F243" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G243" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H243" t="str">
-        <v/>
-      </c>
-      <c r="I243" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -7463,15 +6006,9 @@
         <v>Planilha</v>
       </c>
       <c r="F244" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G244" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H244" t="str">
-        <v/>
-      </c>
-      <c r="I244" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -7492,15 +6029,9 @@
         <v>Planilha</v>
       </c>
       <c r="F245" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G245" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H245" t="str">
-        <v/>
-      </c>
-      <c r="I245" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -7521,15 +6052,9 @@
         <v>Planilha</v>
       </c>
       <c r="F246" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G246" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H246" t="str">
-        <v/>
-      </c>
-      <c r="I246" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -7550,15 +6075,9 @@
         <v>Planilha</v>
       </c>
       <c r="F247" t="str">
-        <v>:Measure Names; Dt Competencia; Promocoes; Promoções_Internas (Count); Segmento</v>
+        <v/>
       </c>
       <c r="G247" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H247" t="str">
-        <v/>
-      </c>
-      <c r="I247" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -7576,18 +6095,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E248" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F248" t="str">
-        <v>Ano; Ano Fiscal; Data; Dia; Dia da Semana; Dia da Semana ID; Extract (Count); Fiscal Year; Mês; Mês Abr; Mês Fiscal; Mês ID; Mês/Ano; Mês/Ano ID; Período Fiscal ID; Período/FY; Período/FY ID; Semana do Ano; Semana do Ano ID; Semana Fiscal do Ano; Semana Fiscal do Ano ID; Semana Fiscal/Ano ID; Semana/Ano; Semana/Ano ID; Semestre Fiscal / Ano ID; Semestre Fiscal do Ano; Semestre ID; Trimestre Fiscal; Trimestre Fiscal/Ano; Trimestre Fiscal/Ano ID</v>
+        <v/>
       </c>
       <c r="G248" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H248" t="str">
-        <v/>
-      </c>
-      <c r="I248" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -7605,18 +6118,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E249" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F249" t="str">
-        <v>Assunto; Atribuído ao Usuário; Criador; Data de Conclusão Alvo; Data de Criação; Data Referência; Em nome de; Equipe Atribuída; Extract (Count); Fila Atribuída; Fonte; Horas SLA; ID do caso; ID do Caso Relacionado; Prioridade; Solicitado por; Status do caso; Subtópico de RH; Tema de RH</v>
+        <v/>
       </c>
       <c r="G249" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H249" t="str">
-        <v/>
-      </c>
-      <c r="I249" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -7634,18 +6141,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E250" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F250" t="str">
-        <v>% No Prazo; :Measure Names; Ano Fiscal; Assunto; Atingiu a Meta; Atribuído ao Usuário; Criador; Data de Conclusão Alvo; Data de Conclusão Alvo Ajustada; Data de Criação; Data de reabertura; Data Referência Resolução; Data/Hora da Primeira Resposta; Data/Hora Resolvida; Dia da Semana Criação; Em nome de; Equipe Atribuída; Extract (Count); Fila Atribuída (Subequipe); Fonte; Horas SLA; ID do Caso Relacionado; Meta; Número do chamado; Período Fiscal; Prioridade; Qtde Em Atraso; Qtde No Prazo; Reabertos; Solicitado por; Status do chamado; Status Prazo Primeiro Atendimento; Subtópico de RH; Tema de RH; Tempo de Resolução do Caso (Dias Úteis); Tempo de Trabalho em Dias Úteis; Tempo de trabalho em horas úteis (até agora); Total Atendimentos</v>
+        <v/>
       </c>
       <c r="G250" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H250" t="str">
-        <v/>
-      </c>
-      <c r="I250" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -7663,18 +6164,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E251" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F251" t="str">
-        <v>Data da Etapa; Data prazo atendimento; Data Referencia; Data/hora início da transação; Dentro do prazo?; Equipe; Etapa de Workflow; Extract (Count); Feriado; Formulário de Workflow; Id etapa de workflow; Id Formulário de Workflow; Id Lançamento de Workflow; Nome do Usuário; Referência; Solicitante; Subequipe</v>
+        <v/>
       </c>
       <c r="G251" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H251" t="str">
-        <v/>
-      </c>
-      <c r="I251" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -7692,18 +6187,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E252" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F252" t="str">
-        <v>% Dentro do Prazo; :Measure Names; Ano Fiscal; Atendido Em; Categoria Dia Entrada Wf; Categoria Dia Prazo Atend; Data Prazo Atendimento; Data Prazo Atendimento 2; Data Referencia; Data Rescisão; Dentro Prazo?; Efetivado?; Entrada Wf; Entrada Wf 2; Equipe; Etapa Destino; Etapa Origem; Etapa Wf - Destino; Etapa Wf - Origem; Extract (Count); Formulário Wf; Grupo Usuário; Id Formulário Wf; Id Grupo Usuário; Id Log Transação Wf; Id Workflow; Meta WFs; Nome Usuário; Novo Status Dentro Prazo; Período Fiscal; Prazo Atendimento 1º Dia Útil Próximo Mês; Prazo Atendimento Exceto Abertura Fim De Mês; Qtde Dentro do Prazo; Qtde Fora do Prazo; Status da Meta; Subequipe; Superior Hierárquico; Tempo Atendim Horas Uteis; Tempo Atendimento Hr; Total Atendimentos</v>
+        <v/>
       </c>
       <c r="G252" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H252" t="str">
-        <v/>
-      </c>
-      <c r="I252" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -7721,18 +6210,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E253" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F253" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G253" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H253" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I253" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -7750,18 +6233,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E254" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F254" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G254" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H254" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I254" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -7779,18 +6256,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E255" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F255" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G255" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H255" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I255" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -7808,18 +6279,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E256" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F256" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G256" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H256" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I256" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -7837,18 +6302,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E257" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F257" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G257" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H257" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I257" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -7866,18 +6325,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E258" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F258" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G258" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H258" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I258" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -7895,18 +6348,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E259" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F259" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G259" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H259" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I259" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -7927,15 +6374,9 @@
         <v>Planilha</v>
       </c>
       <c r="F260" t="str">
-        <v>Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G260" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H260" t="str">
-        <v/>
-      </c>
-      <c r="I260" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7956,15 +6397,9 @@
         <v>Planilha</v>
       </c>
       <c r="F261" t="str">
-        <v>Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G261" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H261" t="str">
-        <v/>
-      </c>
-      <c r="I261" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -7985,15 +6420,9 @@
         <v>Planilha</v>
       </c>
       <c r="F262" t="str">
-        <v>Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G262" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H262" t="str">
-        <v/>
-      </c>
-      <c r="I262" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -8014,15 +6443,9 @@
         <v>Planilha</v>
       </c>
       <c r="F263" t="str">
-        <v>Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+        <v/>
       </c>
       <c r="G263" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H263" t="str">
-        <v/>
-      </c>
-      <c r="I263" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -8043,15 +6466,9 @@
         <v>Planilha</v>
       </c>
       <c r="F264" t="str">
-        <v>Matrícula; PCD (Count); Qtd. Pcd</v>
+        <v/>
       </c>
       <c r="G264" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H264" t="str">
-        <v/>
-      </c>
-      <c r="I264" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -8072,15 +6489,9 @@
         <v>Planilha</v>
       </c>
       <c r="F265" t="str">
-        <v>Matrícula; PCD (Count); Qtd. Pcd</v>
+        <v/>
       </c>
       <c r="G265" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H265" t="str">
-        <v/>
-      </c>
-      <c r="I265" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -8101,15 +6512,9 @@
         <v>Planilha</v>
       </c>
       <c r="F266" t="str">
-        <v>Matrícula; PCD (Count); Qtd. Pcd</v>
+        <v/>
       </c>
       <c r="G266" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H266" t="str">
-        <v/>
-      </c>
-      <c r="I266" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -8130,15 +6535,9 @@
         <v>Planilha</v>
       </c>
       <c r="F267" t="str">
-        <v>Matrícula; PCD (Count); Qtd. Pcd</v>
+        <v/>
       </c>
       <c r="G267" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H267" t="str">
-        <v/>
-      </c>
-      <c r="I267" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -8156,18 +6555,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/52187/lineage</v>
       </c>
       <c r="E268" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F268" t="str">
-        <v>Admissão; Cargo; CL; Colaborador; Cpf; Dados gerados em; Diretoria; Dt Competencia; Dt inic cargo atual; Dt nasc; Gênero; Gestor; Grade; HR Reporting; Matrícula; Munic. cl; Nome do cl; Portfolio; Posição Faixa; Região cl; Segmento; Situação; Tipo cl; Uf cl; Zona posicionamento</v>
+        <v/>
       </c>
       <c r="G268" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H268" t="str">
-        <v/>
-      </c>
-      <c r="I268" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -8185,18 +6578,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E269" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F269" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G269" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H269" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I269" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -8214,18 +6601,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E270" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F270" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G270" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H270" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I270" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -8243,18 +6624,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E271" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F271" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G271" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H271" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I271" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -8272,18 +6647,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E272" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F272" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G272" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H272" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I272" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -8301,18 +6670,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E273" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F273" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G273" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H273" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I273" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -8330,18 +6693,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E274" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F274" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G274" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H274" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I274" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -8359,18 +6716,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E275" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F275" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G275" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H275" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I275" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -8388,18 +6739,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E276" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F276" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G276" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H276" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I276" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -8417,18 +6762,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E277" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F277" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G277" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H277" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I277" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -8446,18 +6785,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E278" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F278" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G278" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H278" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I278" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -8475,18 +6808,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E279" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F279" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G279" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H279" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I279" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -8504,18 +6831,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E280" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F280" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G280" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H280" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I280" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -8533,18 +6854,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E281" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F281" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G281" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H281" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I281" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -8562,18 +6877,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E282" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F282" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G282" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H282" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I282" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -8591,18 +6900,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E283" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F283" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G283" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H283" t="str">
-        <v/>
-      </c>
-      <c r="I283" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -8620,18 +6923,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E284" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F284" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G284" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H284" t="str">
-        <v/>
-      </c>
-      <c r="I284" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -8649,18 +6946,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E285" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F285" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G285" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H285" t="str">
-        <v/>
-      </c>
-      <c r="I285" t="str">
         <v>VW_D_FILIAL</v>
       </c>
     </row>
@@ -8678,18 +6969,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E286" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F286" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G286" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H286" t="str">
-        <v/>
-      </c>
-      <c r="I286" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -8707,18 +6992,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E287" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F287" t="str">
-        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
+        <v>bicompras</v>
       </c>
       <c r="G287" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H287" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I287" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -8736,18 +7015,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E288" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F288" t="str">
-        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
+        <v/>
       </c>
       <c r="G288" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H288" t="str">
-        <v/>
-      </c>
-      <c r="I288" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -8765,18 +7038,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E289" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F289" t="str">
-        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
+        <v>portalbi</v>
       </c>
       <c r="G289" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H289" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I289" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -8794,18 +7061,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E290" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F290" t="str">
-        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
+        <v>bicompras</v>
       </c>
       <c r="G290" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H290" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I290" t="str">
         <v>d_filial_complemento</v>
       </c>
     </row>
@@ -8823,18 +7084,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E291" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F291" t="str">
-        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
+        <v>ciscorp</v>
       </c>
       <c r="G291" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H291" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I291" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -8855,15 +7110,9 @@
         <v>Planilha</v>
       </c>
       <c r="F292" t="str">
-        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
+        <v/>
       </c>
       <c r="G292" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H292" t="str">
-        <v/>
-      </c>
-      <c r="I292" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -8884,15 +7133,9 @@
         <v>Planilha</v>
       </c>
       <c r="F293" t="str">
-        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
+        <v/>
       </c>
       <c r="G293" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H293" t="str">
-        <v/>
-      </c>
-      <c r="I293" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -8913,15 +7156,9 @@
         <v>Planilha</v>
       </c>
       <c r="F294" t="str">
-        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
+        <v/>
       </c>
       <c r="G294" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H294" t="str">
-        <v/>
-      </c>
-      <c r="I294" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -8942,15 +7179,9 @@
         <v>Planilha</v>
       </c>
       <c r="F295" t="str">
-        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
+        <v/>
       </c>
       <c r="G295" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H295" t="str">
-        <v/>
-      </c>
-      <c r="I295" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -8971,15 +7202,9 @@
         <v>Planilha</v>
       </c>
       <c r="F296" t="str">
-        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
+        <v/>
       </c>
       <c r="G296" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H296" t="str">
-        <v/>
-      </c>
-      <c r="I296" t="str">
         <v>Planilha1</v>
       </c>
     </row>
@@ -9000,15 +7225,9 @@
         <v>Planilha</v>
       </c>
       <c r="F297" t="str">
-        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
+        <v/>
       </c>
       <c r="G297" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H297" t="str">
-        <v/>
-      </c>
-      <c r="I297" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -9029,15 +7248,9 @@
         <v>Planilha</v>
       </c>
       <c r="F298" t="str">
-        <v>Competencia; CPF; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos</v>
+        <v/>
       </c>
       <c r="G298" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H298" t="str">
-        <v/>
-      </c>
-      <c r="I298" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -9058,15 +7271,9 @@
         <v>Planilha</v>
       </c>
       <c r="F299" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G299" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H299" t="str">
-        <v/>
-      </c>
-      <c r="I299" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -9087,15 +7294,9 @@
         <v>Planilha</v>
       </c>
       <c r="F300" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G300" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H300" t="str">
-        <v/>
-      </c>
-      <c r="I300" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -9116,15 +7317,9 @@
         <v>Planilha</v>
       </c>
       <c r="F301" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G301" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H301" t="str">
-        <v/>
-      </c>
-      <c r="I301" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -9145,15 +7340,9 @@
         <v>Planilha</v>
       </c>
       <c r="F302" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G302" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H302" t="str">
-        <v/>
-      </c>
-      <c r="I302" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -9174,15 +7363,9 @@
         <v>Planilha</v>
       </c>
       <c r="F303" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G303" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H303" t="str">
-        <v/>
-      </c>
-      <c r="I303" t="str">
         <v>Planilha1</v>
       </c>
     </row>
@@ -9203,15 +7386,9 @@
         <v>Planilha</v>
       </c>
       <c r="F304" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G304" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H304" t="str">
-        <v/>
-      </c>
-      <c r="I304" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -9232,15 +7409,9 @@
         <v>Planilha</v>
       </c>
       <c r="F305" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G305" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H305" t="str">
-        <v/>
-      </c>
-      <c r="I305" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -9261,15 +7432,9 @@
         <v>Planilha</v>
       </c>
       <c r="F306" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G306" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H306" t="str">
-        <v/>
-      </c>
-      <c r="I306" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -9290,15 +7455,9 @@
         <v>Planilha</v>
       </c>
       <c r="F307" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G307" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H307" t="str">
-        <v/>
-      </c>
-      <c r="I307" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -9319,15 +7478,9 @@
         <v>Planilha</v>
       </c>
       <c r="F308" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G308" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H308" t="str">
-        <v/>
-      </c>
-      <c r="I308" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -9348,15 +7501,9 @@
         <v>Planilha</v>
       </c>
       <c r="F309" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G309" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H309" t="str">
-        <v/>
-      </c>
-      <c r="I309" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -9377,15 +7524,9 @@
         <v>Planilha</v>
       </c>
       <c r="F310" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G310" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H310" t="str">
-        <v/>
-      </c>
-      <c r="I310" t="str">
         <v>Planilha1</v>
       </c>
     </row>
@@ -9406,15 +7547,9 @@
         <v>Planilha</v>
       </c>
       <c r="F311" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G311" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H311" t="str">
-        <v/>
-      </c>
-      <c r="I311" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -9435,15 +7570,9 @@
         <v>Planilha</v>
       </c>
       <c r="F312" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; CPF; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G312" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H312" t="str">
-        <v/>
-      </c>
-      <c r="I312" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -9461,18 +7590,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E313" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F313" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G313" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H313" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I313" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -9490,18 +7613,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E314" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F314" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G314" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H314" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I314" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -9519,18 +7636,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E315" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F315" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G315" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H315" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I315" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -9548,18 +7659,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E316" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F316" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G316" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H316" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I316" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -9577,18 +7682,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E317" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F317" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G317" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H317" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I317" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -9606,18 +7705,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E318" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F318" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G318" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H318" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I318" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -9635,18 +7728,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E319" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F319" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G319" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H319" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I319" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -9664,18 +7751,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E320" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F320" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G320" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H320" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I320" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -9693,18 +7774,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E321" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F321" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G321" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H321" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I321" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -9722,18 +7797,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E322" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F322" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G322" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H322" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I322" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -9751,18 +7820,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E323" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F323" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G323" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H323" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I323" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -9780,18 +7843,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E324" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F324" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G324" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H324" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I324" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -9809,18 +7866,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E325" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F325" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G325" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H325" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I325" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -9838,18 +7889,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E326" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F326" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G326" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H326" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I326" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -9867,18 +7912,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E327" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F327" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G327" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H327" t="str">
-        <v/>
-      </c>
-      <c r="I327" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -9896,18 +7935,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E328" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F328" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G328" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H328" t="str">
-        <v/>
-      </c>
-      <c r="I328" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -9925,18 +7958,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E329" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F329" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G329" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H329" t="str">
-        <v/>
-      </c>
-      <c r="I329" t="str">
         <v>VW_D_FILIAL</v>
       </c>
     </row>
@@ -9954,18 +7981,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E330" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F330" t="str">
-        <v>Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v/>
       </c>
       <c r="G330" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H330" t="str">
-        <v/>
-      </c>
-      <c r="I330" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -9983,18 +8004,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E331" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F331" t="str">
-        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
+        <v>bicompras</v>
       </c>
       <c r="G331" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H331" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I331" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -10012,18 +8027,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E332" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F332" t="str">
-        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
+        <v/>
       </c>
       <c r="G332" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H332" t="str">
-        <v/>
-      </c>
-      <c r="I332" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -10041,18 +8050,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E333" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F333" t="str">
-        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
+        <v>portalbi</v>
       </c>
       <c r="G333" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H333" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I333" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -10070,18 +8073,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E334" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F334" t="str">
-        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
+        <v>bicompras</v>
       </c>
       <c r="G334" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H334" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I334" t="str">
         <v>d_filial_complemento</v>
       </c>
     </row>
@@ -10099,18 +8096,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E335" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F335" t="str">
-        <v>AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Bairro; CBO; Cd Business Unit; Cd Cargo; Cd Cargo Hr Reporting; Cd Contrato; Cd Cota Aprendiz Cbo; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação</v>
+        <v>ciscorp</v>
       </c>
       <c r="G335" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H335" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I335" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -10131,15 +8122,9 @@
         <v>Planilha</v>
       </c>
       <c r="F336" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G336" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H336" t="str">
-        <v/>
-      </c>
-      <c r="I336" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -10160,15 +8145,9 @@
         <v>Planilha</v>
       </c>
       <c r="F337" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G337" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H337" t="str">
-        <v/>
-      </c>
-      <c r="I337" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -10189,15 +8168,9 @@
         <v>Planilha</v>
       </c>
       <c r="F338" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G338" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H338" t="str">
-        <v/>
-      </c>
-      <c r="I338" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -10218,15 +8191,9 @@
         <v>Planilha</v>
       </c>
       <c r="F339" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G339" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H339" t="str">
-        <v/>
-      </c>
-      <c r="I339" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -10247,15 +8214,9 @@
         <v>Planilha</v>
       </c>
       <c r="F340" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G340" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H340" t="str">
-        <v/>
-      </c>
-      <c r="I340" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -10276,15 +8237,9 @@
         <v>Planilha</v>
       </c>
       <c r="F341" t="str">
-        <v>% Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Cd Filial; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade</v>
+        <v/>
       </c>
       <c r="G341" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H341" t="str">
-        <v/>
-      </c>
-      <c r="I341" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -10305,15 +8260,9 @@
         <v>Planilha</v>
       </c>
       <c r="F342" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G342" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H342" t="str">
-        <v/>
-      </c>
-      <c r="I342" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -10334,15 +8283,9 @@
         <v>Planilha</v>
       </c>
       <c r="F343" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G343" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H343" t="str">
-        <v/>
-      </c>
-      <c r="I343" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -10363,15 +8306,9 @@
         <v>Planilha</v>
       </c>
       <c r="F344" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G344" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H344" t="str">
-        <v/>
-      </c>
-      <c r="I344" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -10392,15 +8329,9 @@
         <v>Planilha</v>
       </c>
       <c r="F345" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G345" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H345" t="str">
-        <v/>
-      </c>
-      <c r="I345" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -10421,15 +8352,9 @@
         <v>Planilha</v>
       </c>
       <c r="F346" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G346" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H346" t="str">
-        <v/>
-      </c>
-      <c r="I346" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -10450,15 +8375,9 @@
         <v>Planilha</v>
       </c>
       <c r="F347" t="str">
-        <v>Analise Qt Check-in; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Matricula; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Colaboradores; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v/>
       </c>
       <c r="G347" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H347" t="str">
-        <v/>
-      </c>
-      <c r="I347" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -10476,18 +8395,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage</v>
       </c>
       <c r="E348" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F348" t="str">
-        <v>[END] Bairro; [END] CEP; [END] Cidade; [END] LATITUDE; [END] Logadouro; [END] LONGITUDE; [END] UF; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_BUSINESS_UNIT; Dados migrados (Count); Dt Abertura; Dt Encerramento; Fili Email; Fl Ficticia; Inscricaoestadual; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Diretor Operacional; Nm Diretoria; Nm Empresa Sodexo; Nm Filial; Nm Gerente Area; Nm Gerente Regional</v>
+        <v>PORTALBI</v>
       </c>
       <c r="G348" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H348" t="str">
-        <v>PORTALBI</v>
-      </c>
-      <c r="I348" t="str">
         <v>filial_endereco</v>
       </c>
     </row>
@@ -10505,18 +8418,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage</v>
       </c>
       <c r="E349" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F349" t="str">
-        <v>[END] Bairro; [END] CEP; [END] Cidade; [END] LATITUDE; [END] Logadouro; [END] LONGITUDE; [END] UF; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_BUSINESS_UNIT; Dados migrados (Count); Dt Abertura; Dt Encerramento; Fili Email; Fl Ficticia; Inscricaoestadual; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Diretor Operacional; Nm Diretoria; Nm Empresa Sodexo; Nm Filial; Nm Gerente Area; Nm Gerente Regional</v>
+        <v>PORTALBI</v>
       </c>
       <c r="G349" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H349" t="str">
-        <v>PORTALBI</v>
-      </c>
-      <c r="I349" t="str">
         <v>filial_endereco@tecnisaw</v>
       </c>
     </row>
@@ -10534,18 +8441,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E350" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F350" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G350" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H350" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I350" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -10563,18 +8464,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E351" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F351" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G351" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H351" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I351" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -10592,18 +8487,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E352" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F352" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G352" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H352" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I352" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -10621,18 +8510,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E353" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F353" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G353" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H353" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I353" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -10650,18 +8533,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E354" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F354" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G354" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H354" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I354" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -10679,18 +8556,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E355" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F355" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G355" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H355" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I355" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -10708,18 +8579,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E356" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F356" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G356" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H356" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I356" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -10737,18 +8602,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
       </c>
       <c r="E357" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F357" t="str">
-        <v>CBO; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Portfolio; Cd Segmento; Cd Site; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_CARGO; CD_CARGO_HR_REPORTING; CD_CARGO_VAGA; CD_COTA_APRENDIZ_CBO; CD_ESTR_HIERAR; CD_ESTR_HIERAR_COLAB; CD_FILIAL_COLABORADOR; CD_FILIAL_VAGA; CD_FLEXIVEL_VAGA; CD_HORARIO; CD_SINDICATO; CD_SITUACAO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; CD_VAGA; CLASSIFICACAO_HR_REPORTING; COR_PELE; CPF; CTPS</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G357" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H357" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I357" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -10766,18 +8625,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
       </c>
       <c r="E358" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F358" t="str">
-        <v>CBO; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Portfolio; Cd Segmento; Cd Site; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_CARGO; CD_CARGO_HR_REPORTING; CD_CARGO_VAGA; CD_COTA_APRENDIZ_CBO; CD_ESTR_HIERAR; CD_ESTR_HIERAR_COLAB; CD_FILIAL_COLABORADOR; CD_FILIAL_VAGA; CD_FLEXIVEL_VAGA; CD_HORARIO; CD_SINDICATO; CD_SITUACAO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; CD_VAGA; CLASSIFICACAO_HR_REPORTING; COR_PELE; CPF; CTPS</v>
+        <v/>
       </c>
       <c r="G358" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-      <c r="H358" t="str">
-        <v/>
-      </c>
-      <c r="I358" t="str">
         <v>VW_APDATA_STEP_ABERTURA_VAGAS</v>
       </c>
     </row>
@@ -10795,18 +8648,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E359" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F359" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bicompras</v>
       </c>
       <c r="G359" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H359" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="I359" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -10824,18 +8671,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E360" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F360" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G360" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H360" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I360" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -10853,18 +8694,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E361" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F361" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="G361" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H361" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="I361" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -10882,18 +8717,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E362" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F362" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>dpessoal</v>
       </c>
       <c r="G362" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H362" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="I362" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -10911,18 +8740,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E363" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F363" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>portalbi</v>
       </c>
       <c r="G363" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H363" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="I363" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -10940,18 +8763,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E364" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F364" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>bisilver</v>
       </c>
       <c r="G364" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H364" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="I364" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -10969,18 +8786,12 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E365" t="str">
-        <v/>
+        <v>Oracle DW</v>
       </c>
       <c r="F365" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>ciscorp</v>
       </c>
       <c r="G365" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H365" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="I365" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -11001,15 +8812,9 @@
         <v>Planilha</v>
       </c>
       <c r="F366" t="str">
-        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+        <v/>
       </c>
       <c r="G366" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H366" t="str">
-        <v/>
-      </c>
-      <c r="I366" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -11030,21 +8835,466 @@
         <v>Planilha</v>
       </c>
       <c r="F367" t="str">
-        <v>Cargo de Confiança; Categoria; CBO; Cd Cargo; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+        <v/>
       </c>
       <c r="G367" t="str">
-        <v>Campo Calculado</v>
-      </c>
-      <c r="H367" t="str">
-        <v/>
-      </c>
-      <c r="I367" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I367"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G367"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F22"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>relatorio</v>
+      </c>
+      <c r="B1" t="str">
+        <v>link_relatorio</v>
+      </c>
+      <c r="C1" t="str">
+        <v>data_source</v>
+      </c>
+      <c r="D1" t="str">
+        <v>link_datasource</v>
+      </c>
+      <c r="E1" t="str">
+        <v>campos</v>
+      </c>
+      <c r="F1" t="str">
+        <v>tipo_campo</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Horas Extras e Absenteísmo</v>
+      </c>
+      <c r="B2" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/HorasExtraseAbsentesmo/AnalticoHorasExtras</v>
+      </c>
+      <c r="C2" t="str">
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1057/lineage</v>
+      </c>
+      <c r="E2" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Indicadores RH</v>
+      </c>
+      <c r="B3" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresRH_16860832510040/IndicadoresdeRH</v>
+      </c>
+      <c r="C3" t="str">
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+      </c>
+      <c r="D3" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
+      </c>
+      <c r="E3" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Base Colaboradores Geral</v>
+      </c>
+      <c r="B4" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basecolaboradoresgeral/Basecolaboradores</v>
+      </c>
+      <c r="C4" t="str">
+        <v>RH - Colaborador Folha</v>
+      </c>
+      <c r="D4" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+      </c>
+      <c r="E4" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Indicadores DE&amp;I</v>
+      </c>
+      <c r="B5" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
+      </c>
+      <c r="C5" t="str">
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; RH - Promoção; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+      </c>
+      <c r="D5" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
+      </c>
+      <c r="E5" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Motivo Alteracao Grade; CEP; Cidade; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; Deficiencia; Dlg Dlsdesligamento; Cargo de Confiança; Categoria; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Book de Indicadores de Pessoas</v>
+      </c>
+      <c r="B6" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
+      </c>
+      <c r="C6" t="str">
+        <v>RH - Colaborador Folha</v>
+      </c>
+      <c r="D6" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+      </c>
+      <c r="E6" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
+      </c>
+      <c r="B7" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
+      </c>
+      <c r="C7" t="str">
+        <v>RH - Colaborador Ponto Analitico RLS V2; RH - Colaborador Ponto Sintetico RLS; Ondas_Projeto_Ponto</v>
+      </c>
+      <c r="D7" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage; https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Cálculo1; Cálculo2; CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO; CL; Clbr; Onda; Planilha1 (Count)</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Base de Férias em Aberto</v>
+      </c>
+      <c r="B8" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
+      </c>
+      <c r="C8" t="str">
+        <v>RH - Colaborador Ponto Sintetico; RH - Programação de Férias</v>
+      </c>
+      <c r="D8" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/17222/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+      </c>
+      <c r="E8" t="str">
+        <v>CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Modelo de Trabalho</v>
+      </c>
+      <c r="B9" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
+      </c>
+      <c r="C9" t="str">
+        <v>RH - Colaborador Folha</v>
+      </c>
+      <c r="D9" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+      </c>
+      <c r="E9" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Banco de Horas</v>
+      </c>
+      <c r="B10" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
+      </c>
+      <c r="C10" t="str">
+        <v>RH - Colaborador Folha</v>
+      </c>
+      <c r="D10" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+      </c>
+      <c r="E10" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
+      </c>
+      <c r="B11" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
+      </c>
+      <c r="C11" t="str">
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+      </c>
+      <c r="D11" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
+      </c>
+      <c r="E11" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Metas Turnover FY26 - Regrettable e Demissional</v>
+      </c>
+      <c r="B12" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY26-RegrettableeDemissional/MetasdeRHFY26</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Women Leadership</v>
+      </c>
+      <c r="B13" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Wokforce Planning</v>
+      </c>
+      <c r="B14" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
+      </c>
+      <c r="C14" t="str">
+        <v>RH - Colaborador Folha; DE-PARA_BU; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+      </c>
+      <c r="D14" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
+      </c>
+      <c r="E14" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; FY; METAS (Count); Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Indicadores de Chamados e Workflows</v>
+      </c>
+      <c r="B15" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
+      </c>
+      <c r="C15" t="str">
+        <v>dCalendario; fChamadosEmAberto; fChamadosResolvidos; fWorkflowsEmAberto; fWorkflowsResolvidos</v>
+      </c>
+      <c r="D15" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Ano; Ano Fiscal; Data; Dia; Dia da Semana; Dia da Semana ID; Extract (Count); Fiscal Year; Mês; Mês Abr; Mês Fiscal; Mês ID; Mês/Ano; Mês/Ano ID; Período Fiscal ID; Período/FY; Período/FY ID; Semana do Ano; Semana do Ano ID; Semana Fiscal do Ano; Semana Fiscal do Ano ID; Semana Fiscal/Ano ID; Semana/Ano; Semana/Ano ID; Semestre Fiscal / Ano ID; Semestre Fiscal do Ano; Semestre ID; Trimestre Fiscal; Trimestre Fiscal/Ano; Trimestre Fiscal/Ano ID; Assunto; Atribuído ao Usuário; Criador; Data de Conclusão Alvo; Data de Criação; Data Referência; Em nome de; Equipe Atribuída; Fila Atribuída; Fonte; Horas SLA; ID do caso; ID do Caso Relacionado; Prioridade; Solicitado por; Status do caso; Subtópico de RH; Tema de RH; % No Prazo; :Measure Names; Atingiu a Meta; Data de Conclusão Alvo Ajustada; Data de reabertura; Data Referência Resolução; Data/Hora da Primeira Resposta; Data/Hora Resolvida; Dia da Semana Criação; Fila Atribuída (Subequipe); Meta; Número do chamado; Período Fiscal; Qtde Em Atraso; Qtde No Prazo; Reabertos; Status do chamado; Status Prazo Primeiro Atendimento; Tempo de Resolução do Caso (Dias Úteis); Tempo de Trabalho em Dias Úteis; Tempo de trabalho em horas úteis (até agora); Total Atendimentos; Data da Etapa; Data prazo atendimento; Data Referencia; Data/hora início da transação; Dentro do prazo?; Equipe; Etapa de Workflow; Feriado; Formulário de Workflow; Id etapa de workflow; Id Formulário de Workflow; Id Lançamento de Workflow; Nome do Usuário; Referência; Solicitante; Subequipe; % Dentro do Prazo; Atendido Em; Categoria Dia Entrada Wf; Categoria Dia Prazo Atend; Data Prazo Atendimento 2; Data Rescisão; Dentro Prazo?; Efetivado?; Entrada Wf; Entrada Wf 2; Etapa Destino; Etapa Origem; Etapa Wf - Destino; Etapa Wf - Origem; Formulário Wf; Grupo Usuário; Id Formulário Wf; Id Grupo Usuário; Id Log Transação Wf; Id Workflow; Meta WFs; Nome Usuário; Novo Status Dentro Prazo; Prazo Atendimento 1º Dia Útil Próximo Mês; Prazo Atendimento Exceto Abertura Fim De Mês; Qtde Dentro do Prazo; Qtde Fora do Prazo; Status da Meta; Superior Hierárquico; Tempo Atendim Horas Uteis; Tempo Atendimento Hr</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Visão consolidada</v>
+      </c>
+      <c r="B16" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
+      </c>
+      <c r="C16" t="str">
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); PCD (Tableau)</v>
+      </c>
+      <c r="D16" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
+      </c>
+      <c r="E16" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula; PCD (Count); Qtd. Pcd</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Zona Posicionamento Salarial</v>
+      </c>
+      <c r="B17" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
+      </c>
+      <c r="C17" t="str">
+        <v>RH - Base_Enios_Tableau; RH - Colaborador Folha</v>
+      </c>
+      <c r="D17" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/52187/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Admissão; Cargo; CL; Colaborador; Cpf; Dados gerados em; Diretoria; Dt Competencia; Dt inic cargo atual; Dt nasc; Gênero; Gestor; Grade; HR Reporting; Matrícula; Munic. cl; Nome do cl; Portfolio; Posição Faixa; Região cl; Segmento; Situação; Tipo cl; Uf cl; Zona posicionamento; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
+      </c>
+      <c r="B18" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
+      </c>
+      <c r="C18" t="str">
+        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Catracas; Base_Tableau; reserva_mesas_por_colaborador geral</v>
+      </c>
+      <c r="D18" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
+      </c>
+      <c r="E18" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Cardapio; Cd Centro Custo; Cd Empresa Sodexo; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Status; Cd Tipo Atuacao; Cd Tipo Servico; Cd Uf; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Competencia; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos; % Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Mesa; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Indicadores de Promoções Internas</v>
+      </c>
+      <c r="B19" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
+      </c>
+      <c r="C19" t="str">
+        <v>RH - Colaborador Folha</v>
+      </c>
+      <c r="D19" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+      </c>
+      <c r="E19" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Indicadores de Modelo de Trabalho - Home Office</v>
+      </c>
+      <c r="B20" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
+      </c>
+      <c r="C20" t="str">
+        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Tableau; reserva_mesas_por_colaborador geral</v>
+      </c>
+      <c r="D20" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
+      </c>
+      <c r="E20" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Cardapio; Cd Centro Custo; Cd Empresa Sodexo; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Status; Cd Tipo Atuacao; Cd Tipo Servico; Cd Uf; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; % Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Painel de Vagas Operacionais</v>
+      </c>
+      <c r="B21" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
+      </c>
+      <c r="C21" t="str">
+        <v>BIVARREDURA - Filial; RH - Colaborador Folha; RH STEP Abertura de Vagas</v>
+      </c>
+      <c r="D21" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
+      </c>
+      <c r="E21" t="str">
+        <v>[END] Bairro; [END] CEP; [END] Cidade; [END] LATITUDE; [END] Logadouro; [END] LONGITUDE; [END] UF; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_BUSINESS_UNIT; Dados migrados (Count); Dt Abertura; Dt Encerramento; Fili Email; Fl Ficticia; Inscricaoestadual; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Diretor Operacional; Nm Diretoria; Nm Empresa Sodexo; Nm Filial; Nm Gerente Area; Nm Gerente Regional; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial Colaborador; Cd Grupo CL; Cd Matriz Cardapio; Cd Matriz Compras; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Portfolio; CD_CARGO; CD_CARGO_HR_REPORTING; CD_CARGO_VAGA; CD_COTA_APRENDIZ_CBO; CD_ESTR_HIERAR; CD_ESTR_HIERAR_COLAB; CD_FILIAL_COLABORADOR; CD_FILIAL_VAGA; CD_FLEXIVEL_VAGA; CD_SINDICATO; CD_SITUACAO; CD_VAGA; CLASSIFICACAO_HR_REPORTING; COR_PELE; CPF; CTPS</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Pin People On e Off</v>
+      </c>
+      <c r="B22" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
+      </c>
+      <c r="C22" t="str">
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+      </c>
+      <c r="D22" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
+      </c>
+      <c r="E22" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cargo de Confiança; Categoria; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/downloads/hr/output_automacao_hr.xlsx
+++ b/downloads/hr/output_automacao_hr.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G367"/>
+  <dimension ref="A1:F367"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,12 +414,9 @@
         <v>link_datasource</v>
       </c>
       <c r="E1" t="str">
-        <v>origem</v>
+        <v>schema</v>
       </c>
       <c r="F1" t="str">
-        <v>schema</v>
-      </c>
-      <c r="G1" t="str">
         <v>tabela</v>
       </c>
     </row>
@@ -437,12 +434,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E2" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F2" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G2" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -460,12 +454,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E3" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F3" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G3" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -483,12 +474,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E4" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F4" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G4" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -506,12 +494,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E5" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F5" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G5" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -529,12 +514,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E6" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F6" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G6" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -552,12 +534,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E7" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F7" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G7" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -575,12 +554,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E8" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F8" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G8" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -598,12 +574,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1057/lineage</v>
       </c>
       <c r="E9" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -621,12 +594,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1057/lineage</v>
       </c>
       <c r="E10" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -644,12 +614,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1057/lineage</v>
       </c>
       <c r="E11" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -667,12 +634,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1057/lineage</v>
       </c>
       <c r="E12" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -690,12 +654,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E13" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F13" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G13" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -713,12 +674,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E14" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F14" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G14" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -736,12 +694,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E15" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F15" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G15" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -759,12 +714,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E16" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F16" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G16" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -782,12 +734,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E17" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F17" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G17" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -805,12 +754,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E18" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F18" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G18" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -828,12 +774,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E19" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F19" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G19" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -851,12 +794,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E20" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -874,12 +814,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E21" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -897,12 +834,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E22" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v/>
-      </c>
-      <c r="G22" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -920,12 +854,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E23" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -943,12 +874,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E24" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -966,12 +894,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E25" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -989,12 +914,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E26" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1012,12 +934,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E27" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F27" t="str">
-        <v/>
-      </c>
-      <c r="G27" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1035,12 +954,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E28" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F28" t="str">
-        <v/>
-      </c>
-      <c r="G28" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1058,12 +974,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E29" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F29" t="str">
-        <v/>
-      </c>
-      <c r="G29" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -1081,12 +994,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E30" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -1104,12 +1014,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E31" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F31" t="str">
-        <v/>
-      </c>
-      <c r="G31" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1127,12 +1034,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E32" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F32" t="str">
-        <v/>
-      </c>
-      <c r="G32" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1150,12 +1054,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E33" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F33" t="str">
-        <v/>
-      </c>
-      <c r="G33" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1173,12 +1074,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E34" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F34" t="str">
-        <v/>
-      </c>
-      <c r="G34" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1196,12 +1094,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E35" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F35" t="str">
-        <v/>
-      </c>
-      <c r="G35" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1219,12 +1114,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E36" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F36" t="str">
-        <v/>
-      </c>
-      <c r="G36" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1242,12 +1134,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E37" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F37" t="str">
-        <v/>
-      </c>
-      <c r="G37" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1265,12 +1154,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E38" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F38" t="str">
-        <v/>
-      </c>
-      <c r="G38" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1288,12 +1174,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E39" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F39" t="str">
-        <v/>
-      </c>
-      <c r="G39" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -1311,12 +1194,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E40" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F40" t="str">
-        <v/>
-      </c>
-      <c r="G40" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -1334,12 +1214,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E41" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F41" t="str">
-        <v/>
-      </c>
-      <c r="G41" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1357,12 +1234,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E42" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F42" t="str">
-        <v/>
-      </c>
-      <c r="G42" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1380,12 +1254,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E43" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F43" t="str">
-        <v/>
-      </c>
-      <c r="G43" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1403,12 +1274,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E44" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F44" t="str">
-        <v/>
-      </c>
-      <c r="G44" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1426,12 +1294,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E45" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F45" t="str">
-        <v/>
-      </c>
-      <c r="G45" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1449,12 +1314,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E46" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F46" t="str">
-        <v/>
-      </c>
-      <c r="G46" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1472,12 +1334,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E47" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F47" t="str">
-        <v/>
-      </c>
-      <c r="G47" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1495,12 +1354,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E48" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F48" t="str">
-        <v/>
-      </c>
-      <c r="G48" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1518,12 +1374,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E49" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F49" t="str">
-        <v/>
-      </c>
-      <c r="G49" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -1541,12 +1394,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E50" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F50" t="str">
-        <v/>
-      </c>
-      <c r="G50" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -1564,12 +1414,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E51" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F51" t="str">
-        <v/>
-      </c>
-      <c r="G51" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1587,12 +1434,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E52" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F52" t="str">
-        <v/>
-      </c>
-      <c r="G52" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1610,12 +1454,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E53" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F53" t="str">
-        <v/>
-      </c>
-      <c r="G53" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1633,12 +1474,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E54" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F54" t="str">
-        <v/>
-      </c>
-      <c r="G54" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1656,12 +1494,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E55" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F55" t="str">
-        <v/>
-      </c>
-      <c r="G55" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1679,12 +1514,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E56" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F56" t="str">
-        <v/>
-      </c>
-      <c r="G56" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1702,12 +1534,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E57" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F57" t="str">
-        <v/>
-      </c>
-      <c r="G57" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1725,12 +1554,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E58" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F58" t="str">
-        <v/>
-      </c>
-      <c r="G58" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1748,12 +1574,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E59" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F59" t="str">
-        <v/>
-      </c>
-      <c r="G59" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -1771,12 +1594,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E60" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F60" t="str">
-        <v/>
-      </c>
-      <c r="G60" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -1794,12 +1614,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E61" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F61" t="str">
-        <v/>
-      </c>
-      <c r="G61" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -1817,12 +1634,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E62" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F62" t="str">
-        <v/>
-      </c>
-      <c r="G62" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -1840,12 +1654,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E63" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F63" t="str">
-        <v/>
-      </c>
-      <c r="G63" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -1863,12 +1674,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E64" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F64" t="str">
-        <v/>
-      </c>
-      <c r="G64" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -1886,12 +1694,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E65" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F65" t="str">
-        <v/>
-      </c>
-      <c r="G65" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -1909,12 +1714,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E66" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F66" t="str">
-        <v/>
-      </c>
-      <c r="G66" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -1932,12 +1734,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E67" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F67" t="str">
-        <v/>
-      </c>
-      <c r="G67" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -1955,12 +1754,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E68" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F68" t="str">
-        <v/>
-      </c>
-      <c r="G68" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -1978,12 +1774,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E69" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F69" t="str">
-        <v/>
-      </c>
-      <c r="G69" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -2001,12 +1794,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E70" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F70" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G70" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -2024,12 +1814,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E71" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F71" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G71" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -2047,12 +1834,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E72" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F72" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G72" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -2070,12 +1854,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E73" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F73" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G73" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2093,12 +1874,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E74" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F74" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G74" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -2116,12 +1894,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E75" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F75" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G75" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -2139,12 +1914,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E76" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F76" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G76" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -2162,12 +1934,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E77" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F77" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G77" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -2185,12 +1954,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E78" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F78" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G78" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -2208,12 +1974,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E79" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F79" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G79" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -2231,12 +1994,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E80" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F80" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G80" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2254,12 +2014,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E81" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F81" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G81" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -2277,12 +2034,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E82" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F82" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G82" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -2300,12 +2054,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E83" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F83" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G83" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -2323,12 +2074,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage</v>
       </c>
       <c r="E84" t="str">
-        <v>Oracle DW</v>
+        <v>PORTALBI</v>
       </c>
       <c r="F84" t="str">
-        <v>PORTALBI</v>
-      </c>
-      <c r="G84" t="str">
         <v>FILIAL_COMPLEMENTO</v>
       </c>
     </row>
@@ -2346,12 +2094,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage</v>
       </c>
       <c r="E85" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F85" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G85" t="str">
         <v>F_PROMOCAO</v>
       </c>
     </row>
@@ -2369,12 +2114,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage</v>
       </c>
       <c r="E86" t="str">
-        <v>Oracle DW</v>
+        <v>PORTALBI</v>
       </c>
       <c r="F86" t="str">
-        <v>PORTALBI</v>
-      </c>
-      <c r="G86" t="str">
         <v>FILIAL_COMPLEMENTO@TECNISAW</v>
       </c>
     </row>
@@ -2392,12 +2134,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E87" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F87" t="str">
-        <v/>
-      </c>
-      <c r="G87" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -2415,12 +2154,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E88" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F88" t="str">
-        <v/>
-      </c>
-      <c r="G88" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2438,12 +2174,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E89" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F89" t="str">
-        <v/>
-      </c>
-      <c r="G89" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -2461,12 +2194,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E90" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F90" t="str">
-        <v/>
-      </c>
-      <c r="G90" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -2484,12 +2214,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E91" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F91" t="str">
-        <v/>
-      </c>
-      <c r="G91" t="str">
         <v>F_PROMOCAO</v>
       </c>
     </row>
@@ -2507,12 +2234,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E92" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F92" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G92" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -2530,12 +2254,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E93" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F93" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G93" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -2553,12 +2274,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E94" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F94" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G94" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -2576,12 +2294,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E95" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F95" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G95" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -2599,12 +2314,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E96" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F96" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G96" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -2622,12 +2334,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E97" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F97" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G97" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -2645,12 +2354,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E98" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F98" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G98" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -2668,12 +2374,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage</v>
       </c>
       <c r="E99" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F99" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G99" t="str">
         <v>VW_EVT_RH_PONTO_ANALITICO</v>
       </c>
     </row>
@@ -2691,12 +2394,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage</v>
       </c>
       <c r="E100" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F100" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G100" t="str">
         <v>D_USUARIO_FILIAL</v>
       </c>
     </row>
@@ -2714,12 +2414,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage</v>
       </c>
       <c r="E101" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F101" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G101" t="str">
         <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
       </c>
     </row>
@@ -2737,12 +2434,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage</v>
       </c>
       <c r="E102" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F102" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G102" t="str">
         <v>D_USUARIO_FILIAL</v>
       </c>
     </row>
@@ -2760,12 +2454,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
       </c>
       <c r="E103" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F103" t="str">
-        <v/>
-      </c>
-      <c r="G103" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -2783,12 +2474,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
       </c>
       <c r="E104" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F104" t="str">
-        <v/>
-      </c>
-      <c r="G104" t="str">
         <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
       </c>
     </row>
@@ -2806,12 +2494,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
       </c>
       <c r="E105" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F105" t="str">
-        <v/>
-      </c>
-      <c r="G105" t="str">
         <v>VW_EVT_RH_PONTO_ANALITICO</v>
       </c>
     </row>
@@ -2829,12 +2514,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/17222/lineage</v>
       </c>
       <c r="E106" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F106" t="str">
-        <v/>
-      </c>
-      <c r="G106" t="str">
         <v>VW_EVT_RH_PONTO_CONSOLIDADO</v>
       </c>
     </row>
@@ -2852,12 +2534,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E107" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F107" t="str">
-        <v/>
-      </c>
-      <c r="G107" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -2875,12 +2554,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E108" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F108" t="str">
-        <v/>
-      </c>
-      <c r="G108" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -2898,12 +2574,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E109" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F109" t="str">
-        <v/>
-      </c>
-      <c r="G109" t="str">
         <v>VW_D_FILIAL</v>
       </c>
     </row>
@@ -2921,12 +2594,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E110" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F110" t="str">
-        <v/>
-      </c>
-      <c r="G110" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -2944,12 +2614,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E111" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F111" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G111" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -2967,12 +2634,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E112" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F112" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G112" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -2990,12 +2654,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E113" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F113" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G113" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -3013,12 +2674,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E114" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F114" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G114" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3036,12 +2694,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E115" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F115" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G115" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -3059,12 +2714,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E116" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F116" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G116" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -3082,12 +2734,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E117" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F117" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G117" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -3105,12 +2754,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E118" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F118" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G118" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -3128,12 +2774,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E119" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F119" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G119" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -3151,12 +2794,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E120" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F120" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G120" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -3174,12 +2814,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E121" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F121" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G121" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3197,12 +2834,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E122" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F122" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G122" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -3220,12 +2854,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E123" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F123" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G123" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -3243,12 +2874,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E124" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F124" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G124" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -3266,12 +2894,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E125" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F125" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G125" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -3289,12 +2914,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E126" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F126" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G126" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -3312,12 +2934,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E127" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F127" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G127" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -3335,12 +2954,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E128" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F128" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G128" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3358,12 +2974,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E129" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F129" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G129" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -3381,12 +2994,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E130" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F130" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G130" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -3404,12 +3014,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E131" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F131" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G131" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -3427,12 +3034,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E132" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F132" t="str">
-        <v/>
-      </c>
-      <c r="G132" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -3450,12 +3054,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E133" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F133" t="str">
-        <v/>
-      </c>
-      <c r="G133" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3473,12 +3074,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E134" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F134" t="str">
-        <v/>
-      </c>
-      <c r="G134" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -3496,12 +3094,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E135" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F135" t="str">
-        <v/>
-      </c>
-      <c r="G135" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -3519,12 +3114,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E136" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F136" t="str">
-        <v/>
-      </c>
-      <c r="G136" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -3542,12 +3134,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E137" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F137" t="str">
-        <v/>
-      </c>
-      <c r="G137" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -3565,12 +3154,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E138" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F138" t="str">
-        <v/>
-      </c>
-      <c r="G138" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -3588,12 +3174,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E139" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F139" t="str">
-        <v/>
-      </c>
-      <c r="G139" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -3611,12 +3194,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E140" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F140" t="str">
-        <v/>
-      </c>
-      <c r="G140" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -3634,12 +3214,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E141" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F141" t="str">
-        <v/>
-      </c>
-      <c r="G141" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -3657,12 +3234,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E142" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F142" t="str">
-        <v/>
-      </c>
-      <c r="G142" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -3680,12 +3254,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E143" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F143" t="str">
-        <v/>
-      </c>
-      <c r="G143" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -3703,12 +3274,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E144" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F144" t="str">
-        <v/>
-      </c>
-      <c r="G144" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -3726,12 +3294,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E145" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F145" t="str">
-        <v/>
-      </c>
-      <c r="G145" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -3749,12 +3314,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E146" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F146" t="str">
-        <v/>
-      </c>
-      <c r="G146" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -3772,12 +3334,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E147" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F147" t="str">
-        <v/>
-      </c>
-      <c r="G147" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -3795,12 +3354,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E148" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F148" t="str">
-        <v/>
-      </c>
-      <c r="G148" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -3818,12 +3374,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E149" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F149" t="str">
-        <v/>
-      </c>
-      <c r="G149" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -3841,12 +3394,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E150" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F150" t="str">
-        <v/>
-      </c>
-      <c r="G150" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -3864,12 +3414,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E151" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F151" t="str">
-        <v/>
-      </c>
-      <c r="G151" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -3887,12 +3434,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E152" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F152" t="str">
-        <v/>
-      </c>
-      <c r="G152" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -3910,12 +3454,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E153" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F153" t="str">
-        <v/>
-      </c>
-      <c r="G153" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -3933,12 +3474,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E154" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F154" t="str">
-        <v/>
-      </c>
-      <c r="G154" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -3956,12 +3494,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E155" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F155" t="str">
-        <v/>
-      </c>
-      <c r="G155" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -3979,12 +3514,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E156" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F156" t="str">
-        <v/>
-      </c>
-      <c r="G156" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -4002,12 +3534,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E157" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F157" t="str">
-        <v/>
-      </c>
-      <c r="G157" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -4025,12 +3554,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E158" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F158" t="str">
-        <v/>
-      </c>
-      <c r="G158" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -4048,12 +3574,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E159" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F159" t="str">
-        <v/>
-      </c>
-      <c r="G159" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -4071,12 +3594,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E160" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F160" t="str">
-        <v/>
-      </c>
-      <c r="G160" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -4094,12 +3614,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E161" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F161" t="str">
-        <v/>
-      </c>
-      <c r="G161" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -4117,12 +3634,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E162" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F162" t="str">
-        <v/>
-      </c>
-      <c r="G162" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -4140,12 +3654,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E163" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F163" t="str">
-        <v/>
-      </c>
-      <c r="G163" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -4163,12 +3674,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E164" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F164" t="str">
-        <v/>
-      </c>
-      <c r="G164" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -4186,12 +3694,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E165" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F165" t="str">
-        <v/>
-      </c>
-      <c r="G165" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -4209,12 +3714,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E166" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F166" t="str">
-        <v/>
-      </c>
-      <c r="G166" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -4232,12 +3734,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E167" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F167" t="str">
-        <v/>
-      </c>
-      <c r="G167" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -4255,12 +3754,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E168" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F168" t="str">
-        <v/>
-      </c>
-      <c r="G168" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -4278,12 +3774,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E169" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F169" t="str">
-        <v/>
-      </c>
-      <c r="G169" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -4301,12 +3794,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E170" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F170" t="str">
-        <v/>
-      </c>
-      <c r="G170" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -4324,12 +3814,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E171" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F171" t="str">
-        <v/>
-      </c>
-      <c r="G171" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -4347,12 +3834,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E172" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F172" t="str">
-        <v/>
-      </c>
-      <c r="G172" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -4370,12 +3854,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E173" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F173" t="str">
-        <v/>
-      </c>
-      <c r="G173" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -4393,12 +3874,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E174" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F174" t="str">
-        <v/>
-      </c>
-      <c r="G174" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -4416,12 +3894,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E175" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F175" t="str">
-        <v/>
-      </c>
-      <c r="G175" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -4439,12 +3914,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E176" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F176" t="str">
-        <v/>
-      </c>
-      <c r="G176" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -4462,12 +3934,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E177" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F177" t="str">
-        <v/>
-      </c>
-      <c r="G177" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -4485,12 +3954,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E178" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F178" t="str">
-        <v/>
-      </c>
-      <c r="G178" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -4508,12 +3974,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E179" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F179" t="str">
-        <v/>
-      </c>
-      <c r="G179" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -4531,12 +3994,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E180" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F180" t="str">
-        <v/>
-      </c>
-      <c r="G180" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -4554,12 +4014,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E181" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F181" t="str">
-        <v/>
-      </c>
-      <c r="G181" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -4577,12 +4034,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E182" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F182" t="str">
-        <v/>
-      </c>
-      <c r="G182" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -4600,12 +4054,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E183" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F183" t="str">
-        <v/>
-      </c>
-      <c r="G183" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -4623,12 +4074,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E184" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F184" t="str">
-        <v/>
-      </c>
-      <c r="G184" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -4646,12 +4094,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E185" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F185" t="str">
-        <v/>
-      </c>
-      <c r="G185" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -4669,12 +4114,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E186" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F186" t="str">
-        <v/>
-      </c>
-      <c r="G186" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -4692,12 +4134,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E187" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F187" t="str">
-        <v/>
-      </c>
-      <c r="G187" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -4715,12 +4154,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E188" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F188" t="str">
-        <v/>
-      </c>
-      <c r="G188" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -4738,12 +4174,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E189" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F189" t="str">
-        <v/>
-      </c>
-      <c r="G189" t="str">
         <v>Absenteismo_Days</v>
       </c>
     </row>
@@ -4761,12 +4194,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E190" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F190" t="str">
-        <v/>
-      </c>
-      <c r="G190" t="str">
         <v>'Elegiveis cota aprendiz$'</v>
       </c>
     </row>
@@ -4784,12 +4214,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E191" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F191" t="str">
-        <v/>
-      </c>
-      <c r="G191" t="str">
         <v>'Women Leardership$'</v>
       </c>
     </row>
@@ -4807,12 +4234,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E192" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F192" t="str">
-        <v/>
-      </c>
-      <c r="G192" t="str">
         <v>Promoções_Internas</v>
       </c>
     </row>
@@ -4830,12 +4254,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E193" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F193" t="str">
-        <v/>
-      </c>
-      <c r="G193" t="str">
         <v>METAS</v>
       </c>
     </row>
@@ -4853,12 +4274,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E194" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F194" t="str">
-        <v/>
-      </c>
-      <c r="G194" t="str">
         <v>Other_KPIs_HR</v>
       </c>
     </row>
@@ -4876,12 +4294,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E195" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F195" t="str">
-        <v/>
-      </c>
-      <c r="G195" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -4899,12 +4314,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E196" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F196" t="str">
-        <v/>
-      </c>
-      <c r="G196" t="str">
         <v>Absenteismo_Days_Segmentos</v>
       </c>
     </row>
@@ -4927,9 +4339,6 @@
       <c r="F197" t="str">
         <v/>
       </c>
-      <c r="G197" t="str">
-        <v/>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -4950,9 +4359,6 @@
       <c r="F198" t="str">
         <v/>
       </c>
-      <c r="G198" t="str">
-        <v/>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -4968,12 +4374,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E199" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F199" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G199" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -4991,12 +4394,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E200" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F200" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G200" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -5014,12 +4414,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E201" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F201" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G201" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -5037,12 +4434,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E202" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F202" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G202" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5060,12 +4454,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E203" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F203" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G203" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -5083,12 +4474,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E204" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F204" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G204" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -5106,12 +4494,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E205" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F205" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G205" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -5129,12 +4514,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E206" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F206" t="str">
-        <v/>
-      </c>
-      <c r="G206" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5152,12 +4534,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E207" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F207" t="str">
-        <v/>
-      </c>
-      <c r="G207" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5175,12 +4554,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E208" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F208" t="str">
-        <v/>
-      </c>
-      <c r="G208" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5198,12 +4574,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E209" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F209" t="str">
-        <v/>
-      </c>
-      <c r="G209" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5221,12 +4594,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E210" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F210" t="str">
-        <v/>
-      </c>
-      <c r="G210" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -5244,12 +4614,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E211" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F211" t="str">
-        <v/>
-      </c>
-      <c r="G211" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -5267,12 +4634,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E212" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F212" t="str">
-        <v/>
-      </c>
-      <c r="G212" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -5290,12 +4654,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E213" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F213" t="str">
-        <v/>
-      </c>
-      <c r="G213" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5313,12 +4674,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E214" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F214" t="str">
-        <v/>
-      </c>
-      <c r="G214" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5336,12 +4694,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E215" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F215" t="str">
-        <v/>
-      </c>
-      <c r="G215" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5359,12 +4714,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E216" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F216" t="str">
-        <v/>
-      </c>
-      <c r="G216" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5382,12 +4734,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E217" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F217" t="str">
-        <v/>
-      </c>
-      <c r="G217" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -5405,12 +4754,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E218" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F218" t="str">
-        <v/>
-      </c>
-      <c r="G218" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -5428,12 +4774,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E219" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F219" t="str">
-        <v/>
-      </c>
-      <c r="G219" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -5451,12 +4794,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E220" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F220" t="str">
-        <v/>
-      </c>
-      <c r="G220" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5474,12 +4814,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E221" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F221" t="str">
-        <v/>
-      </c>
-      <c r="G221" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5497,12 +4834,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E222" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F222" t="str">
-        <v/>
-      </c>
-      <c r="G222" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5520,12 +4854,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E223" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F223" t="str">
-        <v/>
-      </c>
-      <c r="G223" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5543,12 +4874,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E224" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F224" t="str">
-        <v/>
-      </c>
-      <c r="G224" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -5566,12 +4894,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E225" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F225" t="str">
-        <v/>
-      </c>
-      <c r="G225" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -5589,12 +4914,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E226" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F226" t="str">
-        <v/>
-      </c>
-      <c r="G226" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -5612,12 +4934,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E227" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F227" t="str">
-        <v/>
-      </c>
-      <c r="G227" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5635,12 +4954,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E228" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F228" t="str">
-        <v/>
-      </c>
-      <c r="G228" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5658,12 +4974,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E229" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F229" t="str">
-        <v/>
-      </c>
-      <c r="G229" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5681,12 +4994,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E230" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F230" t="str">
-        <v/>
-      </c>
-      <c r="G230" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5704,12 +5014,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E231" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F231" t="str">
-        <v/>
-      </c>
-      <c r="G231" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -5727,12 +5034,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E232" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F232" t="str">
-        <v/>
-      </c>
-      <c r="G232" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -5750,12 +5054,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E233" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F233" t="str">
-        <v/>
-      </c>
-      <c r="G233" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -5773,12 +5074,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E234" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F234" t="str">
-        <v/>
-      </c>
-      <c r="G234" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5796,12 +5094,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E235" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F235" t="str">
-        <v/>
-      </c>
-      <c r="G235" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5819,12 +5114,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E236" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F236" t="str">
-        <v/>
-      </c>
-      <c r="G236" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -5842,12 +5134,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E237" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F237" t="str">
-        <v/>
-      </c>
-      <c r="G237" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -5865,12 +5154,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E238" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F238" t="str">
-        <v/>
-      </c>
-      <c r="G238" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -5888,12 +5174,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E239" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F239" t="str">
-        <v/>
-      </c>
-      <c r="G239" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -5911,12 +5194,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E240" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F240" t="str">
-        <v/>
-      </c>
-      <c r="G240" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -5934,12 +5214,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E241" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F241" t="str">
-        <v/>
-      </c>
-      <c r="G241" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -5957,12 +5234,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E242" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F242" t="str">
-        <v/>
-      </c>
-      <c r="G242" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -5980,12 +5254,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E243" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F243" t="str">
-        <v/>
-      </c>
-      <c r="G243" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -6003,12 +5274,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E244" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F244" t="str">
-        <v/>
-      </c>
-      <c r="G244" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -6026,12 +5294,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E245" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F245" t="str">
-        <v/>
-      </c>
-      <c r="G245" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -6049,12 +5314,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E246" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F246" t="str">
-        <v/>
-      </c>
-      <c r="G246" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -6072,12 +5334,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E247" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F247" t="str">
-        <v/>
-      </c>
-      <c r="G247" t="str">
         <v>'DE PARA$'</v>
       </c>
     </row>
@@ -6095,12 +5354,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E248" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F248" t="str">
-        <v/>
-      </c>
-      <c r="G248" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -6118,12 +5374,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E249" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F249" t="str">
-        <v/>
-      </c>
-      <c r="G249" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -6141,12 +5394,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E250" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F250" t="str">
-        <v/>
-      </c>
-      <c r="G250" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -6164,12 +5414,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E251" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F251" t="str">
-        <v/>
-      </c>
-      <c r="G251" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -6187,12 +5434,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E252" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F252" t="str">
-        <v/>
-      </c>
-      <c r="G252" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -6210,12 +5454,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E253" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F253" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G253" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -6233,12 +5474,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E254" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F254" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G254" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -6256,12 +5494,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E255" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F255" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G255" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -6279,12 +5514,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E256" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F256" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G256" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6302,12 +5534,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E257" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F257" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G257" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -6325,12 +5554,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E258" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F258" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G258" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -6348,12 +5574,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E259" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F259" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G259" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -6371,12 +5594,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E260" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F260" t="str">
-        <v/>
-      </c>
-      <c r="G260" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -6394,12 +5614,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E261" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F261" t="str">
-        <v/>
-      </c>
-      <c r="G261" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6417,12 +5634,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E262" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F262" t="str">
-        <v/>
-      </c>
-      <c r="G262" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -6440,12 +5654,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E263" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F263" t="str">
-        <v/>
-      </c>
-      <c r="G263" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -6463,12 +5674,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E264" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F264" t="str">
-        <v/>
-      </c>
-      <c r="G264" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -6486,12 +5694,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E265" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F265" t="str">
-        <v/>
-      </c>
-      <c r="G265" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6509,12 +5714,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E266" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F266" t="str">
-        <v/>
-      </c>
-      <c r="G266" t="str">
         <v>F_COLABORADOR_FOLHA_SAL</v>
       </c>
     </row>
@@ -6532,12 +5734,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E267" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F267" t="str">
-        <v/>
-      </c>
-      <c r="G267" t="str">
         <v>D_COLABORADOR_EXPURGO_ROTATIVIDADE</v>
       </c>
     </row>
@@ -6555,12 +5754,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/52187/lineage</v>
       </c>
       <c r="E268" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F268" t="str">
-        <v/>
-      </c>
-      <c r="G268" t="str">
         <v>Extract</v>
       </c>
     </row>
@@ -6578,12 +5774,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E269" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F269" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G269" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -6601,12 +5794,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E270" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F270" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G270" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -6624,12 +5814,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E271" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F271" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G271" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -6647,12 +5834,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E272" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F272" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G272" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6670,12 +5854,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E273" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F273" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G273" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -6693,12 +5874,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E274" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F274" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G274" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -6716,12 +5894,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E275" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F275" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G275" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -6739,12 +5914,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E276" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F276" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G276" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -6762,12 +5934,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E277" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F277" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G277" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -6785,12 +5954,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E278" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F278" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G278" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -6808,12 +5974,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E279" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F279" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G279" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -6831,12 +5994,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E280" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F280" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G280" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -6854,12 +6014,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E281" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F281" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G281" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -6877,12 +6034,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E282" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F282" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G282" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -6900,12 +6054,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E283" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F283" t="str">
-        <v/>
-      </c>
-      <c r="G283" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -6923,12 +6074,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E284" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F284" t="str">
-        <v/>
-      </c>
-      <c r="G284" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -6946,12 +6094,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E285" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F285" t="str">
-        <v/>
-      </c>
-      <c r="G285" t="str">
         <v>VW_D_FILIAL</v>
       </c>
     </row>
@@ -6969,12 +6114,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E286" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F286" t="str">
-        <v/>
-      </c>
-      <c r="G286" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -6992,12 +6134,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E287" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F287" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G287" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -7015,12 +6154,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E288" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F288" t="str">
-        <v/>
-      </c>
-      <c r="G288" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -7038,12 +6174,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E289" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F289" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G289" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -7061,12 +6194,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E290" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F290" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G290" t="str">
         <v>d_filial_complemento</v>
       </c>
     </row>
@@ -7084,12 +6214,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E291" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F291" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G291" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -7107,12 +6234,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E292" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F292" t="str">
-        <v/>
-      </c>
-      <c r="G292" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7130,12 +6254,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E293" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F293" t="str">
-        <v/>
-      </c>
-      <c r="G293" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -7153,12 +6274,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E294" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F294" t="str">
-        <v/>
-      </c>
-      <c r="G294" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -7176,12 +6294,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E295" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F295" t="str">
-        <v/>
-      </c>
-      <c r="G295" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -7199,12 +6314,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E296" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F296" t="str">
-        <v/>
-      </c>
-      <c r="G296" t="str">
         <v>Planilha1</v>
       </c>
     </row>
@@ -7222,12 +6334,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E297" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F297" t="str">
-        <v/>
-      </c>
-      <c r="G297" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -7245,12 +6354,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E298" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F298" t="str">
-        <v/>
-      </c>
-      <c r="G298" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -7268,12 +6374,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E299" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F299" t="str">
-        <v/>
-      </c>
-      <c r="G299" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7291,12 +6394,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E300" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F300" t="str">
-        <v/>
-      </c>
-      <c r="G300" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -7314,12 +6414,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E301" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F301" t="str">
-        <v/>
-      </c>
-      <c r="G301" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -7337,12 +6434,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E302" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F302" t="str">
-        <v/>
-      </c>
-      <c r="G302" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -7360,12 +6454,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E303" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F303" t="str">
-        <v/>
-      </c>
-      <c r="G303" t="str">
         <v>Planilha1</v>
       </c>
     </row>
@@ -7383,12 +6474,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E304" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F304" t="str">
-        <v/>
-      </c>
-      <c r="G304" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -7406,12 +6494,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E305" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F305" t="str">
-        <v/>
-      </c>
-      <c r="G305" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -7429,12 +6514,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E306" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F306" t="str">
-        <v/>
-      </c>
-      <c r="G306" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7452,12 +6534,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E307" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F307" t="str">
-        <v/>
-      </c>
-      <c r="G307" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -7475,12 +6554,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E308" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F308" t="str">
-        <v/>
-      </c>
-      <c r="G308" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -7498,12 +6574,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E309" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F309" t="str">
-        <v/>
-      </c>
-      <c r="G309" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -7521,12 +6594,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E310" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F310" t="str">
-        <v/>
-      </c>
-      <c r="G310" t="str">
         <v>Planilha1</v>
       </c>
     </row>
@@ -7544,12 +6614,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E311" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F311" t="str">
-        <v/>
-      </c>
-      <c r="G311" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -7567,12 +6634,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E312" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F312" t="str">
-        <v/>
-      </c>
-      <c r="G312" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -7590,12 +6654,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E313" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F313" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G313" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -7613,12 +6674,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E314" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F314" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G314" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -7636,12 +6694,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E315" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F315" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G315" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -7659,12 +6714,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E316" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F316" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G316" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -7682,12 +6734,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E317" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F317" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G317" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -7705,12 +6754,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E318" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F318" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G318" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -7728,12 +6774,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E319" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F319" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G319" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -7751,12 +6794,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E320" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F320" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G320" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -7774,12 +6814,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E321" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F321" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G321" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -7797,12 +6834,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E322" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F322" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G322" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -7820,12 +6854,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E323" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F323" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G323" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -7843,12 +6874,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E324" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F324" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G324" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -7866,12 +6894,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E325" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F325" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G325" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -7889,12 +6914,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E326" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F326" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G326" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -7912,12 +6934,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E327" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F327" t="str">
-        <v/>
-      </c>
-      <c r="G327" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -7935,12 +6954,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E328" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F328" t="str">
-        <v/>
-      </c>
-      <c r="G328" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -7958,12 +6974,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E329" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F329" t="str">
-        <v/>
-      </c>
-      <c r="G329" t="str">
         <v>VW_D_FILIAL</v>
       </c>
     </row>
@@ -7981,12 +6994,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E330" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F330" t="str">
-        <v/>
-      </c>
-      <c r="G330" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -8004,12 +7014,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E331" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F331" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G331" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -8027,12 +7034,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E332" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F332" t="str">
-        <v/>
-      </c>
-      <c r="G332" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -8050,12 +7054,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E333" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F333" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G333" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -8073,12 +7074,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E334" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F334" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G334" t="str">
         <v>d_filial_complemento</v>
       </c>
     </row>
@@ -8096,12 +7094,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage</v>
       </c>
       <c r="E335" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F335" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G335" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -8119,12 +7114,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E336" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F336" t="str">
-        <v/>
-      </c>
-      <c r="G336" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -8142,12 +7134,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E337" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F337" t="str">
-        <v/>
-      </c>
-      <c r="G337" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -8165,12 +7154,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E338" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F338" t="str">
-        <v/>
-      </c>
-      <c r="G338" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -8188,12 +7174,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E339" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F339" t="str">
-        <v/>
-      </c>
-      <c r="G339" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -8211,12 +7194,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E340" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F340" t="str">
-        <v/>
-      </c>
-      <c r="G340" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -8234,12 +7214,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E341" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F341" t="str">
-        <v/>
-      </c>
-      <c r="G341" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -8257,12 +7234,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E342" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F342" t="str">
-        <v/>
-      </c>
-      <c r="G342" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -8280,12 +7254,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E343" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F343" t="str">
-        <v/>
-      </c>
-      <c r="G343" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
@@ -8303,12 +7274,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E344" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F344" t="str">
-        <v/>
-      </c>
-      <c r="G344" t="str">
         <v>F_PROGRAMACAO_FERIAS</v>
       </c>
     </row>
@@ -8326,12 +7294,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E345" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F345" t="str">
-        <v/>
-      </c>
-      <c r="G345" t="str">
         <v>VW_APDATA_STEP_AFASTAMENTO</v>
       </c>
     </row>
@@ -8349,12 +7314,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E346" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F346" t="str">
-        <v/>
-      </c>
-      <c r="G346" t="str">
         <v>Base_Tableau</v>
       </c>
     </row>
@@ -8372,12 +7334,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E347" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F347" t="str">
-        <v/>
-      </c>
-      <c r="G347" t="str">
         <v>Plan1</v>
       </c>
     </row>
@@ -8395,12 +7354,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage</v>
       </c>
       <c r="E348" t="str">
-        <v>Oracle DW</v>
+        <v>PORTALBI</v>
       </c>
       <c r="F348" t="str">
-        <v>PORTALBI</v>
-      </c>
-      <c r="G348" t="str">
         <v>filial_endereco</v>
       </c>
     </row>
@@ -8418,12 +7374,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage</v>
       </c>
       <c r="E349" t="str">
-        <v>Oracle DW</v>
+        <v>PORTALBI</v>
       </c>
       <c r="F349" t="str">
-        <v>PORTALBI</v>
-      </c>
-      <c r="G349" t="str">
         <v>filial_endereco@tecnisaw</v>
       </c>
     </row>
@@ -8441,12 +7394,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E350" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F350" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G350" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -8464,12 +7414,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E351" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F351" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G351" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -8487,12 +7434,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E352" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F352" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G352" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -8510,12 +7454,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E353" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F353" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G353" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -8533,12 +7474,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E354" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F354" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G354" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -8556,12 +7494,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E355" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F355" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G355" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -8579,12 +7514,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E356" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F356" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G356" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -8602,12 +7534,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
       </c>
       <c r="E357" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F357" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G357" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -8625,12 +7554,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
       </c>
       <c r="E358" t="str">
-        <v>Oracle DW</v>
+        <v/>
       </c>
       <c r="F358" t="str">
-        <v/>
-      </c>
-      <c r="G358" t="str">
         <v>VW_APDATA_STEP_ABERTURA_VAGAS</v>
       </c>
     </row>
@@ -8648,12 +7574,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E359" t="str">
-        <v>Oracle DW</v>
+        <v>bicompras</v>
       </c>
       <c r="F359" t="str">
-        <v>bicompras</v>
-      </c>
-      <c r="G359" t="str">
         <v>d_filial</v>
       </c>
     </row>
@@ -8671,12 +7594,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E360" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F360" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G360" t="str">
         <v>F_APDATA_ABERTURA_VAGA_STEP</v>
       </c>
     </row>
@@ -8694,12 +7614,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E361" t="str">
-        <v>Oracle DW</v>
+        <v>DPESSOAL</v>
       </c>
       <c r="F361" t="str">
-        <v>DPESSOAL</v>
-      </c>
-      <c r="G361" t="str">
         <v>VW_D_COLABORADOR_GRADE</v>
       </c>
     </row>
@@ -8717,12 +7634,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E362" t="str">
-        <v>Oracle DW</v>
+        <v>dpessoal</v>
       </c>
       <c r="F362" t="str">
-        <v>dpessoal</v>
-      </c>
-      <c r="G362" t="str">
         <v>F_COLABORADOR_FOLHA</v>
       </c>
     </row>
@@ -8740,12 +7654,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E363" t="str">
-        <v>Oracle DW</v>
+        <v>portalbi</v>
       </c>
       <c r="F363" t="str">
-        <v>portalbi</v>
-      </c>
-      <c r="G363" t="str">
         <v>filial_complemento@tecnisaw</v>
       </c>
     </row>
@@ -8763,12 +7674,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E364" t="str">
-        <v>Oracle DW</v>
+        <v>bisilver</v>
       </c>
       <c r="F364" t="str">
-        <v>bisilver</v>
-      </c>
-      <c r="G364" t="str">
         <v>vw_estrutra_gerencial</v>
       </c>
     </row>
@@ -8786,12 +7694,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E365" t="str">
-        <v>Oracle DW</v>
+        <v>ciscorp</v>
       </c>
       <c r="F365" t="str">
-        <v>ciscorp</v>
-      </c>
-      <c r="G365" t="str">
         <v>filial</v>
       </c>
     </row>
@@ -8809,12 +7714,9 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
       </c>
       <c r="E366" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F366" t="str">
-        <v/>
-      </c>
-      <c r="G366" t="str">
         <v>D_COLABORADOR</v>
       </c>
     </row>
@@ -8832,25 +7734,22 @@
         <v>https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
       </c>
       <c r="E367" t="str">
-        <v>Planilha</v>
+        <v/>
       </c>
       <c r="F367" t="str">
-        <v/>
-      </c>
-      <c r="G367" t="str">
         <v>D_COLABORADOR_NVL_CLR_COLUNAR</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G367"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F367"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8894,39 +7793,39 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Indicadores RH</v>
+        <v>Horas Extras e Absenteísmo</v>
       </c>
       <c r="B3" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresRH_16860832510040/IndicadoresdeRH</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/HorasExtraseAbsentesmo/AnalticoHorasExtras</v>
       </c>
       <c r="C3" t="str">
-        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau)</v>
       </c>
       <c r="D3" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1057/lineage</v>
       </c>
       <c r="E3" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>Campo Calculado</v>
+        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Base Colaboradores Geral</v>
+        <v>Indicadores RH</v>
       </c>
       <c r="B4" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Basecolaboradoresgeral/Basecolaboradores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresRH_16860832510040/IndicadoresdeRH</v>
       </c>
       <c r="C4" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
       </c>
       <c r="D4" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E4" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
       </c>
       <c r="F4" t="str">
         <v>Campo Calculado</v>
@@ -8934,30 +7833,30 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Indicadores DE&amp;I</v>
+        <v>Indicadores RH</v>
       </c>
       <c r="B5" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresRH_16860832510040/IndicadoresdeRH</v>
       </c>
       <c r="C5" t="str">
-        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; RH - Promoção; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
       </c>
       <c r="D5" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E5" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Motivo Alteracao Grade; CEP; Cidade; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; Deficiencia; Dlg Dlsdesligamento; Cargo de Confiança; Categoria; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>Campo Calculado</v>
+        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Book de Indicadores de Pessoas</v>
+        <v>Base Colaboradores Geral</v>
       </c>
       <c r="B6" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basecolaboradoresgeral/Basecolaboradores</v>
       </c>
       <c r="C6" t="str">
         <v>RH - Colaborador Folha</v>
@@ -8974,70 +7873,70 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
+        <v>Base Colaboradores Geral</v>
       </c>
       <c r="B7" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basecolaboradoresgeral/Basecolaboradores</v>
       </c>
       <c r="C7" t="str">
-        <v>RH - Colaborador Ponto Analitico RLS V2; RH - Colaborador Ponto Sintetico RLS; Ondas_Projeto_Ponto</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D7" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage; https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E7" t="str">
-        <v>Cálculo1; Cálculo2; CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO; CL; Clbr; Onda; Planilha1 (Count)</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>Campo Calculado</v>
+        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Base de Férias em Aberto</v>
+        <v>Indicadores DE&amp;I</v>
       </c>
       <c r="B8" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C8" t="str">
-        <v>RH - Colaborador Ponto Sintetico; RH - Programação de Férias</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; RH - Promoção; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
       </c>
       <c r="D8" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/17222/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E8" t="str">
-        <v>CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Motivo Alteracao Grade; CEP; Cidade; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; Deficiencia; Dlg Dlsdesligamento; Cargo de Confiança; Categoria; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
       </c>
       <c r="F8" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Campo Calculado</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Modelo de Trabalho</v>
+        <v>Indicadores DE&amp;I</v>
       </c>
       <c r="B9" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C9" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; RH - Promoção; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
       </c>
       <c r="D9" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E9" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>Campo Calculado</v>
+        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Banco de Horas</v>
+        <v>Book de Indicadores de Pessoas</v>
       </c>
       <c r="B10" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
       </c>
       <c r="C10" t="str">
         <v>RH - Colaborador Folha</v>
@@ -9054,79 +7953,79 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
+        <v>Book de Indicadores de Pessoas</v>
       </c>
       <c r="B11" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
       </c>
       <c r="C11" t="str">
-        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D11" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E11" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>Campo Calculado</v>
+        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Metas Turnover FY26 - Regrettable e Demissional</v>
+        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
       </c>
       <c r="B12" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY26-RegrettableeDemissional/MetasdeRHFY26</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>RH - Colaborador Ponto Analitico RLS V2; RH - Colaborador Ponto Sintetico RLS; Ondas_Projeto_Ponto</v>
       </c>
       <c r="D12" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage; https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>Cálculo1; Cálculo2; CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO; CL; Clbr; Onda; Planilha1 (Count)</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>Campo Calculado</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Women Leadership</v>
+        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
       </c>
       <c r="B13" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>RH - Colaborador Ponto Analitico RLS V2; RH - Colaborador Ponto Sintetico RLS; Ondas_Projeto_Ponto</v>
       </c>
       <c r="D13" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage; https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Wokforce Planning</v>
+        <v>Base de Férias em Aberto</v>
       </c>
       <c r="B14" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
       </c>
       <c r="C14" t="str">
-        <v>RH - Colaborador Folha; DE-PARA_BU; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+        <v>RH - Colaborador Ponto Sintetico; RH - Programação de Férias</v>
       </c>
       <c r="D14" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/17222/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E14" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; FY; METAS (Count); Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
+        <v/>
       </c>
       <c r="F14" t="str">
         <v>Campo Calculado</v>
@@ -9134,39 +8033,39 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Indicadores de Chamados e Workflows</v>
+        <v>Base de Férias em Aberto</v>
       </c>
       <c r="B15" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
       </c>
       <c r="C15" t="str">
-        <v>dCalendario; fChamadosEmAberto; fChamadosResolvidos; fWorkflowsEmAberto; fWorkflowsResolvidos</v>
+        <v>RH - Colaborador Ponto Sintetico; RH - Programação de Férias</v>
       </c>
       <c r="D15" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/17222/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E15" t="str">
-        <v>Ano; Ano Fiscal; Data; Dia; Dia da Semana; Dia da Semana ID; Extract (Count); Fiscal Year; Mês; Mês Abr; Mês Fiscal; Mês ID; Mês/Ano; Mês/Ano ID; Período Fiscal ID; Período/FY; Período/FY ID; Semana do Ano; Semana do Ano ID; Semana Fiscal do Ano; Semana Fiscal do Ano ID; Semana Fiscal/Ano ID; Semana/Ano; Semana/Ano ID; Semestre Fiscal / Ano ID; Semestre Fiscal do Ano; Semestre ID; Trimestre Fiscal; Trimestre Fiscal/Ano; Trimestre Fiscal/Ano ID; Assunto; Atribuído ao Usuário; Criador; Data de Conclusão Alvo; Data de Criação; Data Referência; Em nome de; Equipe Atribuída; Fila Atribuída; Fonte; Horas SLA; ID do caso; ID do Caso Relacionado; Prioridade; Solicitado por; Status do caso; Subtópico de RH; Tema de RH; % No Prazo; :Measure Names; Atingiu a Meta; Data de Conclusão Alvo Ajustada; Data de reabertura; Data Referência Resolução; Data/Hora da Primeira Resposta; Data/Hora Resolvida; Dia da Semana Criação; Fila Atribuída (Subequipe); Meta; Número do chamado; Período Fiscal; Qtde Em Atraso; Qtde No Prazo; Reabertos; Status do chamado; Status Prazo Primeiro Atendimento; Tempo de Resolução do Caso (Dias Úteis); Tempo de Trabalho em Dias Úteis; Tempo de trabalho em horas úteis (até agora); Total Atendimentos; Data da Etapa; Data prazo atendimento; Data Referencia; Data/hora início da transação; Dentro do prazo?; Equipe; Etapa de Workflow; Feriado; Formulário de Workflow; Id etapa de workflow; Id Formulário de Workflow; Id Lançamento de Workflow; Nome do Usuário; Referência; Solicitante; Subequipe; % Dentro do Prazo; Atendido Em; Categoria Dia Entrada Wf; Categoria Dia Prazo Atend; Data Prazo Atendimento 2; Data Rescisão; Dentro Prazo?; Efetivado?; Entrada Wf; Entrada Wf 2; Etapa Destino; Etapa Origem; Etapa Wf - Destino; Etapa Wf - Origem; Formulário Wf; Grupo Usuário; Id Formulário Wf; Id Grupo Usuário; Id Log Transação Wf; Id Workflow; Meta WFs; Nome Usuário; Novo Status Dentro Prazo; Prazo Atendimento 1º Dia Útil Próximo Mês; Prazo Atendimento Exceto Abertura Fim De Mês; Qtde Dentro do Prazo; Qtde Fora do Prazo; Status da Meta; Superior Hierárquico; Tempo Atendim Horas Uteis; Tempo Atendimento Hr</v>
+        <v>CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
       <c r="F15" t="str">
-        <v>Campo Calculado</v>
+        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Visão consolidada</v>
+        <v>Modelo de Trabalho</v>
       </c>
       <c r="B16" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
       </c>
       <c r="C16" t="str">
-        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); PCD (Tableau)</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D16" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E16" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula; PCD (Count); Qtd. Pcd</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="F16" t="str">
         <v>Campo Calculado</v>
@@ -9174,39 +8073,39 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Zona Posicionamento Salarial</v>
+        <v>Modelo de Trabalho</v>
       </c>
       <c r="B17" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
       </c>
       <c r="C17" t="str">
-        <v>RH - Base_Enios_Tableau; RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D17" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/52187/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E17" t="str">
-        <v>Admissão; Cargo; CL; Colaborador; Cpf; Dados gerados em; Diretoria; Dt Competencia; Dt inic cargo atual; Dt nasc; Gênero; Gestor; Grade; HR Reporting; Matrícula; Munic. cl; Nome do cl; Portfolio; Posição Faixa; Região cl; Segmento; Situação; Tipo cl; Uf cl; Zona posicionamento; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v/>
       </c>
       <c r="F17" t="str">
-        <v>Campo Calculado</v>
+        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Base de Dados Modelo de Trabalho - Home Office</v>
+        <v>Banco de Horas</v>
       </c>
       <c r="B18" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
       </c>
       <c r="C18" t="str">
-        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Catracas; Base_Tableau; reserva_mesas_por_colaborador geral</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D18" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E18" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Cardapio; Cd Centro Custo; Cd Empresa Sodexo; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Status; Cd Tipo Atuacao; Cd Tipo Servico; Cd Uf; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Competencia; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos; % Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Mesa; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
       <c r="F18" t="str">
         <v>Campo Calculado</v>
@@ -9214,10 +8113,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Indicadores de Promoções Internas</v>
+        <v>Banco de Horas</v>
       </c>
       <c r="B19" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
       </c>
       <c r="C19" t="str">
         <v>RH - Colaborador Folha</v>
@@ -9226,27 +8125,27 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E19" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+        <v/>
       </c>
       <c r="F19" t="str">
-        <v>Campo Calculado</v>
+        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Indicadores de Modelo de Trabalho - Home Office</v>
+        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
       </c>
       <c r="B20" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C20" t="str">
-        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Tableau; reserva_mesas_por_colaborador geral</v>
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
       </c>
       <c r="D20" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E20" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Cardapio; Cd Centro Custo; Cd Empresa Sodexo; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Status; Cd Tipo Atuacao; Cd Tipo Servico; Cd Uf; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; % Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
       </c>
       <c r="F20" t="str">
         <v>Campo Calculado</v>
@@ -9254,47 +8153,467 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Painel de Vagas Operacionais</v>
+        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
       </c>
       <c r="B21" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C21" t="str">
-        <v>BIVARREDURA - Filial; RH - Colaborador Folha; RH STEP Abertura de Vagas</v>
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
       </c>
       <c r="D21" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E21" t="str">
-        <v>[END] Bairro; [END] CEP; [END] Cidade; [END] LATITUDE; [END] Logadouro; [END] LONGITUDE; [END] UF; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_BUSINESS_UNIT; Dados migrados (Count); Dt Abertura; Dt Encerramento; Fili Email; Fl Ficticia; Inscricaoestadual; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Diretor Operacional; Nm Diretoria; Nm Empresa Sodexo; Nm Filial; Nm Gerente Area; Nm Gerente Regional; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial Colaborador; Cd Grupo CL; Cd Matriz Cardapio; Cd Matriz Compras; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Portfolio; CD_CARGO; CD_CARGO_HR_REPORTING; CD_CARGO_VAGA; CD_COTA_APRENDIZ_CBO; CD_ESTR_HIERAR; CD_ESTR_HIERAR_COLAB; CD_FILIAL_COLABORADOR; CD_FILIAL_VAGA; CD_FLEXIVEL_VAGA; CD_SINDICATO; CD_SITUACAO; CD_VAGA; CLASSIFICACAO_HR_REPORTING; COR_PELE; CPF; CTPS</v>
+        <v/>
       </c>
       <c r="F21" t="str">
-        <v>Campo Calculado</v>
+        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Pin People On e Off</v>
+        <v>Metas Turnover FY26 - Regrettable e Demissional</v>
       </c>
       <c r="B22" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY26-RegrettableeDemissional/MetasdeRHFY26</v>
       </c>
       <c r="C22" t="str">
-        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+        <v/>
       </c>
       <c r="D22" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E22" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cargo de Confiança; Categoria; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+        <v/>
       </c>
       <c r="F22" t="str">
         <v>Campo Calculado</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Metas Turnover FY26 - Regrettable e Demissional</v>
+      </c>
+      <c r="B23" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY26-RegrettableeDemissional/MetasdeRHFY26</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Women Leadership</v>
+      </c>
+      <c r="B24" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Women Leadership</v>
+      </c>
+      <c r="B25" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Wokforce Planning</v>
+      </c>
+      <c r="B26" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
+      </c>
+      <c r="C26" t="str">
+        <v>RH - Colaborador Folha; DE-PARA_BU; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+      </c>
+      <c r="D26" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
+      </c>
+      <c r="E26" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; FY; METAS (Count); Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Wokforce Planning</v>
+      </c>
+      <c r="B27" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
+      </c>
+      <c r="C27" t="str">
+        <v>RH - Colaborador Folha; DE-PARA_BU; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+      </c>
+      <c r="D27" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Indicadores de Chamados e Workflows</v>
+      </c>
+      <c r="B28" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
+      </c>
+      <c r="C28" t="str">
+        <v>dCalendario; fChamadosEmAberto; fChamadosResolvidos; fWorkflowsEmAberto; fWorkflowsResolvidos</v>
+      </c>
+      <c r="D28" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Ano; Ano Fiscal; Data; Dia; Dia da Semana; Dia da Semana ID; Extract (Count); Fiscal Year; Mês; Mês Abr; Mês Fiscal; Mês ID; Mês/Ano; Mês/Ano ID; Período Fiscal ID; Período/FY; Período/FY ID; Semana do Ano; Semana do Ano ID; Semana Fiscal do Ano; Semana Fiscal do Ano ID; Semana Fiscal/Ano ID; Semana/Ano; Semana/Ano ID; Semestre Fiscal / Ano ID; Semestre Fiscal do Ano; Semestre ID; Trimestre Fiscal; Trimestre Fiscal/Ano; Trimestre Fiscal/Ano ID; Assunto; Atribuído ao Usuário; Criador; Data de Conclusão Alvo; Data de Criação; Data Referência; Em nome de; Equipe Atribuída; Fila Atribuída; Fonte; Horas SLA; ID do caso; ID do Caso Relacionado; Prioridade; Solicitado por; Status do caso; Subtópico de RH; Tema de RH; % No Prazo; :Measure Names; Atingiu a Meta; Data de Conclusão Alvo Ajustada; Data de reabertura; Data Referência Resolução; Data/Hora da Primeira Resposta; Data/Hora Resolvida; Dia da Semana Criação; Fila Atribuída (Subequipe); Meta; Número do chamado; Período Fiscal; Qtde Em Atraso; Qtde No Prazo; Reabertos; Status do chamado; Status Prazo Primeiro Atendimento; Tempo de Resolução do Caso (Dias Úteis); Tempo de Trabalho em Dias Úteis; Tempo de trabalho em horas úteis (até agora); Total Atendimentos; Data da Etapa; Data prazo atendimento; Data Referencia; Data/hora início da transação; Dentro do prazo?; Equipe; Etapa de Workflow; Feriado; Formulário de Workflow; Id etapa de workflow; Id Formulário de Workflow; Id Lançamento de Workflow; Nome do Usuário; Referência; Solicitante; Subequipe; % Dentro do Prazo; Atendido Em; Categoria Dia Entrada Wf; Categoria Dia Prazo Atend; Data Prazo Atendimento 2; Data Rescisão; Dentro Prazo?; Efetivado?; Entrada Wf; Entrada Wf 2; Etapa Destino; Etapa Origem; Etapa Wf - Destino; Etapa Wf - Origem; Formulário Wf; Grupo Usuário; Id Formulário Wf; Id Grupo Usuário; Id Log Transação Wf; Id Workflow; Meta WFs; Nome Usuário; Novo Status Dentro Prazo; Prazo Atendimento 1º Dia Útil Próximo Mês; Prazo Atendimento Exceto Abertura Fim De Mês; Qtde Dentro do Prazo; Qtde Fora do Prazo; Status da Meta; Superior Hierárquico; Tempo Atendim Horas Uteis; Tempo Atendimento Hr</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Indicadores de Chamados e Workflows</v>
+      </c>
+      <c r="B29" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
+      </c>
+      <c r="C29" t="str">
+        <v>dCalendario; fChamadosEmAberto; fChamadosResolvidos; fWorkflowsEmAberto; fWorkflowsResolvidos</v>
+      </c>
+      <c r="D29" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Visão consolidada</v>
+      </c>
+      <c r="B30" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
+      </c>
+      <c r="C30" t="str">
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); PCD (Tableau)</v>
+      </c>
+      <c r="D30" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
+      </c>
+      <c r="E30" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula; PCD (Count); Qtd. Pcd</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Visão consolidada</v>
+      </c>
+      <c r="B31" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
+      </c>
+      <c r="C31" t="str">
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); PCD (Tableau)</v>
+      </c>
+      <c r="D31" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Zona Posicionamento Salarial</v>
+      </c>
+      <c r="B32" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
+      </c>
+      <c r="C32" t="str">
+        <v>RH - Base_Enios_Tableau; RH - Colaborador Folha</v>
+      </c>
+      <c r="D32" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/52187/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Admissão; Cargo; CL; Colaborador; Cpf; Dados gerados em; Diretoria; Dt Competencia; Dt inic cargo atual; Dt nasc; Gênero; Gestor; Grade; HR Reporting; Matrícula; Munic. cl; Nome do cl; Portfolio; Posição Faixa; Região cl; Segmento; Situação; Tipo cl; Uf cl; Zona posicionamento; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Zona Posicionamento Salarial</v>
+      </c>
+      <c r="B33" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
+      </c>
+      <c r="C33" t="str">
+        <v>RH - Base_Enios_Tableau; RH - Colaborador Folha</v>
+      </c>
+      <c r="D33" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/52187/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
+      </c>
+      <c r="B34" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
+      </c>
+      <c r="C34" t="str">
+        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Catracas; Base_Tableau; reserva_mesas_por_colaborador geral</v>
+      </c>
+      <c r="D34" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
+      </c>
+      <c r="E34" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Cardapio; Cd Centro Custo; Cd Empresa Sodexo; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Status; Cd Tipo Atuacao; Cd Tipo Servico; Cd Uf; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Competencia; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos; % Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Mesa; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
+      </c>
+      <c r="B35" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
+      </c>
+      <c r="C35" t="str">
+        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Catracas; Base_Tableau; reserva_mesas_por_colaborador geral</v>
+      </c>
+      <c r="D35" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Indicadores de Promoções Internas</v>
+      </c>
+      <c r="B36" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
+      </c>
+      <c r="C36" t="str">
+        <v>RH - Colaborador Folha</v>
+      </c>
+      <c r="D36" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+      </c>
+      <c r="E36" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Indicadores de Promoções Internas</v>
+      </c>
+      <c r="B37" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
+      </c>
+      <c r="C37" t="str">
+        <v>RH - Colaborador Folha</v>
+      </c>
+      <c r="D37" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Indicadores de Modelo de Trabalho - Home Office</v>
+      </c>
+      <c r="B38" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
+      </c>
+      <c r="C38" t="str">
+        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Tableau; reserva_mesas_por_colaborador geral</v>
+      </c>
+      <c r="D38" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
+      </c>
+      <c r="E38" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Cardapio; Cd Centro Custo; Cd Empresa Sodexo; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Status; Cd Tipo Atuacao; Cd Tipo Servico; Cd Uf; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; % Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Indicadores de Modelo de Trabalho - Home Office</v>
+      </c>
+      <c r="B39" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
+      </c>
+      <c r="C39" t="str">
+        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Tableau; reserva_mesas_por_colaborador geral</v>
+      </c>
+      <c r="D39" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Painel de Vagas Operacionais</v>
+      </c>
+      <c r="B40" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
+      </c>
+      <c r="C40" t="str">
+        <v>BIVARREDURA - Filial; RH - Colaborador Folha; RH STEP Abertura de Vagas</v>
+      </c>
+      <c r="D40" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
+      </c>
+      <c r="E40" t="str">
+        <v>[END] Bairro; [END] CEP; [END] Cidade; [END] LATITUDE; [END] Logadouro; [END] LONGITUDE; [END] UF; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_BUSINESS_UNIT; Dados migrados (Count); Dt Abertura; Dt Encerramento; Fili Email; Fl Ficticia; Inscricaoestadual; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Diretor Operacional; Nm Diretoria; Nm Empresa Sodexo; Nm Filial; Nm Gerente Area; Nm Gerente Regional; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial Colaborador; Cd Grupo CL; Cd Matriz Cardapio; Cd Matriz Compras; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Portfolio; CD_CARGO; CD_CARGO_HR_REPORTING; CD_CARGO_VAGA; CD_COTA_APRENDIZ_CBO; CD_ESTR_HIERAR; CD_ESTR_HIERAR_COLAB; CD_FILIAL_COLABORADOR; CD_FILIAL_VAGA; CD_FLEXIVEL_VAGA; CD_SINDICATO; CD_SITUACAO; CD_VAGA; CLASSIFICACAO_HR_REPORTING; COR_PELE; CPF; CTPS</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Painel de Vagas Operacionais</v>
+      </c>
+      <c r="B41" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
+      </c>
+      <c r="C41" t="str">
+        <v>BIVARREDURA - Filial; RH - Colaborador Folha; RH STEP Abertura de Vagas</v>
+      </c>
+      <c r="D41" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Pin People On e Off</v>
+      </c>
+      <c r="B42" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
+      </c>
+      <c r="C42" t="str">
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+      </c>
+      <c r="D42" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
+      </c>
+      <c r="E42" t="str">
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cargo de Confiança; Categoria; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Campo Calculado</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Pin People On e Off</v>
+      </c>
+      <c r="B43" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
+      </c>
+      <c r="C43" t="str">
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+      </c>
+      <c r="D43" t="str">
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>Nao e Campo Calculado</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F43"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/downloads/hr/output_automacao_hr.xlsx
+++ b/downloads/hr/output_automacao_hr.xlsx
@@ -7749,7 +7749,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:E22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7767,9 +7767,6 @@
       <c r="E1" t="str">
         <v>campos</v>
       </c>
-      <c r="F1" t="str">
-        <v>tipo_campo</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -7787,76 +7784,64 @@
       <c r="E2" t="str">
         <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula</v>
       </c>
-      <c r="F2" t="str">
-        <v>Campo Calculado</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Horas Extras e Absenteísmo</v>
+        <v>Indicadores RH</v>
       </c>
       <c r="B3" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/HorasExtraseAbsentesmo/AnalticoHorasExtras</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresRH_16860832510040/IndicadoresdeRH</v>
       </c>
       <c r="C3" t="str">
-        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau)</v>
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
       </c>
       <c r="D3" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1057/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
       </c>
       <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Indicadores RH</v>
+        <v>Base Colaboradores Geral</v>
       </c>
       <c r="B4" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresRH_16860832510040/IndicadoresdeRH</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basecolaboradoresgeral/Basecolaboradores</v>
       </c>
       <c r="C4" t="str">
-        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D4" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E4" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Campo Calculado</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Indicadores RH</v>
+        <v>Indicadores DE&amp;I</v>
       </c>
       <c r="B5" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresRH_16860832510040/IndicadoresdeRH</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
       </c>
       <c r="C5" t="str">
-        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; RH - Promoção; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
       </c>
       <c r="D5" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/638/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
       </c>
       <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Motivo Alteracao Grade; CEP; Cidade; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; Deficiencia; Dlg Dlsdesligamento; Cargo de Confiança; Categoria; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Base Colaboradores Geral</v>
+        <v>Book de Indicadores de Pessoas</v>
       </c>
       <c r="B6" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Basecolaboradoresgeral/Basecolaboradores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
       </c>
       <c r="C6" t="str">
         <v>RH - Colaborador Folha</v>
@@ -7867,76 +7852,64 @@
       <c r="E6" t="str">
         <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
-      <c r="F6" t="str">
-        <v>Campo Calculado</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Base Colaboradores Geral</v>
+        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
       </c>
       <c r="B7" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Basecolaboradoresgeral/Basecolaboradores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
       </c>
       <c r="C7" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Ponto Analitico RLS V2; RH - Colaborador Ponto Sintetico RLS; Ondas_Projeto_Ponto</v>
       </c>
       <c r="D7" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage; https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
       </c>
       <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Cálculo1; Cálculo2; CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO; CL; Clbr; Onda; Planilha1 (Count)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Indicadores DE&amp;I</v>
+        <v>Base de Férias em Aberto</v>
       </c>
       <c r="B8" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
       </c>
       <c r="C8" t="str">
-        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; RH - Promoção; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+        <v>RH - Colaborador Ponto Sintetico; RH - Programação de Férias</v>
       </c>
       <c r="D8" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/17222/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
       </c>
       <c r="E8" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Motivo Alteracao Grade; CEP; Cidade; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; Deficiencia; Dlg Dlsdesligamento; Cargo de Confiança; Categoria; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Campo Calculado</v>
+        <v>CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Indicadores DE&amp;I</v>
+        <v>Modelo de Trabalho</v>
       </c>
       <c r="B9" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresDEI/TurnoverAbsentesmoHorasExtrasPcD</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
       </c>
       <c r="C9" t="str">
-        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; RH - Promoção; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
+        <v>RH - Colaborador Folha</v>
       </c>
       <c r="D9" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48036/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1065/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Book de Indicadores de Pessoas</v>
+        <v>Banco de Horas</v>
       </c>
       <c r="B10" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
       </c>
       <c r="C10" t="str">
         <v>RH - Colaborador Folha</v>
@@ -7947,176 +7920,149 @@
       <c r="E10" t="str">
         <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
-      <c r="F10" t="str">
-        <v>Campo Calculado</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Book de Indicadores de Pessoas</v>
+        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
       </c>
       <c r="B11" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BookdeIndicadoresdePessoas/DashboardsdeRH</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
       </c>
       <c r="C11" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
       </c>
       <c r="D11" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
       </c>
       <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
+        <v>Metas Turnover FY26 - Regrettable e Demissional</v>
       </c>
       <c r="B12" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY26-RegrettableeDemissional/MetasdeRHFY26</v>
       </c>
       <c r="C12" t="str">
-        <v>RH - Colaborador Ponto Analitico RLS V2; RH - Colaborador Ponto Sintetico RLS; Ondas_Projeto_Ponto</v>
+        <v/>
       </c>
       <c r="D12" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage; https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E12" t="str">
-        <v>Cálculo1; Cálculo2; CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO; CL; Clbr; Onda; Planilha1 (Count)</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Projeto Ponto - Dashboard de Quantidade de Horas</v>
+        <v>Women Leadership</v>
       </c>
       <c r="B13" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ProjetoPonto-DashboarddeQuantidadedeHoras/ProjetoPonto-EventosAnaltico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
       </c>
       <c r="C13" t="str">
-        <v>RH - Colaborador Ponto Analitico RLS V2; RH - Colaborador Ponto Sintetico RLS; Ondas_Projeto_Ponto</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/57887/lineage; https://analyticsbi.sodexo.com.br/#/datasources/58934/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1275/lineage</v>
+        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
       </c>
       <c r="E13" t="str">
         <v/>
-      </c>
-      <c r="F13" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Base de Férias em Aberto</v>
+        <v>Wokforce Planning</v>
       </c>
       <c r="B14" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
       </c>
       <c r="C14" t="str">
-        <v>RH - Colaborador Ponto Sintetico; RH - Programação de Férias</v>
+        <v>RH - Colaborador Folha; DE-PARA_BU; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
       </c>
       <c r="D14" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/17222/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
       </c>
       <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v>Campo Calculado</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; FY; METAS (Count); Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Base de Férias em Aberto</v>
+        <v>Indicadores de Chamados e Workflows</v>
       </c>
       <c r="B15" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Basedefriasemaberto/Basedefriasemaberto</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
       </c>
       <c r="C15" t="str">
-        <v>RH - Colaborador Ponto Sintetico; RH - Programação de Férias</v>
+        <v>dCalendario; fChamadosEmAberto; fChamadosResolvidos; fWorkflowsEmAberto; fWorkflowsResolvidos</v>
       </c>
       <c r="D15" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/17222/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
       </c>
       <c r="E15" t="str">
-        <v>CD_BUSINESS_UNIT; COLAB_CBO; COLAB_CD_CARGO; COLAB_CD_ESTR_HIERAR; COLAB_CD_ESTR_HIERAR_COLAB; COLAB_CD_FILIAL_COLABORADOR; COLAB_CD_SINDICATO; COLAB_CD_SITUACAO; COLAB_COR_PELE; COLAB_CPF; COLAB_CTPS; COLAB_CTPS_SERIE; COLAB_DEFICIENCIA; COLAB_DLG_DLSDESLIGAMENTO; COLAB_DSC_CARGO; COLAB_DT_ADMISSAO; COLAB_DT_COMPETENCIA; COLAB_DT_FIM_CCUSTO; COLAB_DT_INICIO_AVISO_PREVIO; COLAB_DT_INICIO_CARGO; COLAB_DT_INICIO_CCUSTO; COLAB_DT_INICIO_SITUACAO; COLAB_DT_NASCIMENTO; COLAB_DT_PGTO_RESCISAO; COLAB_DT_REINTEGRACAO; COLAB_DT_RESCISAO; COLAB_E_MAIL; COLAB_ESTADO_CIVIL; COLAB_FLEG_CARGO_ELEGIVEL_JAPRENDIZ; COLAB_FLEG_ENQUADRAMENTO; COLAB_GESTOR; COLAB_GRADE; COLAB_GRAU_INSTRUCAO; COLAB_ID_FOLHA; COLAB_LOCAL; COLAB_MATRICULA; COLAB_MATRICULA_GESTOR; COLAB_MOTIVO_DESLIGAMENTO; COLAB_MOTIVO_REINTEGRACAO; COLAB_MUNICIPIO; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cardapio; Cd Cargo; Cd Cargo HR Reporting; Cd Centro Custo; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Empresa Sodexo; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd Status; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_HORARIO; CD_TP_FILIAL_COLABORADOR; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Ano; Ano Fiscal; Data; Dia; Dia da Semana; Dia da Semana ID; Extract (Count); Fiscal Year; Mês; Mês Abr; Mês Fiscal; Mês ID; Mês/Ano; Mês/Ano ID; Período Fiscal ID; Período/FY; Período/FY ID; Semana do Ano; Semana do Ano ID; Semana Fiscal do Ano; Semana Fiscal do Ano ID; Semana Fiscal/Ano ID; Semana/Ano; Semana/Ano ID; Semestre Fiscal / Ano ID; Semestre Fiscal do Ano; Semestre ID; Trimestre Fiscal; Trimestre Fiscal/Ano; Trimestre Fiscal/Ano ID; Assunto; Atribuído ao Usuário; Criador; Data de Conclusão Alvo; Data de Criação; Data Referência; Em nome de; Equipe Atribuída; Fila Atribuída; Fonte; Horas SLA; ID do caso; ID do Caso Relacionado; Prioridade; Solicitado por; Status do caso; Subtópico de RH; Tema de RH; % No Prazo; :Measure Names; Atingiu a Meta; Data de Conclusão Alvo Ajustada; Data de reabertura; Data Referência Resolução; Data/Hora da Primeira Resposta; Data/Hora Resolvida; Dia da Semana Criação; Fila Atribuída (Subequipe); Meta; Número do chamado; Período Fiscal; Qtde Em Atraso; Qtde No Prazo; Reabertos; Status do chamado; Status Prazo Primeiro Atendimento; Tempo de Resolução do Caso (Dias Úteis); Tempo de Trabalho em Dias Úteis; Tempo de trabalho em horas úteis (até agora); Total Atendimentos; Data da Etapa; Data prazo atendimento; Data Referencia; Data/hora início da transação; Dentro do prazo?; Equipe; Etapa de Workflow; Feriado; Formulário de Workflow; Id etapa de workflow; Id Formulário de Workflow; Id Lançamento de Workflow; Nome do Usuário; Referência; Solicitante; Subequipe; % Dentro do Prazo; Atendido Em; Categoria Dia Entrada Wf; Categoria Dia Prazo Atend; Data Prazo Atendimento 2; Data Rescisão; Dentro Prazo?; Efetivado?; Entrada Wf; Entrada Wf 2; Etapa Destino; Etapa Origem; Etapa Wf - Destino; Etapa Wf - Origem; Formulário Wf; Grupo Usuário; Id Formulário Wf; Id Grupo Usuário; Id Log Transação Wf; Id Workflow; Meta WFs; Nome Usuário; Novo Status Dentro Prazo; Prazo Atendimento 1º Dia Útil Próximo Mês; Prazo Atendimento Exceto Abertura Fim De Mês; Qtde Dentro do Prazo; Qtde Fora do Prazo; Status da Meta; Superior Hierárquico; Tempo Atendim Horas Uteis; Tempo Atendimento Hr</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Modelo de Trabalho</v>
+        <v>Visão consolidada</v>
       </c>
       <c r="B16" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
       </c>
       <c r="C16" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); PCD (Tableau)</v>
       </c>
       <c r="D16" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
       </c>
       <c r="E16" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Campo Calculado</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula; PCD (Count); Qtd. Pcd</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Modelo de Trabalho</v>
+        <v>Zona Posicionamento Salarial</v>
       </c>
       <c r="B17" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ModelodeTrabalho/ModelodeTrabalho</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
       </c>
       <c r="C17" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Base_Enios_Tableau; RH - Colaborador Folha</v>
       </c>
       <c r="D17" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/52187/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Admissão; Cargo; CL; Colaborador; Cpf; Dados gerados em; Diretoria; Dt Competencia; Dt inic cargo atual; Dt nasc; Gênero; Gestor; Grade; HR Reporting; Matrícula; Munic. cl; Nome do cl; Portfolio; Posição Faixa; Região cl; Segmento; Situação; Tipo cl; Uf cl; Zona posicionamento; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Banco de Horas</v>
+        <v>Base de Dados Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B18" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
       </c>
       <c r="C18" t="str">
-        <v>RH - Colaborador Folha</v>
+        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Catracas; Base_Tableau; reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D18" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
       </c>
       <c r="E18" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Campo Calculado</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Cardapio; Cd Centro Custo; Cd Empresa Sodexo; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Status; Cd Tipo Atuacao; Cd Tipo Servico; Cd Uf; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Competencia; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos; % Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Mesa; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Banco de Horas</v>
+        <v>Indicadores de Promoções Internas</v>
       </c>
       <c r="B19" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Bancodehoras/Bancodehoras</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
       </c>
       <c r="C19" t="str">
         <v>RH - Colaborador Folha</v>
@@ -8125,495 +8071,63 @@
         <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
+        <v>Indicadores de Modelo de Trabalho - Home Office</v>
       </c>
       <c r="B20" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
       </c>
       <c r="C20" t="str">
-        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Tableau; reserva_mesas_por_colaborador geral</v>
       </c>
       <c r="D20" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
       </c>
       <c r="E20" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; Diretoria; FY; METAS (Count); Segmento; Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Campo Calculado</v>
+        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Cardapio; Cd Centro Custo; Cd Empresa Sodexo; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Status; Cd Tipo Atuacao; Cd Tipo Servico; Cd Uf; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; % Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Metas Turnover FY25 - Regrettable e Demissional</v>
+        <v>Painel de Vagas Operacionais</v>
       </c>
       <c r="B21" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY25-RegrettableBoostereDemissional/METASDERHFY25</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
       </c>
       <c r="C21" t="str">
-        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
+        <v>BIVARREDURA - Filial; RH - Colaborador Folha; RH STEP Abertura de Vagas</v>
       </c>
       <c r="D21" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1853/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
       </c>
       <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>[END] Bairro; [END] CEP; [END] Cidade; [END] LATITUDE; [END] Logadouro; [END] LONGITUDE; [END] UF; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_BUSINESS_UNIT; Dados migrados (Count); Dt Abertura; Dt Encerramento; Fili Email; Fl Ficticia; Inscricaoestadual; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Diretor Operacional; Nm Diretoria; Nm Empresa Sodexo; Nm Filial; Nm Gerente Area; Nm Gerente Regional; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial Colaborador; Cd Grupo CL; Cd Matriz Cardapio; Cd Matriz Compras; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Portfolio; CD_CARGO; CD_CARGO_HR_REPORTING; CD_CARGO_VAGA; CD_COTA_APRENDIZ_CBO; CD_ESTR_HIERAR; CD_ESTR_HIERAR_COLAB; CD_FILIAL_COLABORADOR; CD_FILIAL_VAGA; CD_FLEXIVEL_VAGA; CD_SINDICATO; CD_SITUACAO; CD_VAGA; CLASSIFICACAO_HR_REPORTING; COR_PELE; CPF; CTPS</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Metas Turnover FY26 - Regrettable e Demissional</v>
+        <v>Pin People On e Off</v>
       </c>
       <c r="B22" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY26-RegrettableeDemissional/MetasdeRHFY26</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
       </c>
       <c r="D22" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
       </c>
       <c r="E22" t="str">
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Metas Turnover FY26 - Regrettable e Demissional</v>
-      </c>
-      <c r="B23" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MetasTurnoverFY26-RegrettableeDemissional/MetasdeRHFY26</v>
-      </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Women Leadership</v>
-      </c>
-      <c r="B24" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
-      </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Women Leadership</v>
-      </c>
-      <c r="B25" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WomenLeadership/IndicadoresWomenLeadership</v>
-      </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Wokforce Planning</v>
-      </c>
-      <c r="B26" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
-      </c>
-      <c r="C26" t="str">
-        <v>RH - Colaborador Folha; DE-PARA_BU; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
-      </c>
-      <c r="D26" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
-      </c>
-      <c r="E26" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; CL; DE PARA (Count); Diretoria; Nome do Centro de Lucro; Nome do Grupo Economico; Nome TLR; Nome TLR-1; Nome TLR-2; Nome TLR-3; Para BU; Para BU SAP; Para Diretoria; Para Diretoria SAP; Para Portfólio; Para Portfólio SAP; Para TLR; Para TLR-1; Para TLR-2; Para TLR-3; Para TLR BU; Portfólio; Segmento; Elegiveis cota aprendiz (Count); F4; Fração p/ Empregado; Função Para Cota Sim; Matrícula; Expurgo Pedido Demissao; Extract (Count); Matricula; FY; METAS (Count); Target Absenteismo; Target Horas Extras; :Measure Names; Absenteismo_Days (Count); Absenteismo_Days_Segmentos (Count); BRAZIL; CORPORATE; Data Compentecia; Data Competencia Womem; Days; Days (Absenteismo!Days!Segmentos); Dt Compentencia; Dt Competencia; Dt Competencia (Absenteismo!Days!Segmentos); Dt Competencia (Women Leardership); E&amp;R; EDUCATION; Filtro Absenteismo Segmentos; HEALTHCARE; KPI; Operacional; Other_KPIs_HR (Count); TARGET; Total; TRANSVERSAL; Women Leardership (Count); Promocoes; Promoções_Internas (Count)</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Wokforce Planning</v>
-      </c>
-      <c r="B27" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/WokforcePlanning/WorkforcePlanning</v>
-      </c>
-      <c r="C27" t="str">
-        <v>RH - Colaborador Folha; DE-PARA_BU; Elegiveis cota aprendiz (Tableau); EXPURGO_PEDIDO_DEMISSAO_FY24 Extração; METAS_HE_ABSENTEISMO; Other_KPIs_HR; Promoções_Internas</v>
-      </c>
-      <c r="D27" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2103/lineage</v>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-      <c r="F27" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Indicadores de Chamados e Workflows</v>
-      </c>
-      <c r="B28" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
-      </c>
-      <c r="C28" t="str">
-        <v>dCalendario; fChamadosEmAberto; fChamadosResolvidos; fWorkflowsEmAberto; fWorkflowsResolvidos</v>
-      </c>
-      <c r="D28" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
-      </c>
-      <c r="E28" t="str">
-        <v>Ano; Ano Fiscal; Data; Dia; Dia da Semana; Dia da Semana ID; Extract (Count); Fiscal Year; Mês; Mês Abr; Mês Fiscal; Mês ID; Mês/Ano; Mês/Ano ID; Período Fiscal ID; Período/FY; Período/FY ID; Semana do Ano; Semana do Ano ID; Semana Fiscal do Ano; Semana Fiscal do Ano ID; Semana Fiscal/Ano ID; Semana/Ano; Semana/Ano ID; Semestre Fiscal / Ano ID; Semestre Fiscal do Ano; Semestre ID; Trimestre Fiscal; Trimestre Fiscal/Ano; Trimestre Fiscal/Ano ID; Assunto; Atribuído ao Usuário; Criador; Data de Conclusão Alvo; Data de Criação; Data Referência; Em nome de; Equipe Atribuída; Fila Atribuída; Fonte; Horas SLA; ID do caso; ID do Caso Relacionado; Prioridade; Solicitado por; Status do caso; Subtópico de RH; Tema de RH; % No Prazo; :Measure Names; Atingiu a Meta; Data de Conclusão Alvo Ajustada; Data de reabertura; Data Referência Resolução; Data/Hora da Primeira Resposta; Data/Hora Resolvida; Dia da Semana Criação; Fila Atribuída (Subequipe); Meta; Número do chamado; Período Fiscal; Qtde Em Atraso; Qtde No Prazo; Reabertos; Status do chamado; Status Prazo Primeiro Atendimento; Tempo de Resolução do Caso (Dias Úteis); Tempo de Trabalho em Dias Úteis; Tempo de trabalho em horas úteis (até agora); Total Atendimentos; Data da Etapa; Data prazo atendimento; Data Referencia; Data/hora início da transação; Dentro do prazo?; Equipe; Etapa de Workflow; Feriado; Formulário de Workflow; Id etapa de workflow; Id Formulário de Workflow; Id Lançamento de Workflow; Nome do Usuário; Referência; Solicitante; Subequipe; % Dentro do Prazo; Atendido Em; Categoria Dia Entrada Wf; Categoria Dia Prazo Atend; Data Prazo Atendimento 2; Data Rescisão; Dentro Prazo?; Efetivado?; Entrada Wf; Entrada Wf 2; Etapa Destino; Etapa Origem; Etapa Wf - Destino; Etapa Wf - Origem; Formulário Wf; Grupo Usuário; Id Formulário Wf; Id Grupo Usuário; Id Log Transação Wf; Id Workflow; Meta WFs; Nome Usuário; Novo Status Dentro Prazo; Prazo Atendimento 1º Dia Útil Próximo Mês; Prazo Atendimento Exceto Abertura Fim De Mês; Qtde Dentro do Prazo; Qtde Fora do Prazo; Status da Meta; Superior Hierárquico; Tempo Atendim Horas Uteis; Tempo Atendimento Hr</v>
-      </c>
-      <c r="F28" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Indicadores de Chamados e Workflows</v>
-      </c>
-      <c r="B29" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeChamadoseWorkflows/Painel0-Home</v>
-      </c>
-      <c r="C29" t="str">
-        <v>dCalendario; fChamadosEmAberto; fChamadosResolvidos; fWorkflowsEmAberto; fWorkflowsResolvidos</v>
-      </c>
-      <c r="D29" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2227/lineage</v>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Visão consolidada</v>
-      </c>
-      <c r="B30" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
-      </c>
-      <c r="C30" t="str">
-        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); PCD (Tableau)</v>
-      </c>
-      <c r="D30" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
-      </c>
-      <c r="E30" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Elegiveis cota aprendiz (Count); Fração p/ Empregado; Função Para Cota Sim; Matrícula; PCD (Count); Qtd. Pcd</v>
-      </c>
-      <c r="F30" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Visão consolidada</v>
-      </c>
-      <c r="B31" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Visoconsolidada/Consolidadodedados</v>
-      </c>
-      <c r="C31" t="str">
-        <v>RH - Colaborador Folha; Elegiveis cota aprendiz (Tableau); PCD (Tableau)</v>
-      </c>
-      <c r="D31" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/700/lineage</v>
-      </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
-      <c r="F31" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Zona Posicionamento Salarial</v>
-      </c>
-      <c r="B32" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
-      </c>
-      <c r="C32" t="str">
-        <v>RH - Base_Enios_Tableau; RH - Colaborador Folha</v>
-      </c>
-      <c r="D32" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/52187/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
-      </c>
-      <c r="E32" t="str">
-        <v>Admissão; Cargo; CL; Colaborador; Cpf; Dados gerados em; Diretoria; Dt Competencia; Dt inic cargo atual; Dt nasc; Gênero; Gestor; Grade; HR Reporting; Matrícula; Munic. cl; Nome do cl; Portfolio; Posição Faixa; Região cl; Segmento; Situação; Tipo cl; Uf cl; Zona posicionamento; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
-      </c>
-      <c r="F32" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Zona Posicionamento Salarial</v>
-      </c>
-      <c r="B33" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ZonaPosicionamentoSalarial/ZonasdePosicionamentoSalarial</v>
-      </c>
-      <c r="C33" t="str">
-        <v>RH - Base_Enios_Tableau; RH - Colaborador Folha</v>
-      </c>
-      <c r="D33" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/52187/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
-      </c>
-      <c r="E33" t="str">
-        <v/>
-      </c>
-      <c r="F33" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Base de Dados Modelo de Trabalho - Home Office</v>
-      </c>
-      <c r="B34" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
-      </c>
-      <c r="C34" t="str">
-        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Catracas; Base_Tableau; reserva_mesas_por_colaborador geral</v>
-      </c>
-      <c r="D34" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
-      </c>
-      <c r="E34" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Cardapio; Cd Centro Custo; Cd Empresa Sodexo; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Status; Cd Tipo Atuacao; Cd Tipo Servico; Cd Uf; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; Competencia; Data Acesso; Email; Empresa; Eqp Id; Equipamento; ES; Hora Acesso; Matricula; Nome; Planilha1 (Count); Qt Acessos; % Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Mesa; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt de Checkin; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
-      </c>
-      <c r="F34" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Base de Dados Modelo de Trabalho - Home Office</v>
-      </c>
-      <c r="B35" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BasedeDadosModelodeTrabalho-HomeOffice/BASEOFICIALPARATABLEAU</v>
-      </c>
-      <c r="C35" t="str">
-        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Catracas; Base_Tableau; reserva_mesas_por_colaborador geral</v>
-      </c>
-      <c r="D35" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2183/lineage</v>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-      <c r="F35" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Indicadores de Promoções Internas</v>
-      </c>
-      <c r="B36" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
-      </c>
-      <c r="C36" t="str">
-        <v>RH - Colaborador Folha</v>
-      </c>
-      <c r="D36" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
-      </c>
-      <c r="E36" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
-      </c>
-      <c r="F36" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Indicadores de Promoções Internas</v>
-      </c>
-      <c r="B37" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdePromoesInternas/PromoesInternas</v>
-      </c>
-      <c r="C37" t="str">
-        <v>RH - Colaborador Folha</v>
-      </c>
-      <c r="D37" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
-      </c>
-      <c r="E37" t="str">
-        <v/>
-      </c>
-      <c r="F37" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Indicadores de Modelo de Trabalho - Home Office</v>
-      </c>
-      <c r="B38" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
-      </c>
-      <c r="C38" t="str">
-        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Tableau; reserva_mesas_por_colaborador geral</v>
-      </c>
-      <c r="D38" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
-      </c>
-      <c r="E38" t="str">
-        <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Cardapio; Cd Centro Custo; Cd Empresa Sodexo; Cd Filial Ficticia; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Período Descanso; Cd Status; Cd Tipo Atuacao; Cd Tipo Servico; Cd Uf; Classificação HR Reporting; Cor Pele; Cpf; Ctps; Ctps Serie; DATABASE; AFAST_CARGO; AFAST_CD_FILIAL; AFAST_CD_SITUACAO; AFAST_CID_DOENCA; AFAST_CID_DOENCA_OFICIAL; AFAST_DSC_DOENCA; AFAST_DSC_MOTIVO_SITUACAO; AFAST_DT_CARGA; AFAST_DT_COMPETENCIA; AFAST_DT_FIM; AFAST_DT_INICIO; AFAST_MATRICULA; AFAST_MOTIVO; AFAST_QT_DIAS_AFASTAMENTO; AFAST_QT_DIAS_AFASTAMENTO_STEP; AFAST_SITUACAO; % Conformidade Hibrido Dentro da Meta; % Conformidade Hibrido Fora da Meta; % Conformidade Home 100%; % Conformidade Home Geral; % Conformidade Home Hibrido; :Measure Names; Analise Qt Check-in; Analise Qt Check-in 2; Base_Tableau (Count); Business Unit; Competência; Cor Conformidade; Dias de afastamento no mês; Dias de férias no mês; Dsc Cargo; Dt Admissao; Elegiveis por UF; Email Gestor; Flag Last 6 Month; Flag Mes Atual; Gestor; Matricula; Matricula Gestor; Modelo de Trabalho; Nm Diretoria; Nm Filial; Nm Segmento; Nome Colaborador; Qt Check-in; Qt Check-in Filtro; Qt Colab Divergente Home 100%; Qt Colab Divergente Home Hibrido; Qt Colaboradores; Qt Colaboradores Filtro; Qt de Check-in; Qt Home Office 100%; Qt Home Office 100% em conformidade; Qt Home Office 100% Não conformidade; Qt Home Office em conformidade; Andar; Cancelado por; Check-in &lt;4; Check-in realizado; Check-out realizado; Competencia; Data da solicitação; Data de cancelamento; Data do check-in; Data do check-out; Data final; Data inicial; E-mail; Id; Mesa; Nome; Plan1 (Count); Planta; Qt Checkin Home Office 100% Divergente; Qt Colab Home Office 100% Divergente; Qt Colab Home Office Hibrido Divergente; Qt Errada Hibrido; Status; Tirou férias no mês?; Total de Check-in; Total de Check-in DIM; Total de Checkin</v>
-      </c>
-      <c r="F38" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Indicadores de Modelo de Trabalho - Home Office</v>
-      </c>
-      <c r="B39" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IndicadoresdeModelodeTrabalho-HomeOffice_17522412067850/DashboardHomeOffice-Colaboradores</v>
-      </c>
-      <c r="C39" t="str">
-        <v>RH - Colaborador Folha; RH - Programação de Férias; RH STEP Afastamento; Base_Tableau; reserva_mesas_por_colaborador geral</v>
-      </c>
-      <c r="D39" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48035/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48064/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2169/lineage</v>
-      </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
-      <c r="F39" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>Painel de Vagas Operacionais</v>
-      </c>
-      <c r="B40" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
-      </c>
-      <c r="C40" t="str">
-        <v>BIVARREDURA - Filial; RH - Colaborador Folha; RH STEP Abertura de Vagas</v>
-      </c>
-      <c r="D40" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
-      </c>
-      <c r="E40" t="str">
-        <v>[END] Bairro; [END] CEP; [END] Cidade; [END] LATITUDE; [END] Logadouro; [END] LONGITUDE; [END] UF; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Grupo Economico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; CD_BUSINESS_UNIT; Dados migrados (Count); Dt Abertura; Dt Encerramento; Fili Email; Fl Ficticia; Inscricaoestadual; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Diretor Operacional; Nm Diretoria; Nm Empresa Sodexo; Nm Filial; Nm Gerente Area; Nm Gerente Regional; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial Colaborador; Cd Grupo CL; Cd Matriz Cardapio; Cd Matriz Compras; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cd Portfolio; CD_CARGO; CD_CARGO_HR_REPORTING; CD_CARGO_VAGA; CD_COTA_APRENDIZ_CBO; CD_ESTR_HIERAR; CD_ESTR_HIERAR_COLAB; CD_FILIAL_COLABORADOR; CD_FILIAL_VAGA; CD_FLEXIVEL_VAGA; CD_SINDICATO; CD_SITUACAO; CD_VAGA; CLASSIFICACAO_HR_REPORTING; COR_PELE; CPF; CTPS</v>
-      </c>
-      <c r="F40" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Painel de Vagas Operacionais</v>
-      </c>
-      <c r="B41" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeVagasOperacionais/AnlisesdeVagasOperacionais</v>
-      </c>
-      <c r="C41" t="str">
-        <v>BIVARREDURA - Filial; RH - Colaborador Folha; RH STEP Abertura de Vagas</v>
-      </c>
-      <c r="D41" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/23931/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48063/lineage</v>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Pin People On e Off</v>
-      </c>
-      <c r="B42" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
-      </c>
-      <c r="C42" t="str">
-        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
-      </c>
-      <c r="D42" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
-      </c>
-      <c r="E42" t="str">
         <v>% Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Cargo de Confiança; Categoria; Cota Aprendiz; Elegibilidade; Elegibilidade CBO; Grade; ID Elegibilidade Cota JA; Id Nível Hierárquico; Job Family; Job Family Group; Job Title - Inglês; Job Title - Português; Nível Hierárquico; Nível Superior; tbElegibilidade_Cargo (Count)</v>
-      </c>
-      <c r="F42" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Pin People On e Off</v>
-      </c>
-      <c r="B43" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PinPeopleOneOff/PinPeople</v>
-      </c>
-      <c r="C43" t="str">
-        <v>RH - Colaborador Folha | Projeto : Fonte de Dados Corporativa; tbElegibilidade_Cargo (db_Elegilidade_Cargos)</v>
-      </c>
-      <c r="D43" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1009/lineage</v>
-      </c>
-      <c r="E43" t="str">
-        <v/>
-      </c>
-      <c r="F43" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
   </ignoredErrors>
 </worksheet>
 </file>